--- a/epsilon-phi-core/src/python/epsilonPhi/core/reporting/formatted_excel.xlsx
+++ b/epsilon-phi-core/src/python/epsilonPhi/core/reporting/formatted_excel.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/python/epsilonPhi/core/reporting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/python/epsilonPhi/core/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA74BDD-380D-4847-B951-17347511899F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86582B5F-B302-1F41-8EA7-2F5FF1A2D7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="5020" windowWidth="35520" windowHeight="23160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3100" yWindow="500" windowWidth="33600" windowHeight="19040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="Portfolios" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Risk-Metrics" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="Factor Charts" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="5" r:id="rId5"/>
     <sheet name="RAW WEIGHTS" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet5" sheetId="11" r:id="rId7"/>
     <sheet name="Sheet3" sheetId="9" r:id="rId8"/>
@@ -4008,7 +4008,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="mmm\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="mmm\ yyyy;@"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -4030,6 +4030,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4641,45 +4642,6 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4691,9 +4653,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4711,7 +4670,7 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4721,7 +4680,7 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4730,7 +4689,7 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4743,7 +4702,7 @@
     <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4784,6 +4743,48 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6735,232 +6736,232 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="57"/>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103" t="s">
+      <c r="C1" s="133"/>
+      <c r="D1" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103" t="s">
+      <c r="G1" s="133"/>
+      <c r="H1" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="104"/>
+      <c r="I1" s="139"/>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="105">
+      <c r="B2" s="132">
         <v>0.745</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105">
+      <c r="E2" s="132"/>
+      <c r="F2" s="132">
         <v>0.36</v>
       </c>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105">
+      <c r="G2" s="132"/>
+      <c r="H2" s="132">
         <v>0.15</v>
       </c>
-      <c r="I2" s="105"/>
+      <c r="I2" s="132"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="98">
+      <c r="B3" s="134">
         <v>0.02</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98">
+      <c r="C3" s="134"/>
+      <c r="D3" s="134">
         <v>0.03</v>
       </c>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98">
+      <c r="E3" s="134"/>
+      <c r="F3" s="134">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98">
+      <c r="G3" s="134"/>
+      <c r="H3" s="134">
         <v>5.5E-2</v>
       </c>
-      <c r="I3" s="98"/>
+      <c r="I3" s="134"/>
     </row>
     <row r="4" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="134">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98">
+      <c r="C4" s="134"/>
+      <c r="D4" s="134">
         <v>0.22500000000000001</v>
       </c>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98">
+      <c r="E4" s="134"/>
+      <c r="F4" s="134">
         <v>0.35499999999999998</v>
       </c>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98">
+      <c r="G4" s="134"/>
+      <c r="H4" s="134">
         <v>0.505</v>
       </c>
-      <c r="I4" s="98"/>
+      <c r="I4" s="134"/>
     </row>
     <row r="5" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="98">
+      <c r="B5" s="134">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98">
+      <c r="C5" s="134"/>
+      <c r="D5" s="134">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98">
+      <c r="E5" s="134"/>
+      <c r="F5" s="134">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98">
+      <c r="G5" s="134"/>
+      <c r="H5" s="134">
         <v>0.03</v>
       </c>
-      <c r="I5" s="98"/>
+      <c r="I5" s="134"/>
     </row>
     <row r="6" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="98">
+      <c r="B6" s="134">
         <v>0.04</v>
       </c>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98">
+      <c r="C6" s="134"/>
+      <c r="D6" s="134">
         <v>5.5E-2</v>
       </c>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98">
+      <c r="E6" s="134"/>
+      <c r="F6" s="134">
         <v>0.12</v>
       </c>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98">
+      <c r="G6" s="134"/>
+      <c r="H6" s="134">
         <v>0.185</v>
       </c>
-      <c r="I6" s="98"/>
+      <c r="I6" s="134"/>
     </row>
     <row r="7" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="99">
+      <c r="B7" s="138">
         <v>0.04</v>
       </c>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99">
+      <c r="C7" s="138"/>
+      <c r="D7" s="138">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99">
+      <c r="E7" s="138"/>
+      <c r="F7" s="138">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99">
+      <c r="G7" s="138"/>
+      <c r="H7" s="138">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I7" s="99"/>
+      <c r="I7" s="138"/>
     </row>
     <row r="8" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="100">
+      <c r="B8" s="137">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100">
+      <c r="C8" s="137"/>
+      <c r="D8" s="137">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100">
+      <c r="E8" s="137"/>
+      <c r="F8" s="137">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100">
+      <c r="G8" s="137"/>
+      <c r="H8" s="137">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="I8" s="100"/>
+      <c r="I8" s="137"/>
     </row>
     <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="101">
+      <c r="B9" s="136">
         <v>0.6</v>
       </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101">
+      <c r="C9" s="136"/>
+      <c r="D9" s="136">
         <v>0.59</v>
       </c>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101">
+      <c r="E9" s="136"/>
+      <c r="F9" s="136">
         <v>0.53</v>
       </c>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101">
+      <c r="G9" s="136"/>
+      <c r="H9" s="136">
         <v>0.49</v>
       </c>
-      <c r="I9" s="101"/>
+      <c r="I9" s="136"/>
     </row>
     <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="98">
+      <c r="B10" s="134">
         <v>3.1E-2</v>
       </c>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98">
+      <c r="C10" s="134"/>
+      <c r="D10" s="134">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98">
+      <c r="E10" s="134"/>
+      <c r="F10" s="134">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98">
+      <c r="G10" s="134"/>
+      <c r="H10" s="134">
         <v>0.10299999999999999</v>
       </c>
-      <c r="I10" s="98"/>
+      <c r="I10" s="134"/>
     </row>
     <row r="11" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102" t="s">
+      <c r="C11" s="135"/>
+      <c r="D11" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102" t="s">
+      <c r="E11" s="135"/>
+      <c r="F11" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102" t="s">
+      <c r="G11" s="135"/>
+      <c r="H11" s="135" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="102"/>
+      <c r="I11" s="135"/>
     </row>
     <row r="12" spans="1:9" s="10" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="63" t="s">
@@ -7253,64 +7254,64 @@
       <c r="A23" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="96">
+      <c r="B23" s="140">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96">
+      <c r="C23" s="140"/>
+      <c r="D23" s="140">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96">
+      <c r="E23" s="140"/>
+      <c r="F23" s="140">
         <v>6.3E-2</v>
       </c>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96">
+      <c r="G23" s="140"/>
+      <c r="H23" s="140">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="I23" s="96"/>
+      <c r="I23" s="140"/>
     </row>
     <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="96">
+      <c r="B24" s="140">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96">
+      <c r="C24" s="140"/>
+      <c r="D24" s="140">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96">
+      <c r="E24" s="140"/>
+      <c r="F24" s="140">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96">
+      <c r="G24" s="140"/>
+      <c r="H24" s="140">
         <v>0.24299999999999999</v>
       </c>
-      <c r="I24" s="96"/>
+      <c r="I24" s="140"/>
     </row>
     <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="97">
+      <c r="B25" s="141">
         <v>0</v>
       </c>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97">
+      <c r="C25" s="141"/>
+      <c r="D25" s="141">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="E25" s="97"/>
-      <c r="F25" s="97">
+      <c r="E25" s="141"/>
+      <c r="F25" s="141">
         <v>0.14899999999999999</v>
       </c>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97">
+      <c r="G25" s="141"/>
+      <c r="H25" s="141">
         <v>0.253</v>
       </c>
-      <c r="I25" s="97"/>
+      <c r="I25" s="141"/>
     </row>
     <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="71" t="s">
@@ -7329,64 +7330,64 @@
       <c r="A27" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="96">
+      <c r="B27" s="140">
         <v>0.23799999999999999</v>
       </c>
-      <c r="C27" s="96"/>
-      <c r="D27" s="96">
+      <c r="C27" s="140"/>
+      <c r="D27" s="140">
         <v>0.27900000000000003</v>
       </c>
-      <c r="E27" s="96"/>
-      <c r="F27" s="96">
+      <c r="E27" s="140"/>
+      <c r="F27" s="140">
         <v>0.314</v>
       </c>
-      <c r="G27" s="96"/>
-      <c r="H27" s="96">
+      <c r="G27" s="140"/>
+      <c r="H27" s="140">
         <v>0.33700000000000002</v>
       </c>
-      <c r="I27" s="96"/>
+      <c r="I27" s="140"/>
     </row>
     <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="96">
+      <c r="B28" s="140">
         <v>0.04</v>
       </c>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96">
+      <c r="C28" s="140"/>
+      <c r="D28" s="140">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="E28" s="96"/>
-      <c r="F28" s="96">
+      <c r="E28" s="140"/>
+      <c r="F28" s="140">
         <v>0.14299999999999999</v>
       </c>
-      <c r="G28" s="96"/>
-      <c r="H28" s="96">
+      <c r="G28" s="140"/>
+      <c r="H28" s="140">
         <v>0.187</v>
       </c>
-      <c r="I28" s="96"/>
+      <c r="I28" s="140"/>
     </row>
     <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="96">
+      <c r="B29" s="140">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96">
+      <c r="C29" s="140"/>
+      <c r="D29" s="140">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="E29" s="96"/>
-      <c r="F29" s="96">
+      <c r="E29" s="140"/>
+      <c r="F29" s="140">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G29" s="96"/>
-      <c r="H29" s="96">
+      <c r="G29" s="140"/>
+      <c r="H29" s="140">
         <v>0.108</v>
       </c>
-      <c r="I29" s="96"/>
+      <c r="I29" s="140"/>
     </row>
     <row r="30" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="63" t="s">
@@ -7780,11 +7781,56 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="B5:C5"/>
@@ -7798,56 +7844,11 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B14:I21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
@@ -8031,16 +8032,16 @@
   <sheetData>
     <row r="1" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23"/>
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="144" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
       <c r="J1" s="25"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
@@ -8048,13 +8049,13 @@
     </row>
     <row r="2" spans="1:16" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26"/>
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
       <c r="G2" s="28" t="s">
         <v>32</v>
       </c>
@@ -9867,7 +9868,7 @@
       <c r="B2" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="97" t="s">
         <v>163</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -9879,7 +9880,7 @@
       <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="110" t="s">
+      <c r="G2" s="97" t="s">
         <v>165</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -9922,10 +9923,10 @@
       <c r="H4" s="3">
         <v>1</v>
       </c>
-      <c r="I4" s="109">
+      <c r="I4" s="96">
         <v>34365</v>
       </c>
-      <c r="J4" s="109">
+      <c r="J4" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -9954,10 +9955,10 @@
       <c r="H5" s="3">
         <v>1</v>
       </c>
-      <c r="I5" s="109">
+      <c r="I5" s="96">
         <v>34365</v>
       </c>
-      <c r="J5" s="109">
+      <c r="J5" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -9986,10 +9987,10 @@
       <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="I6" s="109">
+      <c r="I6" s="96">
         <v>34365</v>
       </c>
-      <c r="J6" s="109">
+      <c r="J6" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10023,10 +10024,10 @@
       <c r="H8" s="3">
         <v>0</v>
       </c>
-      <c r="I8" s="109">
+      <c r="I8" s="96">
         <v>26723</v>
       </c>
-      <c r="J8" s="109">
+      <c r="J8" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10055,10 +10056,10 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="109">
+      <c r="I9" s="96">
         <v>33662</v>
       </c>
-      <c r="J9" s="109">
+      <c r="J9" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10092,10 +10093,10 @@
       <c r="H11" s="3">
         <v>0</v>
       </c>
-      <c r="I11" s="109">
+      <c r="I11" s="96">
         <v>30589</v>
       </c>
-      <c r="J11" s="109">
+      <c r="J11" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10129,10 +10130,10 @@
       <c r="H13" s="3">
         <v>0</v>
       </c>
-      <c r="I13" s="109">
+      <c r="I13" s="96">
         <v>30589</v>
       </c>
-      <c r="J13" s="109">
+      <c r="J13" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10161,10 +10162,10 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="109">
+      <c r="I14" s="96">
         <v>30650</v>
       </c>
-      <c r="J14" s="109">
+      <c r="J14" s="96">
         <v>44925</v>
       </c>
     </row>
@@ -10193,10 +10194,10 @@
       <c r="H15" s="3">
         <v>0</v>
       </c>
-      <c r="I15" s="109">
+      <c r="I15" s="96">
         <v>30680</v>
       </c>
-      <c r="J15" s="109">
+      <c r="J15" s="96">
         <v>44925</v>
       </c>
     </row>
@@ -10230,10 +10231,10 @@
       <c r="H17" s="3">
         <v>0</v>
       </c>
-      <c r="I17" s="109">
+      <c r="I17" s="96">
         <v>25598</v>
       </c>
-      <c r="J17" s="109">
+      <c r="J17" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10262,10 +10263,10 @@
       <c r="H18" s="3">
         <v>0</v>
       </c>
-      <c r="I18" s="109">
+      <c r="I18" s="96">
         <v>34365</v>
       </c>
-      <c r="J18" s="109">
+      <c r="J18" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10294,10 +10295,10 @@
       <c r="H19" s="3">
         <v>0</v>
       </c>
-      <c r="I19" s="109">
+      <c r="I19" s="96">
         <v>30680</v>
       </c>
-      <c r="J19" s="109">
+      <c r="J19" s="96">
         <v>44925</v>
       </c>
     </row>
@@ -10331,10 +10332,10 @@
       <c r="H21" s="3">
         <v>0</v>
       </c>
-      <c r="I21" s="109">
+      <c r="I21" s="96">
         <v>28886</v>
       </c>
-      <c r="J21" s="109">
+      <c r="J21" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10363,10 +10364,10 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="109">
+      <c r="I22" s="96">
         <v>28886</v>
       </c>
-      <c r="J22" s="109">
+      <c r="J22" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10395,10 +10396,10 @@
       <c r="H23" s="3">
         <v>0</v>
       </c>
-      <c r="I23" s="109">
+      <c r="I23" s="96">
         <v>28886</v>
       </c>
-      <c r="J23" s="109">
+      <c r="J23" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10427,10 +10428,10 @@
       <c r="H24" s="3">
         <v>0.7</v>
       </c>
-      <c r="I24" s="109">
+      <c r="I24" s="96">
         <v>25626</v>
       </c>
-      <c r="J24" s="109">
+      <c r="J24" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10459,10 +10460,10 @@
       <c r="H25" s="3">
         <v>0.7</v>
       </c>
-      <c r="I25" s="109">
+      <c r="I25" s="96">
         <v>25598</v>
       </c>
-      <c r="J25" s="109">
+      <c r="J25" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10491,10 +10492,10 @@
       <c r="H26" s="3">
         <v>0.7</v>
       </c>
-      <c r="I26" s="109">
+      <c r="I26" s="96">
         <v>25598</v>
       </c>
-      <c r="J26" s="109">
+      <c r="J26" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10523,10 +10524,10 @@
       <c r="H27" s="3">
         <v>0.7</v>
       </c>
-      <c r="I27" s="109">
+      <c r="I27" s="96">
         <v>25626</v>
       </c>
-      <c r="J27" s="109">
+      <c r="J27" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10555,10 +10556,10 @@
       <c r="H28" s="3">
         <v>0</v>
       </c>
-      <c r="I28" s="109">
+      <c r="I28" s="96">
         <v>32171</v>
       </c>
-      <c r="J28" s="109">
+      <c r="J28" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10587,10 +10588,10 @@
       <c r="H29" s="3">
         <v>0.7</v>
       </c>
-      <c r="I29" s="109">
+      <c r="I29" s="96">
         <v>32720</v>
       </c>
-      <c r="J29" s="109">
+      <c r="J29" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10619,10 +10620,10 @@
       <c r="H30" s="3">
         <v>0.7</v>
       </c>
-      <c r="I30" s="109">
+      <c r="I30" s="96">
         <v>36189</v>
       </c>
-      <c r="J30" s="109">
+      <c r="J30" s="96">
         <v>45777</v>
       </c>
     </row>
@@ -10646,59 +10647,59 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
-      <c r="B1" s="113" t="s">
+      <c r="B1" s="145" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="113" t="s">
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="145" t="s">
         <v>168</v>
       </c>
-      <c r="J1" s="113"/>
+      <c r="J1" s="145"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" s="10" customFormat="1" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" s="116"/>
-      <c r="B2" s="117" t="s">
+      <c r="A2" s="102"/>
+      <c r="B2" s="103" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="118" t="s">
+      <c r="C2" s="104" t="s">
         <v>163</v>
       </c>
-      <c r="D2" s="117" t="s">
+      <c r="D2" s="103" t="s">
         <v>164</v>
       </c>
-      <c r="E2" s="117" t="s">
+      <c r="E2" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="117" t="s">
+      <c r="F2" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="118" t="s">
+      <c r="G2" s="104" t="s">
         <v>165</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="H2" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="J2" s="103" t="s">
         <v>167</v>
       </c>
-      <c r="K2" s="141" t="s">
+      <c r="K2" s="127" t="s">
         <v>169</v>
       </c>
-      <c r="L2" s="117" t="s">
+      <c r="L2" s="103" t="s">
         <v>170</v>
       </c>
-      <c r="M2" s="133" t="s">
+      <c r="M2" s="119" t="s">
         <v>171</v>
       </c>
     </row>
@@ -10706,59 +10707,59 @@
       <c r="A3" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="135"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="121"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="112">
+      <c r="B4" s="99">
         <v>5.7241236937856403E-3</v>
       </c>
-      <c r="C4" s="112">
+      <c r="C4" s="99">
         <v>1.08524678406041E-2</v>
       </c>
-      <c r="D4" s="112">
+      <c r="D4" s="99">
         <v>1.59808119874227E-2</v>
       </c>
-      <c r="E4" s="112">
+      <c r="E4" s="99">
         <v>3.2071468696963902E-2</v>
       </c>
-      <c r="F4" s="114">
+      <c r="F4" s="100">
         <v>0.33838387456298602</v>
       </c>
-      <c r="G4" s="112">
+      <c r="G4" s="99">
         <v>3.5852467840604099E-2</v>
       </c>
-      <c r="H4" s="112">
+      <c r="H4" s="99">
         <v>0</v>
       </c>
-      <c r="I4" s="120">
+      <c r="I4" s="106">
         <v>26723</v>
       </c>
-      <c r="J4" s="120">
+      <c r="J4" s="106">
         <v>45777</v>
       </c>
-      <c r="K4" s="143">
+      <c r="K4" s="129">
         <f>Assumptions!D4</f>
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="L4" s="136">
+      <c r="L4" s="122">
         <f>C4</f>
         <v>1.08524678406041E-2</v>
       </c>
-      <c r="M4" s="137">
+      <c r="M4" s="123">
         <f>L4-K4</f>
         <v>-1.4753215939589982E-4</v>
       </c>
@@ -10767,42 +10768,42 @@
       <c r="A5" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="112">
+      <c r="B5" s="99">
         <v>4.32971260588862E-4</v>
       </c>
-      <c r="C5" s="112">
+      <c r="C5" s="99">
         <v>3.0821903711752401E-3</v>
       </c>
-      <c r="D5" s="112">
+      <c r="D5" s="99">
         <v>5.73140948176162E-3</v>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="99">
         <v>1.4716286970652999E-2</v>
       </c>
-      <c r="F5" s="114">
+      <c r="F5" s="100">
         <v>0.20944076296702299</v>
       </c>
-      <c r="G5" s="112">
+      <c r="G5" s="99">
         <v>2.8082190371175202E-2</v>
       </c>
-      <c r="H5" s="112">
+      <c r="H5" s="99">
         <v>0</v>
       </c>
-      <c r="I5" s="120">
+      <c r="I5" s="106">
         <v>33662</v>
       </c>
-      <c r="J5" s="120">
+      <c r="J5" s="106">
         <v>45777</v>
       </c>
-      <c r="K5" s="143">
+      <c r="K5" s="129">
         <f>Assumptions!D5</f>
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L5" s="136">
+      <c r="L5" s="122">
         <f t="shared" ref="L5:L30" si="0">C5</f>
         <v>3.0821903711752401E-3</v>
       </c>
-      <c r="M5" s="137">
+      <c r="M5" s="123">
         <f t="shared" ref="M5:M30" si="1">L5-K5</f>
         <v>-9.1780962882475996E-4</v>
       </c>
@@ -10811,59 +10812,59 @@
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="112"/>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="112"/>
-      <c r="F6" s="114"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="143"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="137"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="123"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="129" t="s">
+      <c r="A7" s="115" t="s">
         <v>154</v>
       </c>
-      <c r="B7" s="130">
+      <c r="B7" s="116">
         <v>2.64039774019777E-2</v>
       </c>
-      <c r="C7" s="130">
+      <c r="C7" s="116">
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="D7" s="130">
+      <c r="D7" s="116">
         <v>6.0324053411324102E-2</v>
       </c>
-      <c r="E7" s="130">
+      <c r="E7" s="116">
         <v>0.106064123700363</v>
       </c>
-      <c r="F7" s="131">
+      <c r="F7" s="117">
         <v>0.40884715673658401</v>
       </c>
-      <c r="G7" s="130">
+      <c r="G7" s="116">
         <v>6.8364015406650894E-2</v>
       </c>
-      <c r="H7" s="130">
+      <c r="H7" s="116">
         <v>0</v>
       </c>
-      <c r="I7" s="132">
+      <c r="I7" s="118">
         <v>30589</v>
       </c>
-      <c r="J7" s="132">
+      <c r="J7" s="118">
         <v>45777</v>
       </c>
-      <c r="K7" s="144">
+      <c r="K7" s="130">
         <f>Assumptions!D7</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="L7" s="138">
+      <c r="L7" s="124">
         <f t="shared" si="0"/>
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="M7" s="139">
+      <c r="M7" s="125">
         <f t="shared" si="1"/>
         <v>8.3640154066508959E-3</v>
       </c>
@@ -10872,59 +10873,59 @@
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="114"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="120"/>
-      <c r="K8" s="143"/>
-      <c r="L8" s="136"/>
-      <c r="M8" s="137"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="106"/>
+      <c r="K8" s="129"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="123"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="129" t="s">
+      <c r="A9" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="130">
+      <c r="B9" s="116">
         <v>1.7523010713942501E-2</v>
       </c>
-      <c r="C9" s="130">
+      <c r="C9" s="116">
         <v>4.4567317353041203E-2</v>
       </c>
-      <c r="D9" s="130">
+      <c r="D9" s="116">
         <v>7.1611623992139897E-2</v>
       </c>
-      <c r="E9" s="130">
+      <c r="E9" s="116">
         <v>0.16912878874266299</v>
       </c>
-      <c r="F9" s="131">
+      <c r="F9" s="117">
         <v>0.26351112477280397</v>
       </c>
-      <c r="G9" s="130">
+      <c r="G9" s="116">
         <v>6.9567317353041197E-2</v>
       </c>
-      <c r="H9" s="130">
+      <c r="H9" s="116">
         <v>0</v>
       </c>
-      <c r="I9" s="132">
+      <c r="I9" s="118">
         <v>28886</v>
       </c>
-      <c r="J9" s="132">
+      <c r="J9" s="118">
         <v>45777</v>
       </c>
-      <c r="K9" s="144">
+      <c r="K9" s="130">
         <f>Assumptions!D9</f>
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="L9" s="138">
+      <c r="L9" s="124">
         <f t="shared" si="0"/>
         <v>4.4567317353041203E-2</v>
       </c>
-      <c r="M9" s="139">
+      <c r="M9" s="125">
         <f t="shared" si="1"/>
         <v>-9.4326826469587968E-3</v>
       </c>
@@ -10933,86 +10934,86 @@
       <c r="A10" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="112">
+      <c r="B10" s="99">
         <v>3.7739774522967298E-2</v>
       </c>
-      <c r="C10" s="112">
+      <c r="C10" s="99">
         <v>6.09896272276437E-2</v>
       </c>
-      <c r="D10" s="112">
+      <c r="D10" s="99">
         <v>8.4239479932320005E-2</v>
       </c>
-      <c r="E10" s="112">
+      <c r="E10" s="99">
         <v>0.145399158457341</v>
       </c>
-      <c r="F10" s="114">
+      <c r="F10" s="100">
         <v>0.41946341281980098</v>
       </c>
-      <c r="G10" s="112">
+      <c r="G10" s="99">
         <v>8.5989627227643695E-2</v>
       </c>
-      <c r="H10" s="112">
+      <c r="H10" s="99">
         <v>0</v>
       </c>
-      <c r="I10" s="120">
+      <c r="I10" s="106">
         <v>28886</v>
       </c>
-      <c r="J10" s="120">
+      <c r="J10" s="106">
         <v>45777</v>
       </c>
-      <c r="K10" s="143">
+      <c r="K10" s="129">
         <f>Assumptions!D10</f>
         <v>0.06</v>
       </c>
-      <c r="L10" s="136">
+      <c r="L10" s="122">
         <f t="shared" si="0"/>
         <v>6.09896272276437E-2</v>
       </c>
-      <c r="M10" s="137">
+      <c r="M10" s="123">
         <f t="shared" si="1"/>
         <v>9.8962722764370237E-4</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="129" t="s">
+      <c r="A11" s="115" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="130">
+      <c r="B11" s="116">
         <v>3.9116118459153602E-2</v>
       </c>
-      <c r="C11" s="130">
+      <c r="C11" s="116">
         <v>6.9881103642633002E-2</v>
       </c>
-      <c r="D11" s="130">
+      <c r="D11" s="116">
         <v>0.10064608882611201</v>
       </c>
-      <c r="E11" s="130">
+      <c r="E11" s="116">
         <v>0.19239704493830101</v>
       </c>
-      <c r="F11" s="131">
+      <c r="F11" s="117">
         <v>0.36321297795942198</v>
       </c>
-      <c r="G11" s="130">
+      <c r="G11" s="116">
         <v>9.4881103642632997E-2</v>
       </c>
-      <c r="H11" s="130">
+      <c r="H11" s="116">
         <v>0</v>
       </c>
-      <c r="I11" s="132">
+      <c r="I11" s="118">
         <v>28886</v>
       </c>
-      <c r="J11" s="132">
+      <c r="J11" s="118">
         <v>45777</v>
       </c>
-      <c r="K11" s="144">
+      <c r="K11" s="130">
         <f>Assumptions!D11</f>
         <v>6.3E-2</v>
       </c>
-      <c r="L11" s="138">
+      <c r="L11" s="124">
         <f t="shared" si="0"/>
         <v>6.9881103642633002E-2</v>
       </c>
-      <c r="M11" s="139">
+      <c r="M11" s="125">
         <f t="shared" si="1"/>
         <v>6.8811036426330019E-3</v>
       </c>
@@ -11021,42 +11022,42 @@
       <c r="A12" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="112">
+      <c r="B12" s="99">
         <v>2.0982633206710101E-2</v>
       </c>
-      <c r="C12" s="112">
+      <c r="C12" s="99">
         <v>4.7043208728656999E-2</v>
       </c>
-      <c r="D12" s="112">
+      <c r="D12" s="99">
         <v>7.3103784250604098E-2</v>
       </c>
-      <c r="E12" s="112">
+      <c r="E12" s="99">
         <v>0.16297676367829</v>
       </c>
-      <c r="F12" s="114">
+      <c r="F12" s="100">
         <v>0.288649790724268</v>
       </c>
-      <c r="G12" s="112">
+      <c r="G12" s="99">
         <v>7.2043208728657104E-2</v>
       </c>
-      <c r="H12" s="112">
+      <c r="H12" s="99">
         <v>0.7</v>
       </c>
-      <c r="I12" s="120">
+      <c r="I12" s="106">
         <v>25626</v>
       </c>
-      <c r="J12" s="120">
+      <c r="J12" s="106">
         <v>45777</v>
       </c>
-      <c r="K12" s="143">
+      <c r="K12" s="129">
         <f>Assumptions!D12</f>
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="L12" s="136">
+      <c r="L12" s="122">
         <f t="shared" si="0"/>
         <v>4.7043208728656999E-2</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="123">
         <f t="shared" si="1"/>
         <v>-9.5679127134300213E-4</v>
       </c>
@@ -11065,42 +11066,42 @@
       <c r="A13" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="112">
+      <c r="B13" s="99">
         <v>2.5237430201924101E-2</v>
       </c>
-      <c r="C13" s="112">
+      <c r="C13" s="99">
         <v>4.8975926757622301E-2</v>
       </c>
-      <c r="D13" s="112">
+      <c r="D13" s="99">
         <v>7.2714423313320495E-2</v>
       </c>
-      <c r="E13" s="112">
+      <c r="E13" s="99">
         <v>0.14845502318157899</v>
       </c>
-      <c r="F13" s="114">
+      <c r="F13" s="100">
         <v>0.32990414004192098</v>
       </c>
-      <c r="G13" s="112">
+      <c r="G13" s="99">
         <v>7.3975926757622296E-2</v>
       </c>
-      <c r="H13" s="112">
+      <c r="H13" s="99">
         <v>0.7</v>
       </c>
-      <c r="I13" s="120">
+      <c r="I13" s="106">
         <v>25598</v>
       </c>
-      <c r="J13" s="120">
+      <c r="J13" s="106">
         <v>45777</v>
       </c>
-      <c r="K13" s="143">
+      <c r="K13" s="129">
         <f>Assumptions!D13</f>
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="L13" s="136">
+      <c r="L13" s="122">
         <f t="shared" si="0"/>
         <v>4.8975926757622301E-2</v>
       </c>
-      <c r="M13" s="137">
+      <c r="M13" s="123">
         <f t="shared" si="1"/>
         <v>-2.0240732423776955E-3</v>
       </c>
@@ -11109,130 +11110,130 @@
       <c r="A14" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="112">
+      <c r="B14" s="99">
         <v>-1.15459534877681E-3</v>
       </c>
-      <c r="C14" s="112">
+      <c r="C14" s="99">
         <v>2.82523559089745E-2</v>
       </c>
-      <c r="D14" s="112">
+      <c r="D14" s="99">
         <v>5.76593071667258E-2</v>
       </c>
-      <c r="E14" s="112">
+      <c r="E14" s="99">
         <v>0.18390421737222901</v>
       </c>
-      <c r="F14" s="114">
+      <c r="F14" s="100">
         <v>0.15362538343419599</v>
       </c>
-      <c r="G14" s="112">
+      <c r="G14" s="99">
         <v>5.3252355908974501E-2</v>
       </c>
-      <c r="H14" s="112">
+      <c r="H14" s="99">
         <v>0.7</v>
       </c>
-      <c r="I14" s="120">
+      <c r="I14" s="106">
         <v>25598</v>
       </c>
-      <c r="J14" s="120">
+      <c r="J14" s="106">
         <v>45777</v>
       </c>
-      <c r="K14" s="143">
+      <c r="K14" s="129">
         <f>Assumptions!D14</f>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="L14" s="136">
+      <c r="L14" s="122">
         <f t="shared" si="0"/>
         <v>2.82523559089745E-2</v>
       </c>
-      <c r="M14" s="137">
+      <c r="M14" s="123">
         <f t="shared" si="1"/>
         <v>2.2523559089745009E-3</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="129" t="s">
+      <c r="A15" s="115" t="s">
         <v>146</v>
       </c>
-      <c r="B15" s="130">
+      <c r="B15" s="116">
         <v>2.74370548378081E-2</v>
       </c>
-      <c r="C15" s="130">
+      <c r="C15" s="116">
         <v>5.6359980577740498E-2</v>
       </c>
-      <c r="D15" s="130">
+      <c r="D15" s="116">
         <v>8.5282906317672894E-2</v>
       </c>
-      <c r="E15" s="130">
+      <c r="E15" s="116">
         <v>0.17096972354367099</v>
       </c>
-      <c r="F15" s="131">
+      <c r="F15" s="117">
         <v>0.32964889577857998</v>
       </c>
-      <c r="G15" s="130">
+      <c r="G15" s="116">
         <v>8.1359980577740507E-2</v>
       </c>
-      <c r="H15" s="130">
+      <c r="H15" s="116">
         <v>0.7</v>
       </c>
-      <c r="I15" s="132">
+      <c r="I15" s="118">
         <v>25626</v>
       </c>
-      <c r="J15" s="132">
+      <c r="J15" s="118">
         <v>45777</v>
       </c>
-      <c r="K15" s="144">
+      <c r="K15" s="130">
         <f>Assumptions!D15</f>
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="L15" s="138">
+      <c r="L15" s="124">
         <f t="shared" si="0"/>
         <v>5.6359980577740498E-2</v>
       </c>
-      <c r="M15" s="139">
+      <c r="M15" s="125">
         <f t="shared" si="1"/>
         <v>-1.2640019422259507E-2</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="129" t="s">
+      <c r="A16" s="115" t="s">
         <v>147</v>
       </c>
-      <c r="B16" s="130">
+      <c r="B16" s="116">
         <v>3.5865028766390701E-2</v>
       </c>
-      <c r="C16" s="130">
+      <c r="C16" s="116">
         <v>7.5241692772873098E-2</v>
       </c>
-      <c r="D16" s="130">
+      <c r="D16" s="116">
         <v>0.114618356779355</v>
       </c>
-      <c r="E16" s="130">
+      <c r="E16" s="116">
         <v>0.23276405090531699</v>
       </c>
-      <c r="F16" s="131">
+      <c r="F16" s="117">
         <v>0.32325306455282199</v>
       </c>
-      <c r="G16" s="130">
+      <c r="G16" s="116">
         <v>0.100241692772873</v>
       </c>
-      <c r="H16" s="130">
+      <c r="H16" s="116">
         <v>0</v>
       </c>
-      <c r="I16" s="132">
+      <c r="I16" s="118">
         <v>32171</v>
       </c>
-      <c r="J16" s="132">
+      <c r="J16" s="118">
         <v>45777</v>
       </c>
-      <c r="K16" s="144">
+      <c r="K16" s="130">
         <f>Assumptions!D16</f>
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="L16" s="138">
+      <c r="L16" s="124">
         <f t="shared" si="0"/>
         <v>7.5241692772873098E-2</v>
       </c>
-      <c r="M16" s="139">
+      <c r="M16" s="125">
         <f t="shared" si="1"/>
         <v>-1.0758307227126895E-2</v>
       </c>
@@ -11241,42 +11242,42 @@
       <c r="A17" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B17" s="112">
+      <c r="B17" s="99">
         <v>3.9211523567242897E-2</v>
       </c>
-      <c r="C17" s="112">
+      <c r="C17" s="99">
         <v>6.4800724140040705E-2</v>
       </c>
-      <c r="D17" s="112">
+      <c r="D17" s="99">
         <v>9.0389924712838396E-2</v>
       </c>
-      <c r="E17" s="112">
+      <c r="E17" s="99">
         <v>0.14797197236920701</v>
       </c>
-      <c r="F17" s="114">
+      <c r="F17" s="100">
         <v>0.43792566323543602</v>
       </c>
-      <c r="G17" s="112">
+      <c r="G17" s="99">
         <v>8.98007241400407E-2</v>
       </c>
-      <c r="H17" s="112">
+      <c r="H17" s="99">
         <v>0.7</v>
       </c>
-      <c r="I17" s="120">
+      <c r="I17" s="106">
         <v>32720</v>
       </c>
-      <c r="J17" s="120">
+      <c r="J17" s="106">
         <v>45777</v>
       </c>
-      <c r="K17" s="143">
+      <c r="K17" s="129">
         <f>Assumptions!D17</f>
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="L17" s="136">
+      <c r="L17" s="122">
         <f t="shared" si="0"/>
         <v>6.4800724140040705E-2</v>
       </c>
-      <c r="M17" s="137">
+      <c r="M17" s="123">
         <f t="shared" si="1"/>
         <v>3.8007241400407066E-3</v>
       </c>
@@ -11285,42 +11286,42 @@
       <c r="A18" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="112">
+      <c r="B18" s="99">
         <v>1.6403181443203799E-2</v>
       </c>
-      <c r="C18" s="112">
+      <c r="C18" s="99">
         <v>4.4976836696510598E-2</v>
       </c>
-      <c r="D18" s="112">
+      <c r="D18" s="99">
         <v>7.3550491949817401E-2</v>
       </c>
-      <c r="E18" s="112">
+      <c r="E18" s="99">
         <v>0.139789727557039</v>
       </c>
-      <c r="F18" s="114">
+      <c r="F18" s="100">
         <v>0.32174636493341902</v>
       </c>
-      <c r="G18" s="112">
+      <c r="G18" s="99">
         <v>6.99768366965106E-2</v>
       </c>
-      <c r="H18" s="112">
+      <c r="H18" s="99">
         <v>0.7</v>
       </c>
-      <c r="I18" s="120">
+      <c r="I18" s="106">
         <v>36189</v>
       </c>
-      <c r="J18" s="120">
+      <c r="J18" s="106">
         <v>45777</v>
       </c>
-      <c r="K18" s="143">
+      <c r="K18" s="129">
         <f>Assumptions!D18</f>
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="L18" s="136">
+      <c r="L18" s="122">
         <f t="shared" si="0"/>
         <v>4.4976836696510598E-2</v>
       </c>
-      <c r="M18" s="137">
+      <c r="M18" s="123">
         <f t="shared" si="1"/>
         <v>-3.0231633034894026E-3</v>
       </c>
@@ -11329,147 +11330,147 @@
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="112"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="112"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="114"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="143"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="137"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="129"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="123"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B20" s="112">
+      <c r="B20" s="99">
         <v>7.6750631221554899E-3</v>
       </c>
-      <c r="C20" s="112">
+      <c r="C20" s="99">
         <v>1.9169505465816701E-2</v>
       </c>
-      <c r="D20" s="112">
+      <c r="D20" s="99">
         <v>3.0663947809477999E-2</v>
       </c>
-      <c r="E20" s="112">
+      <c r="E20" s="99">
         <v>6.1826317761391997E-2</v>
       </c>
-      <c r="F20" s="114">
+      <c r="F20" s="100">
         <v>0.31005413487178901</v>
       </c>
-      <c r="G20" s="112">
+      <c r="G20" s="99">
         <v>4.41695054658168E-2</v>
       </c>
-      <c r="H20" s="112">
+      <c r="H20" s="99">
         <v>1</v>
       </c>
-      <c r="I20" s="120">
+      <c r="I20" s="106">
         <v>34365</v>
       </c>
-      <c r="J20" s="120">
+      <c r="J20" s="106">
         <v>45777</v>
       </c>
-      <c r="K20" s="143">
+      <c r="K20" s="129">
         <f>Assumptions!D20</f>
         <v>1.9E-2</v>
       </c>
-      <c r="L20" s="136">
+      <c r="L20" s="122">
         <f t="shared" si="0"/>
         <v>1.9169505465816701E-2</v>
       </c>
-      <c r="M20" s="137">
+      <c r="M20" s="123">
         <f t="shared" si="1"/>
         <v>1.6950546581670153E-4</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="129" t="s">
+      <c r="A21" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="B21" s="130">
+      <c r="B21" s="116">
         <v>4.3657888915111303E-3</v>
       </c>
-      <c r="C21" s="130">
+      <c r="C21" s="116">
         <v>2.0771382280796301E-2</v>
       </c>
-      <c r="D21" s="130">
+      <c r="D21" s="116">
         <v>3.7176975670081602E-2</v>
       </c>
-      <c r="E21" s="130">
+      <c r="E21" s="116">
         <v>8.8242421826534606E-2</v>
       </c>
-      <c r="F21" s="131">
+      <c r="F21" s="117">
         <v>0.23538998421449001</v>
       </c>
-      <c r="G21" s="130">
+      <c r="G21" s="116">
         <v>4.5771382280796302E-2</v>
       </c>
-      <c r="H21" s="130">
+      <c r="H21" s="116">
         <v>1</v>
       </c>
-      <c r="I21" s="132">
+      <c r="I21" s="118">
         <v>34365</v>
       </c>
-      <c r="J21" s="132">
+      <c r="J21" s="118">
         <v>45777</v>
       </c>
-      <c r="K21" s="144">
+      <c r="K21" s="130">
         <f>Assumptions!D21</f>
         <v>2.7E-2</v>
       </c>
-      <c r="L21" s="138">
+      <c r="L21" s="124">
         <f t="shared" si="0"/>
         <v>2.0771382280796301E-2</v>
       </c>
-      <c r="M21" s="139">
+      <c r="M21" s="125">
         <f t="shared" si="1"/>
         <v>-6.2286177192036989E-3</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="129" t="s">
+      <c r="A22" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="B22" s="130">
+      <c r="B22" s="116">
         <v>3.4812134452342201E-3</v>
       </c>
-      <c r="C22" s="130">
+      <c r="C22" s="116">
         <v>1.8658048030354601E-2</v>
       </c>
-      <c r="D22" s="130">
+      <c r="D22" s="116">
         <v>3.3834882615475001E-2</v>
       </c>
-      <c r="E22" s="130">
+      <c r="E22" s="116">
         <v>8.1633172764504602E-2</v>
       </c>
-      <c r="F22" s="131">
+      <c r="F22" s="117">
         <v>0.228559633277753</v>
       </c>
-      <c r="G22" s="130">
+      <c r="G22" s="116">
         <v>4.3658048030354599E-2</v>
       </c>
-      <c r="H22" s="130">
+      <c r="H22" s="116">
         <v>1</v>
       </c>
-      <c r="I22" s="132">
+      <c r="I22" s="118">
         <v>34365</v>
       </c>
-      <c r="J22" s="132">
+      <c r="J22" s="118">
         <v>45777</v>
       </c>
-      <c r="K22" s="144">
+      <c r="K22" s="130">
         <f>Assumptions!D22</f>
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="L22" s="138">
+      <c r="L22" s="124">
         <f t="shared" si="0"/>
         <v>1.8658048030354601E-2</v>
       </c>
-      <c r="M22" s="139">
+      <c r="M22" s="125">
         <f t="shared" si="1"/>
         <v>-1.0341951969645401E-2</v>
       </c>
@@ -11478,59 +11479,59 @@
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="112"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="114"/>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="143"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="137"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="99"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="123"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="112">
+      <c r="B24" s="99">
         <v>2.6608812004023499E-2</v>
       </c>
-      <c r="C24" s="112">
+      <c r="C24" s="99">
         <v>5.0216749358222103E-2</v>
       </c>
-      <c r="D24" s="112">
+      <c r="D24" s="99">
         <v>7.3824686712420803E-2</v>
       </c>
-      <c r="E24" s="112">
+      <c r="E24" s="99">
         <v>0.14763853637333799</v>
       </c>
-      <c r="F24" s="114">
+      <c r="F24" s="100">
         <v>0.340133074952987</v>
       </c>
-      <c r="G24" s="112">
+      <c r="G24" s="99">
         <v>7.5216749358222104E-2</v>
       </c>
-      <c r="H24" s="112">
+      <c r="H24" s="99">
         <v>0</v>
       </c>
-      <c r="I24" s="120">
+      <c r="I24" s="106">
         <v>25598</v>
       </c>
-      <c r="J24" s="120">
+      <c r="J24" s="106">
         <v>45777</v>
       </c>
-      <c r="K24" s="143">
+      <c r="K24" s="129">
         <f>Assumptions!D24</f>
         <v>0.08</v>
       </c>
-      <c r="L24" s="136">
+      <c r="L24" s="122">
         <f t="shared" si="0"/>
         <v>5.0216749358222103E-2</v>
       </c>
-      <c r="M24" s="137">
+      <c r="M24" s="123">
         <f t="shared" si="1"/>
         <v>-2.9783250641777899E-2</v>
       </c>
@@ -11539,42 +11540,42 @@
       <c r="A25" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="112">
+      <c r="B25" s="99">
         <v>1.78707608365977E-2</v>
       </c>
-      <c r="C25" s="112">
+      <c r="C25" s="99">
         <v>3.5944264317563202E-2</v>
       </c>
-      <c r="D25" s="112">
+      <c r="D25" s="99">
         <v>5.40177677985288E-2</v>
       </c>
-      <c r="E25" s="112">
+      <c r="E25" s="99">
         <v>9.7213778264937697E-2</v>
       </c>
-      <c r="F25" s="114">
+      <c r="F25" s="100">
         <v>0.369744546082799</v>
       </c>
-      <c r="G25" s="112">
+      <c r="G25" s="99">
         <v>6.0944264317563203E-2</v>
       </c>
-      <c r="H25" s="112">
+      <c r="H25" s="99">
         <v>0</v>
       </c>
-      <c r="I25" s="120">
+      <c r="I25" s="106">
         <v>34365</v>
       </c>
-      <c r="J25" s="120">
+      <c r="J25" s="106">
         <v>45777</v>
       </c>
-      <c r="K25" s="143">
+      <c r="K25" s="129">
         <f>Assumptions!D25</f>
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="L25" s="136">
+      <c r="L25" s="122">
         <f t="shared" si="0"/>
         <v>3.5944264317563202E-2</v>
       </c>
-      <c r="M25" s="137">
+      <c r="M25" s="123">
         <f t="shared" si="1"/>
         <v>-4.6055735682436802E-2</v>
       </c>
@@ -11583,42 +11584,42 @@
       <c r="A26" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="112">
+      <c r="B26" s="99">
         <v>1.3852677823030299E-2</v>
       </c>
-      <c r="C26" s="112">
+      <c r="C26" s="99">
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="D26" s="112">
+      <c r="D26" s="99">
         <v>8.1345289061248299E-2</v>
       </c>
-      <c r="E26" s="112">
+      <c r="E26" s="99">
         <v>0.21081962919687999</v>
       </c>
-      <c r="F26" s="114">
+      <c r="F26" s="100">
         <v>0.225780605076804</v>
       </c>
-      <c r="G26" s="112">
+      <c r="G26" s="99">
         <v>7.2598983442139303E-2</v>
       </c>
-      <c r="H26" s="112">
+      <c r="H26" s="99">
         <v>0</v>
       </c>
-      <c r="I26" s="120">
+      <c r="I26" s="106">
         <v>30680</v>
       </c>
-      <c r="J26" s="120">
+      <c r="J26" s="106">
         <v>44925</v>
       </c>
-      <c r="K26" s="143">
+      <c r="K26" s="129">
         <f>Assumptions!D26</f>
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="L26" s="136">
+      <c r="L26" s="122">
         <f t="shared" si="0"/>
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="M26" s="137">
+      <c r="M26" s="123">
         <f t="shared" si="1"/>
         <v>-2.5401016557860694E-2</v>
       </c>
@@ -11627,147 +11628,147 @@
       <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="112"/>
-      <c r="C27" s="112"/>
-      <c r="D27" s="112"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="120"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="143"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="137"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="99"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="123"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B28" s="112">
+      <c r="B28" s="99">
         <v>2.64039774019777E-2</v>
       </c>
-      <c r="C28" s="112">
+      <c r="C28" s="99">
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="D28" s="112">
+      <c r="D28" s="99">
         <v>6.0324053411324102E-2</v>
       </c>
-      <c r="E28" s="112">
+      <c r="E28" s="99">
         <v>0.106064123700363</v>
       </c>
-      <c r="F28" s="114">
+      <c r="F28" s="100">
         <v>0.40884715673658401</v>
       </c>
-      <c r="G28" s="112">
+      <c r="G28" s="99">
         <v>6.8364015406650894E-2</v>
       </c>
-      <c r="H28" s="112">
+      <c r="H28" s="99">
         <v>0</v>
       </c>
-      <c r="I28" s="120">
+      <c r="I28" s="106">
         <v>30589</v>
       </c>
-      <c r="J28" s="120">
+      <c r="J28" s="106">
         <v>45777</v>
       </c>
-      <c r="K28" s="143">
+      <c r="K28" s="129">
         <f>Assumptions!D28</f>
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="L28" s="136">
+      <c r="L28" s="122">
         <f t="shared" si="0"/>
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="M28" s="137">
+      <c r="M28" s="123">
         <f t="shared" si="1"/>
         <v>-6.3598459334909818E-4</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="121" t="s">
+      <c r="A29" s="107" t="s">
         <v>156</v>
       </c>
-      <c r="B29" s="122">
+      <c r="B29" s="108">
         <v>3.9132178171297799E-2</v>
       </c>
-      <c r="C29" s="122">
+      <c r="C29" s="108">
         <v>6.2011235623535797E-2</v>
       </c>
-      <c r="D29" s="122">
+      <c r="D29" s="108">
         <v>8.4890293075773796E-2</v>
       </c>
-      <c r="E29" s="122">
+      <c r="E29" s="108">
         <v>0.143080291393996</v>
       </c>
-      <c r="F29" s="123">
+      <c r="F29" s="109">
         <v>0.43340165874262299</v>
       </c>
-      <c r="G29" s="122">
+      <c r="G29" s="108">
         <v>8.7011235623535799E-2</v>
       </c>
-      <c r="H29" s="122">
+      <c r="H29" s="108">
         <v>0</v>
       </c>
-      <c r="I29" s="124">
+      <c r="I29" s="110">
         <v>30650</v>
       </c>
-      <c r="J29" s="124">
+      <c r="J29" s="110">
         <v>44925</v>
       </c>
-      <c r="K29" s="143">
+      <c r="K29" s="129">
         <f>Assumptions!D29</f>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="L29" s="136">
+      <c r="L29" s="122">
         <f t="shared" si="0"/>
         <v>6.2011235623535797E-2</v>
       </c>
-      <c r="M29" s="137">
+      <c r="M29" s="123">
         <f t="shared" si="1"/>
         <v>2.4011235623535798E-2</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="115" t="s">
+      <c r="A30" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="B30" s="125">
+      <c r="B30" s="111">
         <v>1.3852677823030299E-2</v>
       </c>
-      <c r="C30" s="125">
+      <c r="C30" s="111">
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="D30" s="125">
+      <c r="D30" s="111">
         <v>8.1345289061248299E-2</v>
       </c>
-      <c r="E30" s="125">
+      <c r="E30" s="111">
         <v>0.21081962919687999</v>
       </c>
-      <c r="F30" s="126">
+      <c r="F30" s="112">
         <v>0.225780605076804</v>
       </c>
-      <c r="G30" s="125">
+      <c r="G30" s="111">
         <v>7.2598983442139303E-2</v>
       </c>
-      <c r="H30" s="125">
+      <c r="H30" s="111">
         <v>0</v>
       </c>
-      <c r="I30" s="127">
+      <c r="I30" s="113">
         <v>30680</v>
       </c>
-      <c r="J30" s="127">
+      <c r="J30" s="113">
         <v>44925</v>
       </c>
-      <c r="K30" s="145">
+      <c r="K30" s="131">
         <f>Assumptions!D30</f>
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="L30" s="128">
+      <c r="L30" s="114">
         <f t="shared" si="0"/>
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="M30" s="140">
+      <c r="M30" s="126">
         <f t="shared" si="1"/>
         <v>4.5989834421393053E-3</v>
       </c>

--- a/epsilon-phi-core/src/python/epsilonPhi/core/reporting/formatted_excel.xlsx
+++ b/epsilon-phi-core/src/python/epsilonPhi/core/reporting/formatted_excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/python/epsilonPhi/core/reporting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/python/epsilonPhi/core/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C773E2-BA42-D345-A983-3571AF531347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1D610B-1983-D244-AD5C-3DF7C844BB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="7120" windowWidth="33600" windowHeight="19040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="26440" windowHeight="19040" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolios" sheetId="2" r:id="rId1"/>
@@ -908,7 +908,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1081,6 +1081,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="FF737373"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1089,7 +1098,7 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1499,56 +1508,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1560,9 +1524,6 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1645,6 +1606,82 @@
     </xf>
     <xf numFmtId="17" fontId="23" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="24" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="24" fillId="16" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="24" fillId="16" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1667,6 +1704,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF737373"/>
       <color rgb="FF807C80"/>
       <color rgb="FF000004"/>
       <color rgb="FF039644"/>
@@ -1676,7 +1714,6 @@
       <color rgb="FF567707"/>
       <color rgb="FF0F2442"/>
       <color rgb="FFFFFFFF"/>
-      <color rgb="FFFAFFFF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3623,107 +3660,107 @@
     <col min="9" max="10" width="11.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="169"/>
-      <c r="B1" s="170" t="s">
+    <row r="1" spans="1:10" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="213"/>
+      <c r="B1" s="214" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="170" t="s">
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="214" t="s">
         <v>155</v>
       </c>
-      <c r="J1" s="170"/>
-    </row>
-    <row r="2" spans="1:10" s="8" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="172"/>
-      <c r="B2" s="173" t="s">
+      <c r="J1" s="214"/>
+    </row>
+    <row r="2" spans="1:10" s="8" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="157"/>
+      <c r="B2" s="204" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="159" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="174" t="s">
+      <c r="F2" s="159" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="175" t="s">
+      <c r="G2" s="158" t="s">
         <v>152</v>
       </c>
-      <c r="H2" s="174" t="s">
+      <c r="H2" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="174" t="s">
+      <c r="I2" s="159" t="s">
         <v>153</v>
       </c>
-      <c r="J2" s="174" t="s">
+      <c r="J2" s="159" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="168" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+    <row r="3" spans="1:10" s="154" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="177"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="177"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="169" t="s">
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="161"/>
+    </row>
+    <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="155" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="178">
+      <c r="B4" s="162">
         <v>5.7241236937856403E-3</v>
       </c>
-      <c r="C4" s="179">
+      <c r="C4" s="163">
         <v>1.08524678406041E-2</v>
       </c>
-      <c r="D4" s="180">
+      <c r="D4" s="164">
         <v>1.59808119874227E-2</v>
       </c>
-      <c r="E4" s="179">
+      <c r="E4" s="163">
         <v>3.2071468696963902E-2</v>
       </c>
-      <c r="F4" s="181">
+      <c r="F4" s="165">
         <v>0.33838387456298602</v>
       </c>
-      <c r="G4" s="179">
+      <c r="G4" s="163">
         <v>3.5852467840604099E-2</v>
       </c>
-      <c r="H4" s="182">
+      <c r="H4" s="166">
         <v>0</v>
       </c>
-      <c r="I4" s="183">
+      <c r="I4" s="167">
         <v>26723</v>
       </c>
-      <c r="J4" s="183">
+      <c r="J4" s="167">
         <v>45777</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="168" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="192" t="s">
+    <row r="5" spans="1:10" s="154" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="193"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="197"/>
-      <c r="I5" s="198"/>
-      <c r="J5" s="198"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="210"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3835,232 +3872,232 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="53"/>
-      <c r="B1" s="160" t="s">
+      <c r="B1" s="197" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160" t="s">
+      <c r="C1" s="197"/>
+      <c r="D1" s="197" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160" t="s">
+      <c r="E1" s="197"/>
+      <c r="F1" s="197" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160" t="s">
+      <c r="G1" s="197"/>
+      <c r="H1" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="161"/>
+      <c r="I1" s="198"/>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="162">
+      <c r="B2" s="199">
         <v>0.745</v>
       </c>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162" t="s">
+      <c r="C2" s="199"/>
+      <c r="D2" s="199" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162">
+      <c r="E2" s="199"/>
+      <c r="F2" s="199">
         <v>0.36</v>
       </c>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162">
+      <c r="G2" s="199"/>
+      <c r="H2" s="199">
         <v>0.15</v>
       </c>
-      <c r="I2" s="162"/>
+      <c r="I2" s="199"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="155">
+      <c r="B3" s="192">
         <v>0.02</v>
       </c>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155">
+      <c r="C3" s="192"/>
+      <c r="D3" s="192">
         <v>0.03</v>
       </c>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155">
+      <c r="E3" s="192"/>
+      <c r="F3" s="192">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155">
+      <c r="G3" s="192"/>
+      <c r="H3" s="192">
         <v>5.5E-2</v>
       </c>
-      <c r="I3" s="155"/>
+      <c r="I3" s="192"/>
     </row>
     <row r="4" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="155">
+      <c r="B4" s="192">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155">
+      <c r="C4" s="192"/>
+      <c r="D4" s="192">
         <v>0.22500000000000001</v>
       </c>
-      <c r="E4" s="155"/>
-      <c r="F4" s="155">
+      <c r="E4" s="192"/>
+      <c r="F4" s="192">
         <v>0.35499999999999998</v>
       </c>
-      <c r="G4" s="155"/>
-      <c r="H4" s="155">
+      <c r="G4" s="192"/>
+      <c r="H4" s="192">
         <v>0.505</v>
       </c>
-      <c r="I4" s="155"/>
+      <c r="I4" s="192"/>
     </row>
     <row r="5" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="155">
+      <c r="B5" s="192">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155">
+      <c r="C5" s="192"/>
+      <c r="D5" s="192">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155">
+      <c r="E5" s="192"/>
+      <c r="F5" s="192">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155">
+      <c r="G5" s="192"/>
+      <c r="H5" s="192">
         <v>0.03</v>
       </c>
-      <c r="I5" s="155"/>
+      <c r="I5" s="192"/>
     </row>
     <row r="6" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="155">
+      <c r="B6" s="192">
         <v>0.04</v>
       </c>
-      <c r="C6" s="155"/>
-      <c r="D6" s="155">
+      <c r="C6" s="192"/>
+      <c r="D6" s="192">
         <v>5.5E-2</v>
       </c>
-      <c r="E6" s="155"/>
-      <c r="F6" s="155">
+      <c r="E6" s="192"/>
+      <c r="F6" s="192">
         <v>0.12</v>
       </c>
-      <c r="G6" s="155"/>
-      <c r="H6" s="155">
+      <c r="G6" s="192"/>
+      <c r="H6" s="192">
         <v>0.185</v>
       </c>
-      <c r="I6" s="155"/>
+      <c r="I6" s="192"/>
     </row>
     <row r="7" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="156">
+      <c r="B7" s="193">
         <v>0.04</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156">
+      <c r="C7" s="193"/>
+      <c r="D7" s="193">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156">
+      <c r="E7" s="193"/>
+      <c r="F7" s="193">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156">
+      <c r="G7" s="193"/>
+      <c r="H7" s="193">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I7" s="156"/>
+      <c r="I7" s="193"/>
     </row>
     <row r="8" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="157">
+      <c r="B8" s="194">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="C8" s="157"/>
-      <c r="D8" s="157">
+      <c r="C8" s="194"/>
+      <c r="D8" s="194">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157">
+      <c r="E8" s="194"/>
+      <c r="F8" s="194">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="G8" s="157"/>
-      <c r="H8" s="157">
+      <c r="G8" s="194"/>
+      <c r="H8" s="194">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="I8" s="157"/>
+      <c r="I8" s="194"/>
     </row>
     <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="158">
+      <c r="B9" s="195">
         <v>0.6</v>
       </c>
-      <c r="C9" s="158"/>
-      <c r="D9" s="158">
+      <c r="C9" s="195"/>
+      <c r="D9" s="195">
         <v>0.59</v>
       </c>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158">
+      <c r="E9" s="195"/>
+      <c r="F9" s="195">
         <v>0.53</v>
       </c>
-      <c r="G9" s="158"/>
-      <c r="H9" s="158">
+      <c r="G9" s="195"/>
+      <c r="H9" s="195">
         <v>0.49</v>
       </c>
-      <c r="I9" s="158"/>
+      <c r="I9" s="195"/>
     </row>
     <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="155">
+      <c r="B10" s="192">
         <v>3.1E-2</v>
       </c>
-      <c r="C10" s="155"/>
-      <c r="D10" s="155">
+      <c r="C10" s="192"/>
+      <c r="D10" s="192">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="E10" s="155"/>
-      <c r="F10" s="155">
+      <c r="E10" s="192"/>
+      <c r="F10" s="192">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="G10" s="155"/>
-      <c r="H10" s="155">
+      <c r="G10" s="192"/>
+      <c r="H10" s="192">
         <v>0.10299999999999999</v>
       </c>
-      <c r="I10" s="155"/>
+      <c r="I10" s="192"/>
     </row>
     <row r="11" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="159" t="s">
+      <c r="B11" s="196" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="159"/>
-      <c r="D11" s="159" t="s">
+      <c r="C11" s="196"/>
+      <c r="D11" s="196" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="159"/>
-      <c r="F11" s="159" t="s">
+      <c r="E11" s="196"/>
+      <c r="F11" s="196" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="159"/>
-      <c r="H11" s="159" t="s">
+      <c r="G11" s="196"/>
+      <c r="H11" s="196" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="159"/>
+      <c r="I11" s="196"/>
     </row>
     <row r="12" spans="1:9" s="8" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="59" t="s">
@@ -4353,64 +4390,64 @@
       <c r="A23" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="153">
+      <c r="B23" s="190">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153">
+      <c r="C23" s="190"/>
+      <c r="D23" s="190">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E23" s="153"/>
-      <c r="F23" s="153">
+      <c r="E23" s="190"/>
+      <c r="F23" s="190">
         <v>6.3E-2</v>
       </c>
-      <c r="G23" s="153"/>
-      <c r="H23" s="153">
+      <c r="G23" s="190"/>
+      <c r="H23" s="190">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="I23" s="153"/>
+      <c r="I23" s="190"/>
     </row>
     <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="153">
+      <c r="B24" s="190">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153">
+      <c r="C24" s="190"/>
+      <c r="D24" s="190">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="E24" s="153"/>
-      <c r="F24" s="153">
+      <c r="E24" s="190"/>
+      <c r="F24" s="190">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G24" s="153"/>
-      <c r="H24" s="153">
+      <c r="G24" s="190"/>
+      <c r="H24" s="190">
         <v>0.24299999999999999</v>
       </c>
-      <c r="I24" s="153"/>
+      <c r="I24" s="190"/>
     </row>
     <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="154">
+      <c r="B25" s="191">
         <v>0</v>
       </c>
-      <c r="C25" s="154"/>
-      <c r="D25" s="154">
+      <c r="C25" s="191"/>
+      <c r="D25" s="191">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154">
+      <c r="E25" s="191"/>
+      <c r="F25" s="191">
         <v>0.14899999999999999</v>
       </c>
-      <c r="G25" s="154"/>
-      <c r="H25" s="154">
+      <c r="G25" s="191"/>
+      <c r="H25" s="191">
         <v>0.253</v>
       </c>
-      <c r="I25" s="154"/>
+      <c r="I25" s="191"/>
     </row>
     <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="67" t="s">
@@ -4429,64 +4466,64 @@
       <c r="A27" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="153">
+      <c r="B27" s="190">
         <v>0.23799999999999999</v>
       </c>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153">
+      <c r="C27" s="190"/>
+      <c r="D27" s="190">
         <v>0.27900000000000003</v>
       </c>
-      <c r="E27" s="153"/>
-      <c r="F27" s="153">
+      <c r="E27" s="190"/>
+      <c r="F27" s="190">
         <v>0.314</v>
       </c>
-      <c r="G27" s="153"/>
-      <c r="H27" s="153">
+      <c r="G27" s="190"/>
+      <c r="H27" s="190">
         <v>0.33700000000000002</v>
       </c>
-      <c r="I27" s="153"/>
+      <c r="I27" s="190"/>
     </row>
     <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="153">
+      <c r="B28" s="190">
         <v>0.04</v>
       </c>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153">
+      <c r="C28" s="190"/>
+      <c r="D28" s="190">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153">
+      <c r="E28" s="190"/>
+      <c r="F28" s="190">
         <v>0.14299999999999999</v>
       </c>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153">
+      <c r="G28" s="190"/>
+      <c r="H28" s="190">
         <v>0.187</v>
       </c>
-      <c r="I28" s="153"/>
+      <c r="I28" s="190"/>
     </row>
     <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="153">
+      <c r="B29" s="190">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C29" s="153"/>
-      <c r="D29" s="153">
+      <c r="C29" s="190"/>
+      <c r="D29" s="190">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="E29" s="153"/>
-      <c r="F29" s="153">
+      <c r="E29" s="190"/>
+      <c r="F29" s="190">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G29" s="153"/>
-      <c r="H29" s="153">
+      <c r="G29" s="190"/>
+      <c r="H29" s="190">
         <v>0.108</v>
       </c>
-      <c r="I29" s="153"/>
+      <c r="I29" s="190"/>
     </row>
     <row r="30" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="59" t="s">
@@ -5131,16 +5168,16 @@
   <sheetData>
     <row r="1" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="19"/>
-      <c r="B1" s="165" t="s">
+      <c r="B1" s="202" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="202"/>
+      <c r="I1" s="202"/>
       <c r="J1" s="21"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -5148,13 +5185,13 @@
     </row>
     <row r="2" spans="1:16" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="200" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
+      <c r="C2" s="200"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="201"/>
       <c r="G2" s="24" t="s">
         <v>31</v>
       </c>
@@ -6016,7 +6053,7 @@
       <c r="P26" s="3"/>
     </row>
     <row r="27" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="167" t="s">
+      <c r="A27" s="153" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="30"/>
@@ -6302,832 +6339,832 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="169"/>
-      <c r="B1" s="170" t="s">
+      <c r="A1" s="155"/>
+      <c r="B1" s="203" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="170" t="s">
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="203" t="s">
         <v>155</v>
       </c>
-      <c r="J1" s="170"/>
+      <c r="J1" s="203"/>
     </row>
     <row r="2" spans="1:10" s="8" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="172"/>
-      <c r="B2" s="173" t="s">
+      <c r="A2" s="157"/>
+      <c r="B2" s="204" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="159" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="174" t="s">
+      <c r="F2" s="159" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="175" t="s">
+      <c r="G2" s="158" t="s">
         <v>152</v>
       </c>
-      <c r="H2" s="174" t="s">
+      <c r="H2" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="174" t="s">
+      <c r="I2" s="159" t="s">
         <v>153</v>
       </c>
-      <c r="J2" s="174" t="s">
+      <c r="J2" s="159" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="168" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+    <row r="3" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="177"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="177"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="161"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="169" t="s">
+      <c r="A4" s="155" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="178">
+      <c r="B4" s="162">
         <v>5.7241236937856403E-3</v>
       </c>
-      <c r="C4" s="179">
+      <c r="C4" s="163">
         <v>1.08524678406041E-2</v>
       </c>
-      <c r="D4" s="180">
+      <c r="D4" s="164">
         <v>1.59808119874227E-2</v>
       </c>
-      <c r="E4" s="179">
+      <c r="E4" s="163">
         <v>3.2071468696963902E-2</v>
       </c>
-      <c r="F4" s="181">
+      <c r="F4" s="165">
         <v>0.33838387456298602</v>
       </c>
-      <c r="G4" s="179">
+      <c r="G4" s="163">
         <v>3.5852467840604099E-2</v>
       </c>
-      <c r="H4" s="182">
+      <c r="H4" s="166">
         <v>0</v>
       </c>
-      <c r="I4" s="183">
+      <c r="I4" s="167">
         <v>26723</v>
       </c>
-      <c r="J4" s="183">
+      <c r="J4" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="199" t="s">
+      <c r="A5" s="183" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="200">
+      <c r="B5" s="184">
         <v>4.32971260588862E-4</v>
       </c>
-      <c r="C5" s="201">
+      <c r="C5" s="185">
         <v>3.0821903711752401E-3</v>
       </c>
-      <c r="D5" s="202">
+      <c r="D5" s="186">
         <v>5.73140948176162E-3</v>
       </c>
-      <c r="E5" s="201">
+      <c r="E5" s="185">
         <v>1.4716286970652999E-2</v>
       </c>
-      <c r="F5" s="203">
+      <c r="F5" s="187">
         <v>0.20944076296702299</v>
       </c>
-      <c r="G5" s="201">
+      <c r="G5" s="185">
         <v>2.8082190371175202E-2</v>
       </c>
-      <c r="H5" s="204">
+      <c r="H5" s="188">
         <v>0</v>
       </c>
-      <c r="I5" s="205">
+      <c r="I5" s="189">
         <v>33662</v>
       </c>
-      <c r="J5" s="205">
+      <c r="J5" s="189">
         <v>45777</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="168" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="192" t="s">
+    <row r="6" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="176" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="193"/>
-      <c r="C6" s="194"/>
-      <c r="D6" s="195"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="197"/>
-      <c r="I6" s="198"/>
-      <c r="J6" s="198"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="179"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="180"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="181"/>
+      <c r="I6" s="182"/>
+      <c r="J6" s="182"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="199" t="s">
+      <c r="A7" s="183" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="200">
+      <c r="B7" s="184">
         <v>2.64039774019777E-2</v>
       </c>
-      <c r="C7" s="201">
+      <c r="C7" s="185">
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="D7" s="202">
+      <c r="D7" s="186">
         <v>6.0324053411324102E-2</v>
       </c>
-      <c r="E7" s="201">
+      <c r="E7" s="185">
         <v>0.106064123700363</v>
       </c>
-      <c r="F7" s="203">
+      <c r="F7" s="187">
         <v>0.40884715673658401</v>
       </c>
-      <c r="G7" s="201">
+      <c r="G7" s="185">
         <v>6.8364015406650894E-2</v>
       </c>
-      <c r="H7" s="204">
+      <c r="H7" s="188">
         <v>0</v>
       </c>
-      <c r="I7" s="205">
+      <c r="I7" s="189">
         <v>30589</v>
       </c>
-      <c r="J7" s="205">
+      <c r="J7" s="189">
         <v>45777</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="168" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="192" t="s">
+    <row r="8" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="193"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="195"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="194"/>
-      <c r="H8" s="197"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="198"/>
+      <c r="B8" s="177"/>
+      <c r="C8" s="178"/>
+      <c r="D8" s="179"/>
+      <c r="E8" s="178"/>
+      <c r="F8" s="180"/>
+      <c r="G8" s="178"/>
+      <c r="H8" s="181"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="182"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="169" t="s">
+      <c r="A9" s="155" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="178">
+      <c r="B9" s="162">
         <v>1.7523010713942501E-2</v>
       </c>
-      <c r="C9" s="179">
+      <c r="C9" s="163">
         <v>4.4567317353041203E-2</v>
       </c>
-      <c r="D9" s="180">
+      <c r="D9" s="164">
         <v>7.1611623992139897E-2</v>
       </c>
-      <c r="E9" s="179">
+      <c r="E9" s="163">
         <v>0.16912878874266299</v>
       </c>
-      <c r="F9" s="181">
+      <c r="F9" s="165">
         <v>0.26351112477280397</v>
       </c>
-      <c r="G9" s="179">
+      <c r="G9" s="163">
         <v>6.9567317353041197E-2</v>
       </c>
-      <c r="H9" s="182">
+      <c r="H9" s="166">
         <v>0</v>
       </c>
-      <c r="I9" s="183">
+      <c r="I9" s="167">
         <v>28886</v>
       </c>
-      <c r="J9" s="183">
+      <c r="J9" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="169" t="s">
+      <c r="A10" s="155" t="s">
         <v>176</v>
       </c>
-      <c r="B10" s="178">
+      <c r="B10" s="162">
         <v>3.7739774522967298E-2</v>
       </c>
-      <c r="C10" s="179">
+      <c r="C10" s="163">
         <v>6.09896272276437E-2</v>
       </c>
-      <c r="D10" s="180">
+      <c r="D10" s="164">
         <v>8.4239479932320005E-2</v>
       </c>
-      <c r="E10" s="179">
+      <c r="E10" s="163">
         <v>0.145399158457341</v>
       </c>
-      <c r="F10" s="181">
+      <c r="F10" s="165">
         <v>0.41946341281980098</v>
       </c>
-      <c r="G10" s="179">
+      <c r="G10" s="163">
         <v>8.5989627227643695E-2</v>
       </c>
-      <c r="H10" s="182">
+      <c r="H10" s="166">
         <v>0</v>
       </c>
-      <c r="I10" s="183">
+      <c r="I10" s="167">
         <v>28886</v>
       </c>
-      <c r="J10" s="183">
+      <c r="J10" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="169" t="s">
+      <c r="A11" s="155" t="s">
         <v>177</v>
       </c>
-      <c r="B11" s="178">
+      <c r="B11" s="162">
         <v>3.9116118459153602E-2</v>
       </c>
-      <c r="C11" s="179">
+      <c r="C11" s="163">
         <v>6.9881103642633002E-2</v>
       </c>
-      <c r="D11" s="180">
+      <c r="D11" s="164">
         <v>0.10064608882611201</v>
       </c>
-      <c r="E11" s="179">
+      <c r="E11" s="163">
         <v>0.19239704493830101</v>
       </c>
-      <c r="F11" s="181">
+      <c r="F11" s="165">
         <v>0.36321297795942198</v>
       </c>
-      <c r="G11" s="179">
+      <c r="G11" s="163">
         <v>9.4881103642632997E-2</v>
       </c>
-      <c r="H11" s="182">
+      <c r="H11" s="166">
         <v>0</v>
       </c>
-      <c r="I11" s="183">
+      <c r="I11" s="167">
         <v>28886</v>
       </c>
-      <c r="J11" s="183">
+      <c r="J11" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="169" t="s">
+      <c r="A12" s="155" t="s">
         <v>178</v>
       </c>
-      <c r="B12" s="178">
+      <c r="B12" s="162">
         <v>2.0982633206710101E-2</v>
       </c>
-      <c r="C12" s="179">
+      <c r="C12" s="163">
         <v>4.7043208728656999E-2</v>
       </c>
-      <c r="D12" s="180">
+      <c r="D12" s="164">
         <v>7.3103784250604098E-2</v>
       </c>
-      <c r="E12" s="179">
+      <c r="E12" s="163">
         <v>0.16297676367829</v>
       </c>
-      <c r="F12" s="181">
+      <c r="F12" s="165">
         <v>0.288649790724268</v>
       </c>
-      <c r="G12" s="179">
+      <c r="G12" s="163">
         <v>7.2043208728657104E-2</v>
       </c>
-      <c r="H12" s="182">
+      <c r="H12" s="166">
         <v>0.7</v>
       </c>
-      <c r="I12" s="183">
+      <c r="I12" s="167">
         <v>25626</v>
       </c>
-      <c r="J12" s="183">
+      <c r="J12" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="169" t="s">
+      <c r="A13" s="155" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="178">
+      <c r="B13" s="162">
         <v>2.5237430201924101E-2</v>
       </c>
-      <c r="C13" s="179">
+      <c r="C13" s="163">
         <v>4.8975926757622301E-2</v>
       </c>
-      <c r="D13" s="180">
+      <c r="D13" s="164">
         <v>7.2714423313320495E-2</v>
       </c>
-      <c r="E13" s="179">
+      <c r="E13" s="163">
         <v>0.14845502318157899</v>
       </c>
-      <c r="F13" s="181">
+      <c r="F13" s="165">
         <v>0.32990414004192098</v>
       </c>
-      <c r="G13" s="179">
+      <c r="G13" s="163">
         <v>7.3975926757622296E-2</v>
       </c>
-      <c r="H13" s="182">
+      <c r="H13" s="166">
         <v>0.7</v>
       </c>
-      <c r="I13" s="183">
+      <c r="I13" s="167">
         <v>25598</v>
       </c>
-      <c r="J13" s="183">
+      <c r="J13" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="169" t="s">
+      <c r="A14" s="155" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="178">
+      <c r="B14" s="162">
         <v>-1.15459534877681E-3</v>
       </c>
-      <c r="C14" s="179">
+      <c r="C14" s="163">
         <v>2.82523559089745E-2</v>
       </c>
-      <c r="D14" s="180">
+      <c r="D14" s="164">
         <v>5.76593071667258E-2</v>
       </c>
-      <c r="E14" s="179">
+      <c r="E14" s="163">
         <v>0.18390421737222901</v>
       </c>
-      <c r="F14" s="181">
+      <c r="F14" s="165">
         <v>0.15362538343419599</v>
       </c>
-      <c r="G14" s="179">
+      <c r="G14" s="163">
         <v>5.3252355908974501E-2</v>
       </c>
-      <c r="H14" s="182">
+      <c r="H14" s="166">
         <v>0.7</v>
       </c>
-      <c r="I14" s="183">
+      <c r="I14" s="167">
         <v>25598</v>
       </c>
-      <c r="J14" s="183">
+      <c r="J14" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="169" t="s">
+      <c r="A15" s="155" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="178">
+      <c r="B15" s="162">
         <v>2.74370548378081E-2</v>
       </c>
-      <c r="C15" s="179">
+      <c r="C15" s="163">
         <v>5.6359980577740498E-2</v>
       </c>
-      <c r="D15" s="180">
+      <c r="D15" s="164">
         <v>8.5282906317672894E-2</v>
       </c>
-      <c r="E15" s="179">
+      <c r="E15" s="163">
         <v>0.17096972354367099</v>
       </c>
-      <c r="F15" s="181">
+      <c r="F15" s="165">
         <v>0.32964889577857998</v>
       </c>
-      <c r="G15" s="179">
+      <c r="G15" s="163">
         <v>8.1359980577740507E-2</v>
       </c>
-      <c r="H15" s="182">
+      <c r="H15" s="166">
         <v>0.7</v>
       </c>
-      <c r="I15" s="183">
+      <c r="I15" s="167">
         <v>25626</v>
       </c>
-      <c r="J15" s="183">
+      <c r="J15" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="169" t="s">
+      <c r="A16" s="155" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="178">
+      <c r="B16" s="162">
         <v>3.5865028766390701E-2</v>
       </c>
-      <c r="C16" s="179">
+      <c r="C16" s="163">
         <v>7.5241692772873098E-2</v>
       </c>
-      <c r="D16" s="180">
+      <c r="D16" s="164">
         <v>0.114618356779355</v>
       </c>
-      <c r="E16" s="179">
+      <c r="E16" s="163">
         <v>0.23276405090531699</v>
       </c>
-      <c r="F16" s="181">
+      <c r="F16" s="165">
         <v>0.32325306455282199</v>
       </c>
-      <c r="G16" s="179">
+      <c r="G16" s="163">
         <v>0.100241692772873</v>
       </c>
-      <c r="H16" s="182">
+      <c r="H16" s="166">
         <v>0</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="167">
         <v>32171</v>
       </c>
-      <c r="J16" s="183">
+      <c r="J16" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="169" t="s">
+      <c r="A17" s="155" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="178">
+      <c r="B17" s="162">
         <v>3.9211523567242897E-2</v>
       </c>
-      <c r="C17" s="179">
+      <c r="C17" s="163">
         <v>6.4800724140040705E-2</v>
       </c>
-      <c r="D17" s="180">
+      <c r="D17" s="164">
         <v>9.0389924712838396E-2</v>
       </c>
-      <c r="E17" s="179">
+      <c r="E17" s="163">
         <v>0.14797197236920701</v>
       </c>
-      <c r="F17" s="181">
+      <c r="F17" s="165">
         <v>0.43792566323543602</v>
       </c>
-      <c r="G17" s="179">
+      <c r="G17" s="163">
         <v>8.98007241400407E-2</v>
       </c>
-      <c r="H17" s="182">
+      <c r="H17" s="166">
         <v>0.7</v>
       </c>
-      <c r="I17" s="183">
+      <c r="I17" s="167">
         <v>32720</v>
       </c>
-      <c r="J17" s="183">
+      <c r="J17" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="199" t="s">
+      <c r="A18" s="183" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="200">
+      <c r="B18" s="184">
         <v>1.6403181443203799E-2</v>
       </c>
-      <c r="C18" s="201">
+      <c r="C18" s="185">
         <v>4.4976836696510598E-2</v>
       </c>
-      <c r="D18" s="202">
+      <c r="D18" s="186">
         <v>7.3550491949817401E-2</v>
       </c>
-      <c r="E18" s="201">
+      <c r="E18" s="185">
         <v>0.139789727557039</v>
       </c>
-      <c r="F18" s="203">
+      <c r="F18" s="187">
         <v>0.32174636493341902</v>
       </c>
-      <c r="G18" s="201">
+      <c r="G18" s="185">
         <v>6.99768366965106E-2</v>
       </c>
-      <c r="H18" s="204">
+      <c r="H18" s="188">
         <v>0.7</v>
       </c>
-      <c r="I18" s="205">
+      <c r="I18" s="189">
         <v>36189</v>
       </c>
-      <c r="J18" s="205">
+      <c r="J18" s="189">
         <v>45777</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="168" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="192" t="s">
+    <row r="19" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="193"/>
-      <c r="C19" s="194"/>
-      <c r="D19" s="195"/>
-      <c r="E19" s="194"/>
-      <c r="F19" s="196"/>
-      <c r="G19" s="194"/>
-      <c r="H19" s="197"/>
-      <c r="I19" s="198"/>
-      <c r="J19" s="198"/>
+      <c r="B19" s="177"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="179"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="180"/>
+      <c r="G19" s="178"/>
+      <c r="H19" s="181"/>
+      <c r="I19" s="182"/>
+      <c r="J19" s="182"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="169" t="s">
+      <c r="A20" s="155" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="178">
+      <c r="B20" s="162">
         <v>7.6750631221554899E-3</v>
       </c>
-      <c r="C20" s="179">
+      <c r="C20" s="163">
         <v>1.9169505465816701E-2</v>
       </c>
-      <c r="D20" s="180">
+      <c r="D20" s="164">
         <v>3.0663947809477999E-2</v>
       </c>
-      <c r="E20" s="179">
+      <c r="E20" s="163">
         <v>6.1826317761391997E-2</v>
       </c>
-      <c r="F20" s="191">
+      <c r="F20" s="175">
         <v>0.31005413487178901</v>
       </c>
-      <c r="G20" s="179">
+      <c r="G20" s="163">
         <v>4.41695054658168E-2</v>
       </c>
-      <c r="H20" s="182">
+      <c r="H20" s="166">
         <v>1</v>
       </c>
-      <c r="I20" s="183">
+      <c r="I20" s="167">
         <v>34365</v>
       </c>
-      <c r="J20" s="183">
+      <c r="J20" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="169" t="s">
+      <c r="A21" s="155" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="178">
+      <c r="B21" s="162">
         <v>4.3657888915111303E-3</v>
       </c>
-      <c r="C21" s="179">
+      <c r="C21" s="163">
         <v>2.0771382280796301E-2</v>
       </c>
-      <c r="D21" s="180">
+      <c r="D21" s="164">
         <v>3.7176975670081602E-2</v>
       </c>
-      <c r="E21" s="179">
+      <c r="E21" s="163">
         <v>8.8242421826534606E-2</v>
       </c>
-      <c r="F21" s="181">
+      <c r="F21" s="165">
         <v>0.23538998421449001</v>
       </c>
-      <c r="G21" s="179">
+      <c r="G21" s="163">
         <v>4.5771382280796302E-2</v>
       </c>
-      <c r="H21" s="182">
+      <c r="H21" s="166">
         <v>1</v>
       </c>
-      <c r="I21" s="183">
+      <c r="I21" s="167">
         <v>34365</v>
       </c>
-      <c r="J21" s="183">
+      <c r="J21" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="199" t="s">
+      <c r="A22" s="183" t="s">
         <v>140</v>
       </c>
-      <c r="B22" s="200">
+      <c r="B22" s="184">
         <v>3.4812134452342201E-3</v>
       </c>
-      <c r="C22" s="201">
+      <c r="C22" s="185">
         <v>1.8658048030354601E-2</v>
       </c>
-      <c r="D22" s="202">
+      <c r="D22" s="186">
         <v>3.3834882615475001E-2</v>
       </c>
-      <c r="E22" s="201">
+      <c r="E22" s="185">
         <v>8.1633172764504602E-2</v>
       </c>
-      <c r="F22" s="203">
+      <c r="F22" s="187">
         <v>0.228559633277753</v>
       </c>
-      <c r="G22" s="201">
+      <c r="G22" s="185">
         <v>4.3658048030354599E-2</v>
       </c>
-      <c r="H22" s="204">
+      <c r="H22" s="188">
         <v>1</v>
       </c>
-      <c r="I22" s="205">
+      <c r="I22" s="189">
         <v>34365</v>
       </c>
-      <c r="J22" s="205">
+      <c r="J22" s="189">
         <v>45777</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="168" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="192" t="s">
+    <row r="23" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="176" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="193"/>
-      <c r="C23" s="194"/>
-      <c r="D23" s="195"/>
-      <c r="E23" s="194"/>
-      <c r="F23" s="196"/>
-      <c r="G23" s="194"/>
-      <c r="H23" s="197"/>
-      <c r="I23" s="198"/>
-      <c r="J23" s="198"/>
+      <c r="B23" s="177"/>
+      <c r="C23" s="178"/>
+      <c r="D23" s="179"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="180"/>
+      <c r="G23" s="178"/>
+      <c r="H23" s="181"/>
+      <c r="I23" s="182"/>
+      <c r="J23" s="182"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="169" t="s">
+      <c r="A24" s="155" t="s">
         <v>145</v>
       </c>
-      <c r="B24" s="178">
+      <c r="B24" s="162">
         <v>2.6608812004023499E-2</v>
       </c>
-      <c r="C24" s="179">
+      <c r="C24" s="163">
         <v>5.0216749358222103E-2</v>
       </c>
-      <c r="D24" s="180">
+      <c r="D24" s="164">
         <v>7.3824686712420803E-2</v>
       </c>
-      <c r="E24" s="179">
+      <c r="E24" s="163">
         <v>0.14763853637333799</v>
       </c>
-      <c r="F24" s="181">
+      <c r="F24" s="165">
         <v>0.340133074952987</v>
       </c>
-      <c r="G24" s="179">
+      <c r="G24" s="163">
         <v>7.5216749358222104E-2</v>
       </c>
-      <c r="H24" s="182">
+      <c r="H24" s="166">
         <v>0</v>
       </c>
-      <c r="I24" s="183">
+      <c r="I24" s="167">
         <v>25598</v>
       </c>
-      <c r="J24" s="183">
+      <c r="J24" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="169" t="s">
+      <c r="A25" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="178">
+      <c r="B25" s="162">
         <v>1.78707608365977E-2</v>
       </c>
-      <c r="C25" s="179">
+      <c r="C25" s="163">
         <v>3.5944264317563202E-2</v>
       </c>
-      <c r="D25" s="180">
+      <c r="D25" s="164">
         <v>5.40177677985288E-2</v>
       </c>
-      <c r="E25" s="179">
+      <c r="E25" s="163">
         <v>9.7213778264937697E-2</v>
       </c>
-      <c r="F25" s="181">
+      <c r="F25" s="165">
         <v>0.369744546082799</v>
       </c>
-      <c r="G25" s="179">
+      <c r="G25" s="163">
         <v>6.0944264317563203E-2</v>
       </c>
-      <c r="H25" s="182">
+      <c r="H25" s="166">
         <v>0</v>
       </c>
-      <c r="I25" s="183">
+      <c r="I25" s="167">
         <v>34365</v>
       </c>
-      <c r="J25" s="183">
+      <c r="J25" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="199" t="s">
+      <c r="A26" s="183" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="200">
+      <c r="B26" s="184">
         <v>1.3852677823030299E-2</v>
       </c>
-      <c r="C26" s="201">
+      <c r="C26" s="185">
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="D26" s="202">
+      <c r="D26" s="186">
         <v>8.1345289061248299E-2</v>
       </c>
-      <c r="E26" s="201">
+      <c r="E26" s="185">
         <v>0.21081962919687999</v>
       </c>
-      <c r="F26" s="203">
+      <c r="F26" s="187">
         <v>0.225780605076804</v>
       </c>
-      <c r="G26" s="201">
+      <c r="G26" s="185">
         <v>7.2598983442139303E-2</v>
       </c>
-      <c r="H26" s="204">
+      <c r="H26" s="188">
         <v>0</v>
       </c>
-      <c r="I26" s="205">
+      <c r="I26" s="189">
         <v>30680</v>
       </c>
-      <c r="J26" s="205">
+      <c r="J26" s="189">
         <v>44925</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="168" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="192" t="s">
+    <row r="27" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="176" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="193"/>
-      <c r="C27" s="194"/>
-      <c r="D27" s="195"/>
-      <c r="E27" s="194"/>
-      <c r="F27" s="196"/>
-      <c r="G27" s="194"/>
-      <c r="H27" s="197"/>
-      <c r="I27" s="198"/>
-      <c r="J27" s="198"/>
+      <c r="B27" s="177"/>
+      <c r="C27" s="178"/>
+      <c r="D27" s="179"/>
+      <c r="E27" s="178"/>
+      <c r="F27" s="180"/>
+      <c r="G27" s="178"/>
+      <c r="H27" s="181"/>
+      <c r="I27" s="182"/>
+      <c r="J27" s="182"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="169" t="s">
+      <c r="A28" s="155" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="178">
+      <c r="B28" s="162">
         <v>2.64039774019777E-2</v>
       </c>
-      <c r="C28" s="179">
+      <c r="C28" s="163">
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="D28" s="180">
+      <c r="D28" s="164">
         <v>6.0324053411324102E-2</v>
       </c>
-      <c r="E28" s="179">
+      <c r="E28" s="163">
         <v>0.106064123700363</v>
       </c>
-      <c r="F28" s="181">
+      <c r="F28" s="165">
         <v>0.40884715673658401</v>
       </c>
-      <c r="G28" s="179">
+      <c r="G28" s="163">
         <v>6.8364015406650894E-2</v>
       </c>
-      <c r="H28" s="182">
+      <c r="H28" s="166">
         <v>0</v>
       </c>
-      <c r="I28" s="183">
+      <c r="I28" s="167">
         <v>30589</v>
       </c>
-      <c r="J28" s="183">
+      <c r="J28" s="167">
         <v>45777</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="169" t="s">
+      <c r="A29" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="178">
+      <c r="B29" s="162">
         <v>3.9132178171297799E-2</v>
       </c>
-      <c r="C29" s="179">
+      <c r="C29" s="163">
         <v>6.2011235623535797E-2</v>
       </c>
-      <c r="D29" s="180">
+      <c r="D29" s="164">
         <v>8.4890293075773796E-2</v>
       </c>
-      <c r="E29" s="179">
+      <c r="E29" s="163">
         <v>0.143080291393996</v>
       </c>
-      <c r="F29" s="181">
+      <c r="F29" s="165">
         <v>0.43340165874262299</v>
       </c>
-      <c r="G29" s="179">
+      <c r="G29" s="163">
         <v>8.7011235623535799E-2</v>
       </c>
-      <c r="H29" s="182">
+      <c r="H29" s="166">
         <v>0</v>
       </c>
-      <c r="I29" s="183">
+      <c r="I29" s="167">
         <v>30650</v>
       </c>
-      <c r="J29" s="183">
+      <c r="J29" s="167">
         <v>44925</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="184" t="s">
+      <c r="A30" s="168" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="185">
+      <c r="B30" s="169">
         <v>1.3852677823030299E-2</v>
       </c>
-      <c r="C30" s="186">
+      <c r="C30" s="170">
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="D30" s="187">
+      <c r="D30" s="171">
         <v>8.1345289061248299E-2</v>
       </c>
-      <c r="E30" s="186">
+      <c r="E30" s="170">
         <v>0.21081962919687999</v>
       </c>
-      <c r="F30" s="188">
+      <c r="F30" s="172">
         <v>0.225780605076804</v>
       </c>
-      <c r="G30" s="186">
+      <c r="G30" s="170">
         <v>7.2598983442139303E-2</v>
       </c>
-      <c r="H30" s="189">
+      <c r="H30" s="173">
         <v>0</v>
       </c>
-      <c r="I30" s="190">
+      <c r="I30" s="174">
         <v>30680</v>
       </c>
-      <c r="J30" s="190">
+      <c r="J30" s="174">
         <v>44925</v>
       </c>
     </row>
@@ -7797,19 +7834,19 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
-      <c r="B1" s="166" t="s">
+      <c r="B1" s="205" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
       <c r="H1" s="91"/>
-      <c r="I1" s="166" t="s">
+      <c r="I1" s="205" t="s">
         <v>155</v>
       </c>
-      <c r="J1" s="166"/>
+      <c r="J1" s="205"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>

--- a/epsilon-phi-core/src/python/epsilonPhi/core/reporting/formatted_excel.xlsx
+++ b/epsilon-phi-core/src/python/epsilonPhi/core/reporting/formatted_excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/python/epsilonPhi/core/reporting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/python/epsilonPhi/core/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1D610B-1983-D244-AD5C-3DF7C844BB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9248B3E2-DF9D-6149-9185-F6EE7063FDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26440" windowHeight="19040" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10520" yWindow="1860" windowWidth="26440" windowHeight="19040" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolios" sheetId="2" r:id="rId1"/>
@@ -403,9 +403,6 @@
     <t>PE_BUYOUT</t>
   </si>
   <si>
-    <t>PE_DISTRESSED</t>
-  </si>
-  <si>
     <t>PE_VENTURE</t>
   </si>
   <si>
@@ -611,6 +608,9 @@
   </si>
   <si>
     <t xml:space="preserve">    Core Real Estate</t>
+  </si>
+  <si>
+    <t>PE_GROWTH</t>
   </si>
 </sst>
 </file>
@@ -1607,54 +1607,6 @@
     <xf numFmtId="17" fontId="23" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="24" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1677,10 +1629,58 @@
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="6" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" s="150">
         <v>2</v>
@@ -3661,28 +3661,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="213"/>
-      <c r="B1" s="214" t="s">
+      <c r="A1" s="197"/>
+      <c r="B1" s="215" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="214" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" s="214"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="215" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="215"/>
     </row>
     <row r="2" spans="1:10" s="8" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="157"/>
-      <c r="B2" s="204" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
+      <c r="B2" s="213" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="213"/>
+      <c r="D2" s="213"/>
       <c r="E2" s="159" t="s">
         <v>31</v>
       </c>
@@ -3690,16 +3690,16 @@
         <v>30</v>
       </c>
       <c r="G2" s="158" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H2" s="159" t="s">
         <v>67</v>
       </c>
       <c r="I2" s="159" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="159" t="s">
         <v>153</v>
-      </c>
-      <c r="J2" s="159" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="154" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3718,7 +3718,7 @@
     </row>
     <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="155" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B4" s="162">
         <v>5.7241236937856403E-3</v>
@@ -3749,18 +3749,18 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="154" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="206" t="s">
+      <c r="A5" s="190" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="207"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="209"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="210"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
+      <c r="B5" s="191"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="193"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="194"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="195"/>
+      <c r="I5" s="196"/>
+      <c r="J5" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3872,232 +3872,232 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="53"/>
-      <c r="B1" s="197" t="s">
+      <c r="B1" s="206" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197" t="s">
+      <c r="C1" s="206"/>
+      <c r="D1" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197" t="s">
+      <c r="E1" s="206"/>
+      <c r="F1" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197" t="s">
+      <c r="G1" s="206"/>
+      <c r="H1" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="198"/>
+      <c r="I1" s="207"/>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="199">
+      <c r="B2" s="208">
         <v>0.745</v>
       </c>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199" t="s">
+      <c r="C2" s="208"/>
+      <c r="D2" s="208" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="199"/>
-      <c r="F2" s="199">
+      <c r="E2" s="208"/>
+      <c r="F2" s="208">
         <v>0.36</v>
       </c>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199">
+      <c r="G2" s="208"/>
+      <c r="H2" s="208">
         <v>0.15</v>
       </c>
-      <c r="I2" s="199"/>
+      <c r="I2" s="208"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="192">
+      <c r="B3" s="201">
         <v>0.02</v>
       </c>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192">
+      <c r="C3" s="201"/>
+      <c r="D3" s="201">
         <v>0.03</v>
       </c>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192">
+      <c r="E3" s="201"/>
+      <c r="F3" s="201">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G3" s="192"/>
-      <c r="H3" s="192">
+      <c r="G3" s="201"/>
+      <c r="H3" s="201">
         <v>5.5E-2</v>
       </c>
-      <c r="I3" s="192"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="192">
+      <c r="B4" s="201">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C4" s="192"/>
-      <c r="D4" s="192">
+      <c r="C4" s="201"/>
+      <c r="D4" s="201">
         <v>0.22500000000000001</v>
       </c>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192">
+      <c r="E4" s="201"/>
+      <c r="F4" s="201">
         <v>0.35499999999999998</v>
       </c>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192">
+      <c r="G4" s="201"/>
+      <c r="H4" s="201">
         <v>0.505</v>
       </c>
-      <c r="I4" s="192"/>
+      <c r="I4" s="201"/>
     </row>
     <row r="5" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="192">
+      <c r="B5" s="201">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C5" s="192"/>
-      <c r="D5" s="192">
+      <c r="C5" s="201"/>
+      <c r="D5" s="201">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192">
+      <c r="E5" s="201"/>
+      <c r="F5" s="201">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G5" s="192"/>
-      <c r="H5" s="192">
+      <c r="G5" s="201"/>
+      <c r="H5" s="201">
         <v>0.03</v>
       </c>
-      <c r="I5" s="192"/>
+      <c r="I5" s="201"/>
     </row>
     <row r="6" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="192">
+      <c r="B6" s="201">
         <v>0.04</v>
       </c>
-      <c r="C6" s="192"/>
-      <c r="D6" s="192">
+      <c r="C6" s="201"/>
+      <c r="D6" s="201">
         <v>5.5E-2</v>
       </c>
-      <c r="E6" s="192"/>
-      <c r="F6" s="192">
+      <c r="E6" s="201"/>
+      <c r="F6" s="201">
         <v>0.12</v>
       </c>
-      <c r="G6" s="192"/>
-      <c r="H6" s="192">
+      <c r="G6" s="201"/>
+      <c r="H6" s="201">
         <v>0.185</v>
       </c>
-      <c r="I6" s="192"/>
+      <c r="I6" s="201"/>
     </row>
     <row r="7" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="193">
+      <c r="B7" s="202">
         <v>0.04</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="193">
+      <c r="C7" s="202"/>
+      <c r="D7" s="202">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E7" s="193"/>
-      <c r="F7" s="193">
+      <c r="E7" s="202"/>
+      <c r="F7" s="202">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G7" s="193"/>
-      <c r="H7" s="193">
+      <c r="G7" s="202"/>
+      <c r="H7" s="202">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I7" s="193"/>
+      <c r="I7" s="202"/>
     </row>
     <row r="8" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="194">
+      <c r="B8" s="203">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194">
+      <c r="C8" s="203"/>
+      <c r="D8" s="203">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194">
+      <c r="E8" s="203"/>
+      <c r="F8" s="203">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="G8" s="194"/>
-      <c r="H8" s="194">
+      <c r="G8" s="203"/>
+      <c r="H8" s="203">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="I8" s="194"/>
+      <c r="I8" s="203"/>
     </row>
     <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="195">
+      <c r="B9" s="204">
         <v>0.6</v>
       </c>
-      <c r="C9" s="195"/>
-      <c r="D9" s="195">
+      <c r="C9" s="204"/>
+      <c r="D9" s="204">
         <v>0.59</v>
       </c>
-      <c r="E9" s="195"/>
-      <c r="F9" s="195">
+      <c r="E9" s="204"/>
+      <c r="F9" s="204">
         <v>0.53</v>
       </c>
-      <c r="G9" s="195"/>
-      <c r="H9" s="195">
+      <c r="G9" s="204"/>
+      <c r="H9" s="204">
         <v>0.49</v>
       </c>
-      <c r="I9" s="195"/>
+      <c r="I9" s="204"/>
     </row>
     <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="192">
+      <c r="B10" s="201">
         <v>3.1E-2</v>
       </c>
-      <c r="C10" s="192"/>
-      <c r="D10" s="192">
+      <c r="C10" s="201"/>
+      <c r="D10" s="201">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="E10" s="192"/>
-      <c r="F10" s="192">
+      <c r="E10" s="201"/>
+      <c r="F10" s="201">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="G10" s="192"/>
-      <c r="H10" s="192">
+      <c r="G10" s="201"/>
+      <c r="H10" s="201">
         <v>0.10299999999999999</v>
       </c>
-      <c r="I10" s="192"/>
+      <c r="I10" s="201"/>
     </row>
     <row r="11" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="196" t="s">
+      <c r="B11" s="205" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="196"/>
-      <c r="D11" s="196" t="s">
+      <c r="C11" s="205"/>
+      <c r="D11" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="196"/>
-      <c r="F11" s="196" t="s">
+      <c r="E11" s="205"/>
+      <c r="F11" s="205" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="196"/>
-      <c r="H11" s="196" t="s">
+      <c r="G11" s="205"/>
+      <c r="H11" s="205" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="196"/>
+      <c r="I11" s="205"/>
     </row>
     <row r="12" spans="1:9" s="8" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="59" t="s">
@@ -4390,64 +4390,64 @@
       <c r="A23" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="190">
+      <c r="B23" s="199">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C23" s="190"/>
-      <c r="D23" s="190">
+      <c r="C23" s="199"/>
+      <c r="D23" s="199">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E23" s="190"/>
-      <c r="F23" s="190">
+      <c r="E23" s="199"/>
+      <c r="F23" s="199">
         <v>6.3E-2</v>
       </c>
-      <c r="G23" s="190"/>
-      <c r="H23" s="190">
+      <c r="G23" s="199"/>
+      <c r="H23" s="199">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="I23" s="190"/>
+      <c r="I23" s="199"/>
     </row>
     <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="190">
+      <c r="B24" s="199">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C24" s="190"/>
-      <c r="D24" s="190">
+      <c r="C24" s="199"/>
+      <c r="D24" s="199">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="E24" s="190"/>
-      <c r="F24" s="190">
+      <c r="E24" s="199"/>
+      <c r="F24" s="199">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G24" s="190"/>
-      <c r="H24" s="190">
+      <c r="G24" s="199"/>
+      <c r="H24" s="199">
         <v>0.24299999999999999</v>
       </c>
-      <c r="I24" s="190"/>
+      <c r="I24" s="199"/>
     </row>
     <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="191">
+      <c r="B25" s="200">
         <v>0</v>
       </c>
-      <c r="C25" s="191"/>
-      <c r="D25" s="191">
+      <c r="C25" s="200"/>
+      <c r="D25" s="200">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="E25" s="191"/>
-      <c r="F25" s="191">
+      <c r="E25" s="200"/>
+      <c r="F25" s="200">
         <v>0.14899999999999999</v>
       </c>
-      <c r="G25" s="191"/>
-      <c r="H25" s="191">
+      <c r="G25" s="200"/>
+      <c r="H25" s="200">
         <v>0.253</v>
       </c>
-      <c r="I25" s="191"/>
+      <c r="I25" s="200"/>
     </row>
     <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="67" t="s">
@@ -4466,64 +4466,64 @@
       <c r="A27" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="190">
+      <c r="B27" s="199">
         <v>0.23799999999999999</v>
       </c>
-      <c r="C27" s="190"/>
-      <c r="D27" s="190">
+      <c r="C27" s="199"/>
+      <c r="D27" s="199">
         <v>0.27900000000000003</v>
       </c>
-      <c r="E27" s="190"/>
-      <c r="F27" s="190">
+      <c r="E27" s="199"/>
+      <c r="F27" s="199">
         <v>0.314</v>
       </c>
-      <c r="G27" s="190"/>
-      <c r="H27" s="190">
+      <c r="G27" s="199"/>
+      <c r="H27" s="199">
         <v>0.33700000000000002</v>
       </c>
-      <c r="I27" s="190"/>
+      <c r="I27" s="199"/>
     </row>
     <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="190">
+      <c r="B28" s="199">
         <v>0.04</v>
       </c>
-      <c r="C28" s="190"/>
-      <c r="D28" s="190">
+      <c r="C28" s="199"/>
+      <c r="D28" s="199">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="E28" s="190"/>
-      <c r="F28" s="190">
+      <c r="E28" s="199"/>
+      <c r="F28" s="199">
         <v>0.14299999999999999</v>
       </c>
-      <c r="G28" s="190"/>
-      <c r="H28" s="190">
+      <c r="G28" s="199"/>
+      <c r="H28" s="199">
         <v>0.187</v>
       </c>
-      <c r="I28" s="190"/>
+      <c r="I28" s="199"/>
     </row>
     <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="190">
+      <c r="B29" s="199">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C29" s="190"/>
-      <c r="D29" s="190">
+      <c r="C29" s="199"/>
+      <c r="D29" s="199">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="E29" s="190"/>
-      <c r="F29" s="190">
+      <c r="E29" s="199"/>
+      <c r="F29" s="199">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G29" s="190"/>
-      <c r="H29" s="190">
+      <c r="G29" s="199"/>
+      <c r="H29" s="199">
         <v>0.108</v>
       </c>
-      <c r="I29" s="190"/>
+      <c r="I29" s="199"/>
     </row>
     <row r="30" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="59" t="s">
@@ -5168,16 +5168,16 @@
   <sheetData>
     <row r="1" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="19"/>
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="211" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
       <c r="J1" s="21"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -5185,13 +5185,13 @@
     </row>
     <row r="2" spans="1:16" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
-      <c r="B2" s="200" t="s">
+      <c r="B2" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="210"/>
       <c r="G2" s="24" t="s">
         <v>31</v>
       </c>
@@ -6340,27 +6340,27 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="155"/>
-      <c r="B1" s="203" t="s">
+      <c r="B1" s="212" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
       <c r="H1" s="156"/>
-      <c r="I1" s="203" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" s="203"/>
+      <c r="I1" s="212" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="212"/>
     </row>
     <row r="2" spans="1:10" s="8" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="157"/>
-      <c r="B2" s="204" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
+      <c r="B2" s="213" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="213"/>
+      <c r="D2" s="213"/>
       <c r="E2" s="159" t="s">
         <v>31</v>
       </c>
@@ -6368,16 +6368,16 @@
         <v>30</v>
       </c>
       <c r="G2" s="158" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H2" s="159" t="s">
         <v>67</v>
       </c>
       <c r="I2" s="159" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="159" t="s">
         <v>153</v>
-      </c>
-      <c r="J2" s="159" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
@@ -6396,7 +6396,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="155" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B4" s="162">
         <v>5.7241236937856403E-3</v>
@@ -6428,7 +6428,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="183" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B5" s="184">
         <v>4.32971260588862E-4</v>
@@ -6474,7 +6474,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="183" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B7" s="184">
         <v>2.64039774019777E-2</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="155" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B9" s="162">
         <v>1.7523010713942501E-2</v>
@@ -6552,7 +6552,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B10" s="162">
         <v>3.7739774522967298E-2</v>
@@ -6584,7 +6584,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B11" s="162">
         <v>3.9116118459153602E-2</v>
@@ -6616,7 +6616,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="155" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B12" s="162">
         <v>2.0982633206710101E-2</v>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="155" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B13" s="162">
         <v>2.5237430201924101E-2</v>
@@ -6680,7 +6680,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="155" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B14" s="162">
         <v>-1.15459534877681E-3</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="155" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B15" s="162">
         <v>2.74370548378081E-2</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="155" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B16" s="162">
         <v>3.5865028766390701E-2</v>
@@ -6776,7 +6776,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="155" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B17" s="162">
         <v>3.9211523567242897E-2</v>
@@ -6808,7 +6808,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="183" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B18" s="184">
         <v>1.6403181443203799E-2</v>
@@ -6854,7 +6854,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="155" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B20" s="162">
         <v>7.6750631221554899E-3</v>
@@ -6886,7 +6886,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="155" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B21" s="162">
         <v>4.3657888915111303E-3</v>
@@ -6918,7 +6918,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="183" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B22" s="184">
         <v>3.4812134452342201E-3</v>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="155" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B24" s="162">
         <v>2.6608812004023499E-2</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="155" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B25" s="162">
         <v>1.78707608365977E-2</v>
@@ -7028,7 +7028,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="183" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B26" s="184">
         <v>1.3852677823030299E-2</v>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="155" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B28" s="162">
         <v>2.64039774019777E-2</v>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="155" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B29" s="162">
         <v>3.9132178171297799E-2</v>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="168" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B30" s="169">
         <v>1.3852677823030299E-2</v>
@@ -7197,10 +7197,10 @@
         <v>117</v>
       </c>
       <c r="B1" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="86" t="s">
         <v>159</v>
-      </c>
-      <c r="C1" s="86" t="s">
-        <v>160</v>
       </c>
       <c r="D1" s="87" t="s">
         <v>0</v>
@@ -7246,10 +7246,10 @@
     </row>
     <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C3" s="74" t="s">
         <v>4</v>
@@ -7275,7 +7275,7 @@
         <v>101</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="74" t="s">
         <v>6</v>
@@ -7662,7 +7662,7 @@
     </row>
     <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="B19" s="74" t="s">
         <v>23</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" s="74" t="s">
         <v>24</v>
@@ -7714,7 +7714,7 @@
     </row>
     <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B21" s="74" t="s">
         <v>26</v>
@@ -7740,7 +7740,7 @@
     </row>
     <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B22" s="74" t="s">
         <v>97</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="23" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" s="74" t="s">
         <v>27</v>
@@ -7834,19 +7834,19 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
-      <c r="B1" s="205" t="s">
+      <c r="B1" s="214" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
       <c r="H1" s="91"/>
-      <c r="I1" s="205" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" s="205"/>
+      <c r="I1" s="214" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="214"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
@@ -7854,13 +7854,13 @@
     <row r="2" spans="1:13" s="8" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="95"/>
       <c r="B2" s="96" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="97" t="s">
         <v>149</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="D2" s="96" t="s">
         <v>150</v>
-      </c>
-      <c r="D2" s="96" t="s">
-        <v>151</v>
       </c>
       <c r="E2" s="96" t="s">
         <v>31</v>
@@ -7869,30 +7869,30 @@
         <v>30</v>
       </c>
       <c r="G2" s="97" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H2" s="96" t="s">
         <v>67</v>
       </c>
       <c r="I2" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="96" t="s">
         <v>153</v>
       </c>
-      <c r="J2" s="96" t="s">
-        <v>154</v>
-      </c>
       <c r="K2" s="120" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="L2" s="96" t="s">
+      <c r="M2" s="112" t="s">
         <v>157</v>
-      </c>
-      <c r="M2" s="112" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B3" s="92"/>
       <c r="C3" s="92"/>
@@ -7909,7 +7909,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4" s="92">
         <v>5.7241236937856403E-3</v>
@@ -7953,7 +7953,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" s="92">
         <v>4.32971260588862E-4</v>
@@ -8014,7 +8014,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="108" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B7" s="109">
         <v>2.64039774019777E-2</v>
@@ -8075,7 +8075,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="108" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="109">
         <v>1.7523010713942501E-2</v>
@@ -8119,7 +8119,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" s="92">
         <v>3.7739774522967298E-2</v>
@@ -8163,7 +8163,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="108" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" s="109">
         <v>3.9116118459153602E-2</v>
@@ -8207,7 +8207,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="92">
         <v>2.0982633206710101E-2</v>
@@ -8251,7 +8251,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B13" s="92">
         <v>2.5237430201924101E-2</v>
@@ -8295,7 +8295,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B14" s="92">
         <v>-1.15459534877681E-3</v>
@@ -8339,7 +8339,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="108" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B15" s="109">
         <v>2.74370548378081E-2</v>
@@ -8383,7 +8383,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B16" s="109">
         <v>3.5865028766390701E-2</v>
@@ -8427,7 +8427,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B17" s="92">
         <v>3.9211523567242897E-2</v>
@@ -8471,7 +8471,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B18" s="92">
         <v>1.6403181443203799E-2</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B20" s="92">
         <v>7.6750631221554899E-3</v>
@@ -8576,7 +8576,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B21" s="109">
         <v>4.3657888915111303E-3</v>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="108" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B22" s="109">
         <v>3.4812134452342201E-3</v>
@@ -8681,7 +8681,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B24" s="92">
         <v>2.6608812004023499E-2</v>
@@ -8725,7 +8725,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B25" s="92">
         <v>1.78707608365977E-2</v>
@@ -8769,7 +8769,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B26" s="92">
         <v>1.3852677823030299E-2</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B28" s="92">
         <v>2.64039774019777E-2</v>
@@ -8874,7 +8874,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="100" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B29" s="101">
         <v>3.9132178171297799E-2</v>
@@ -8918,7 +8918,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="94" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B30" s="104">
         <v>1.3852677823030299E-2</v>
@@ -9115,34 +9115,34 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="143" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1" s="143" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="144" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B2" s="128" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="145" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B3" s="145" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="146" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" s="147" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -9151,18 +9151,18 @@
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B7" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -9171,10 +9171,10 @@
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B9" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -9183,10 +9183,10 @@
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B11" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/epsilon-phi-core/src/python/epsilonPhi/core/reporting/formatted_excel.xlsx
+++ b/epsilon-phi-core/src/python/epsilonPhi/core/reporting/formatted_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/python/epsilonPhi/core/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9248B3E2-DF9D-6149-9185-F6EE7063FDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207272FA-1F82-F647-99CE-A030A062C170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10520" yWindow="1860" windowWidth="26440" windowHeight="19040" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-40300" yWindow="2780" windowWidth="32820" windowHeight="20420" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolios" sheetId="2" r:id="rId1"/>
@@ -811,7 +811,7 @@
       <name val="Grotesque"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -832,30 +832,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -886,18 +862,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF577908"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8F5A31"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1098,7 +1062,7 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1130,10 +1094,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1208,7 +1168,7 @@
     <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1279,10 +1239,10 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="11"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1328,7 +1288,7 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1381,14 +1341,14 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1406,10 +1366,10 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1424,7 +1384,7 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="8" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1439,7 +1399,7 @@
     <xf numFmtId="2" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="9"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1482,22 +1442,22 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="9"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="9"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1506,130 +1466,152 @@
     <xf numFmtId="165" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="9"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="23" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="23" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="16" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="23" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="23" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="16" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="16" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="16" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="23" fillId="16" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="23" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="16" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="23" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="23" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="23" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="28" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="28" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="24" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="24" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="24" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="16" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="24" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="24" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="24" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="16" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="10" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="16" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="10" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="16" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="23" fillId="16" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="23" fillId="10" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="16" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="23" fillId="10" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="23" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="23" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="24" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="24" fillId="10" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="10" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="10" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="24" fillId="16" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="10" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="16" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="24" fillId="10" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="24" fillId="16" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="24" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1638,30 +1620,6 @@
     <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1671,17 +1629,20 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1704,16 +1665,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF737373"/>
-      <color rgb="FF807C80"/>
-      <color rgb="FF000004"/>
-      <color rgb="FF039644"/>
-      <color rgb="FF0F243E"/>
-      <color rgb="FF56A82A"/>
-      <color rgb="FF56A807"/>
-      <color rgb="FF567707"/>
-      <color rgb="FF0F2442"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF16537D"/>
+      <color rgb="FFB37838"/>
+      <color rgb="FF999A9A"/>
+      <color rgb="FF658E00"/>
+      <color rgb="FF418E00"/>
+      <color rgb="FFDDA500"/>
+      <color rgb="FF000000"/>
+      <color rgb="FFCE9A00"/>
+      <color rgb="FFA26C32"/>
+      <color rgb="FF1B5381"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1728,6 +1689,438 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.6596068786070678E-2"/>
+          <c:y val="4.0039682539682549E-2"/>
+          <c:w val="0.9068078624278586"/>
+          <c:h val="0.9163095238095238"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Factor Charts'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:srgbClr val="16537D"/>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-91AB-C94E-B35D-8C6D46E5D70B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="wdDnDiag">
+                <a:fgClr>
+                  <a:srgbClr val="658E00"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="40000"/>
+                    <a:lumOff val="60000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-91AB-C94E-B35D-8C6D46E5D70B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="wdUpDiag">
+                <a:fgClr>
+                  <a:srgbClr val="B37838"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-91AB-C94E-B35D-8C6D46E5D70B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="plaid">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-91AB-C94E-B35D-8C6D46E5D70B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="solidDmnd">
+                <a:fgClr>
+                  <a:schemeClr val="accent4"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-91AB-C94E-B35D-8C6D46E5D70B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="smCheck">
+                <a:fgClr>
+                  <a:srgbClr val="DDA500"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="40000"/>
+                    <a:lumOff val="60000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-91AB-C94E-B35D-8C6D46E5D70B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>'Factor Charts'!$I$2:$I$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="1">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-91AB-C94E-B35D-8C6D46E5D70B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="0"/>
+        <c:overlap val="100"/>
+        <c:axId val="295615184"/>
+        <c:axId val="344716032"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="295615184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="50000"/>
+                <a:alpha val="99000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="344716032"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:tickMarkSkip val="8"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="344716032"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="295615184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -2208,7 +2601,552 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2715,6 +3653,47 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>744362</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>56443</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>767080</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>158042</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3E8C5EF-66D3-328F-4C2C-338F9D886CB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>806450</xdr:colOff>
       <xdr:row>9</xdr:row>
@@ -3045,510 +4024,510 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70"/>
-      <c r="B1" s="71" t="s">
+      <c r="A1" s="66"/>
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="67" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="148">
+      <c r="B2" s="144">
         <v>0.745</v>
       </c>
-      <c r="C2" s="148" t="s">
+      <c r="C2" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="148">
+      <c r="D2" s="144">
         <v>0.36</v>
       </c>
-      <c r="E2" s="148">
+      <c r="E2" s="144">
         <v>0.15</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="149">
+      <c r="B3" s="145">
         <v>24.5</v>
       </c>
-      <c r="C3" s="149">
+      <c r="C3" s="145">
         <v>58.5</v>
       </c>
-      <c r="D3" s="150">
+      <c r="D3" s="146">
         <v>36</v>
       </c>
-      <c r="E3" s="150">
+      <c r="E3" s="146">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="150">
+      <c r="B4" s="146">
         <v>50</v>
       </c>
-      <c r="C4" s="149" t="s">
+      <c r="C4" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="149" t="s">
+      <c r="D4" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="149" t="s">
+      <c r="E4" s="145" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="148">
+      <c r="B5" s="144">
         <v>0.02</v>
       </c>
-      <c r="C5" s="148">
+      <c r="C5" s="144">
         <v>0.03</v>
       </c>
-      <c r="D5" s="148">
+      <c r="D5" s="144">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="E5" s="148">
+      <c r="E5" s="144">
         <v>5.5E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="70" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="150">
+      <c r="B6" s="146">
         <v>2</v>
       </c>
-      <c r="C6" s="150">
+      <c r="C6" s="146">
         <v>3</v>
       </c>
-      <c r="D6" s="149">
+      <c r="D6" s="145">
         <v>4.5</v>
       </c>
-      <c r="E6" s="149">
+      <c r="E6" s="145">
         <v>5.5</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="148">
+      <c r="B7" s="144">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C7" s="148">
+      <c r="C7" s="144">
         <v>0.22500000000000001</v>
       </c>
-      <c r="D7" s="148">
+      <c r="D7" s="144">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E7" s="148">
+      <c r="E7" s="144">
         <v>0.505</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="149">
+      <c r="B8" s="145">
         <v>3.9</v>
       </c>
-      <c r="C8" s="149">
+      <c r="C8" s="145">
         <v>6.3</v>
       </c>
-      <c r="D8" s="150">
+      <c r="D8" s="146">
         <v>10</v>
       </c>
-      <c r="E8" s="149">
+      <c r="E8" s="145">
         <v>14.2</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="149">
+      <c r="B9" s="145">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C9" s="149">
+      <c r="C9" s="145">
         <v>7.1</v>
       </c>
-      <c r="D9" s="149">
+      <c r="D9" s="145">
         <v>11.2</v>
       </c>
-      <c r="E9" s="149">
+      <c r="E9" s="145">
         <v>15.9</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="149">
+      <c r="B10" s="145">
         <v>1.4</v>
       </c>
-      <c r="C10" s="149">
+      <c r="C10" s="145">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D10" s="149">
+      <c r="D10" s="145">
         <v>3.5</v>
       </c>
-      <c r="E10" s="150">
+      <c r="E10" s="146">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="149">
+      <c r="B11" s="145">
         <v>1.6</v>
       </c>
-      <c r="C11" s="149">
+      <c r="C11" s="145">
         <v>2.5</v>
       </c>
-      <c r="D11" s="150">
+      <c r="D11" s="146">
         <v>4</v>
       </c>
-      <c r="E11" s="149">
+      <c r="E11" s="145">
         <v>5.7</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="149">
+      <c r="B12" s="145">
         <v>0.5</v>
       </c>
-      <c r="C12" s="149">
+      <c r="C12" s="145">
         <v>0.8</v>
       </c>
-      <c r="D12" s="149">
+      <c r="D12" s="145">
         <v>1.2</v>
       </c>
-      <c r="E12" s="149">
+      <c r="E12" s="145">
         <v>1.7</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="149">
+      <c r="B13" s="145">
         <v>0.7</v>
       </c>
-      <c r="C13" s="149">
+      <c r="C13" s="145">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D13" s="149">
+      <c r="D13" s="145">
         <v>1.8</v>
       </c>
-      <c r="E13" s="149">
+      <c r="E13" s="145">
         <v>2.6</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="149">
+      <c r="B14" s="145">
         <v>0.4</v>
       </c>
-      <c r="C14" s="149">
+      <c r="C14" s="145">
         <v>0.6</v>
       </c>
-      <c r="D14" s="149">
+      <c r="D14" s="145">
         <v>0.9</v>
       </c>
-      <c r="E14" s="149">
+      <c r="E14" s="145">
         <v>1.3</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="149">
+      <c r="B15" s="145">
         <v>0.4</v>
       </c>
-      <c r="C15" s="149">
+      <c r="C15" s="145">
         <v>0.6</v>
       </c>
-      <c r="D15" s="149">
+      <c r="D15" s="145">
         <v>0.9</v>
       </c>
-      <c r="E15" s="149">
+      <c r="E15" s="145">
         <v>1.3</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="74" t="s">
+      <c r="A16" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="150">
+      <c r="B16" s="146">
         <v>0.4</v>
       </c>
-      <c r="C16" s="150">
+      <c r="C16" s="146">
         <v>0.65</v>
       </c>
-      <c r="D16" s="150">
+      <c r="D16" s="146">
         <v>1</v>
       </c>
-      <c r="E16" s="150">
+      <c r="E16" s="146">
         <v>1.4</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="74" t="s">
+      <c r="A17" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="150">
+      <c r="B17" s="146">
         <v>0.4</v>
       </c>
-      <c r="C17" s="150">
+      <c r="C17" s="146">
         <v>0.65</v>
       </c>
-      <c r="D17" s="150">
+      <c r="D17" s="146">
         <v>1</v>
       </c>
-      <c r="E17" s="150">
+      <c r="E17" s="146">
         <v>1.4</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="72" t="s">
+      <c r="A18" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="148">
+      <c r="B18" s="144">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C18" s="148">
+      <c r="C18" s="144">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="D18" s="148">
+      <c r="D18" s="144">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="E18" s="148">
+      <c r="E18" s="144">
         <v>0.03</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="74" t="s">
+      <c r="A19" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="149">
+      <c r="B19" s="145">
         <v>0.3</v>
       </c>
-      <c r="C19" s="149">
+      <c r="C19" s="145">
         <v>0.7</v>
       </c>
-      <c r="D19" s="149">
+      <c r="D19" s="145">
         <v>0.9</v>
       </c>
-      <c r="E19" s="149">
+      <c r="E19" s="145">
         <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="149">
+      <c r="B20" s="145">
         <v>0.6</v>
       </c>
-      <c r="C20" s="149">
+      <c r="C20" s="145">
         <v>1.4</v>
       </c>
-      <c r="D20" s="149">
+      <c r="D20" s="145">
         <v>1.8</v>
       </c>
-      <c r="E20" s="149">
+      <c r="E20" s="145">
         <v>1.2</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="74" t="s">
+      <c r="A21" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="149">
+      <c r="B21" s="145">
         <v>0.6</v>
       </c>
-      <c r="C21" s="149">
+      <c r="C21" s="145">
         <v>1.4</v>
       </c>
-      <c r="D21" s="149">
+      <c r="D21" s="145">
         <v>1.8</v>
       </c>
-      <c r="E21" s="149">
+      <c r="E21" s="145">
         <v>1.2</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="148">
+      <c r="B22" s="144">
         <v>0.04</v>
       </c>
-      <c r="C22" s="148">
+      <c r="C22" s="144">
         <v>5.5E-2</v>
       </c>
-      <c r="D22" s="148">
+      <c r="D22" s="144">
         <v>0.12</v>
       </c>
-      <c r="E22" s="148">
+      <c r="E22" s="144">
         <v>0.185</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="150">
+      <c r="B23" s="146">
         <v>3</v>
       </c>
-      <c r="C23" s="150">
+      <c r="C23" s="146">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D23" s="150">
+      <c r="D23" s="146">
         <v>8.4</v>
       </c>
-      <c r="E23" s="150">
+      <c r="E23" s="146">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="74" t="s">
+      <c r="A24" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="150">
+      <c r="B24" s="146">
         <v>1</v>
       </c>
-      <c r="C24" s="150">
+      <c r="C24" s="146">
         <v>1.4</v>
       </c>
-      <c r="D24" s="150">
+      <c r="D24" s="146">
         <v>2.8</v>
       </c>
-      <c r="E24" s="150">
+      <c r="E24" s="146">
         <v>4.3</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="74" t="s">
+      <c r="A25" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="149" t="s">
+      <c r="B25" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="149" t="s">
+      <c r="C25" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="149">
+      <c r="D25" s="145">
         <v>0.8</v>
       </c>
-      <c r="E25" s="149">
+      <c r="E25" s="145">
         <v>1.2</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="148">
+      <c r="B26" s="144">
         <v>0.04</v>
       </c>
-      <c r="C26" s="148">
+      <c r="C26" s="144">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D26" s="148">
+      <c r="D26" s="144">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E26" s="148">
+      <c r="E26" s="144">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="74" t="s">
+      <c r="A27" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="149">
+      <c r="B27" s="145">
         <v>1.3</v>
       </c>
-      <c r="C27" s="149">
+      <c r="C27" s="145">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D27" s="149">
+      <c r="D27" s="145">
         <v>3.5</v>
       </c>
-      <c r="E27" s="149">
+      <c r="E27" s="145">
         <v>3.5</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="74" t="s">
+      <c r="A28" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="150">
+      <c r="B28" s="146">
         <v>1.35</v>
       </c>
-      <c r="C28" s="150">
+      <c r="C28" s="146">
         <v>2.35</v>
       </c>
-      <c r="D28" s="150">
+      <c r="D28" s="146">
         <v>2</v>
       </c>
-      <c r="E28" s="150">
+      <c r="E28" s="146">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="74" t="s">
+      <c r="A29" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="150">
+      <c r="B29" s="146">
         <v>1.35</v>
       </c>
-      <c r="C29" s="150">
+      <c r="C29" s="146">
         <v>2.35</v>
       </c>
-      <c r="D29" s="150">
+      <c r="D29" s="146">
         <v>2</v>
       </c>
-      <c r="E29" s="150">
+      <c r="E29" s="146">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="76" t="s">
+      <c r="A30" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="77">
+      <c r="B30" s="73">
         <v>1</v>
       </c>
-      <c r="C30" s="77">
+      <c r="C30" s="73">
         <v>1</v>
       </c>
-      <c r="D30" s="77">
+      <c r="D30" s="73">
         <v>1</v>
       </c>
-      <c r="E30" s="77">
+      <c r="E30" s="73">
         <v>1</v>
       </c>
     </row>
@@ -3560,84 +4539,84 @@
       <c r="E31" s="7"/>
     </row>
     <row r="32" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="78" t="s">
+      <c r="A32" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="79">
+      <c r="B32" s="75">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="C32" s="79">
+      <c r="C32" s="75">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="D32" s="79">
+      <c r="D32" s="75">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="E32" s="79">
+      <c r="E32" s="75">
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="78" t="s">
+      <c r="A33" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="80">
+      <c r="B33" s="76">
         <v>0.6</v>
       </c>
-      <c r="C33" s="80">
+      <c r="C33" s="76">
         <v>0.59</v>
       </c>
-      <c r="D33" s="80">
+      <c r="D33" s="76">
         <v>0.53</v>
       </c>
-      <c r="E33" s="80">
+      <c r="E33" s="76">
         <v>0.49</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="125"/>
-      <c r="B34" s="127"/>
-      <c r="C34" s="127"/>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
+      <c r="A34" s="121"/>
+      <c r="B34" s="123"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="123"/>
+      <c r="E34" s="123"/>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="78" t="s">
+      <c r="A35" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="79">
+      <c r="B35" s="75">
         <v>3.1E-2</v>
       </c>
-      <c r="C35" s="79">
+      <c r="C35" s="75">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="D35" s="79">
+      <c r="D35" s="75">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="E35" s="79">
+      <c r="E35" s="75">
         <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="125"/>
-      <c r="B36" s="126"/>
-      <c r="C36" s="126"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
+      <c r="A36" s="121"/>
+      <c r="B36" s="122"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
     </row>
     <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="78" t="s">
+      <c r="A37" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="81" t="s">
+      <c r="B37" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="81" t="s">
+      <c r="C37" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="81" t="s">
+      <c r="D37" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E37" s="81" t="s">
+      <c r="E37" s="77" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3661,106 +4640,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="197"/>
-      <c r="B1" s="215" t="s">
+      <c r="A1" s="191"/>
+      <c r="B1" s="209" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="198"/>
-      <c r="I1" s="215" t="s">
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="209"/>
+      <c r="F1" s="209"/>
+      <c r="G1" s="209"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="209" t="s">
         <v>154</v>
       </c>
-      <c r="J1" s="215"/>
+      <c r="J1" s="209"/>
     </row>
     <row r="2" spans="1:10" s="8" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="157"/>
-      <c r="B2" s="213" t="s">
+      <c r="A2" s="151"/>
+      <c r="B2" s="207" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="159" t="s">
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="153" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="159" t="s">
+      <c r="F2" s="153" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="158" t="s">
+      <c r="G2" s="152" t="s">
         <v>151</v>
       </c>
-      <c r="H2" s="159" t="s">
+      <c r="H2" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="159" t="s">
+      <c r="I2" s="153" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="159" t="s">
+      <c r="J2" s="153" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="154" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="160" t="s">
+    <row r="3" spans="1:10" s="148" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="154" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="161"/>
-      <c r="C3" s="161"/>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="161"/>
-      <c r="I3" s="161"/>
-      <c r="J3" s="161"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
     </row>
     <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="155" t="s">
+      <c r="A4" s="149" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="162">
+      <c r="B4" s="156">
         <v>5.7241236937856403E-3</v>
       </c>
-      <c r="C4" s="163">
+      <c r="C4" s="157">
         <v>1.08524678406041E-2</v>
       </c>
-      <c r="D4" s="164">
+      <c r="D4" s="158">
         <v>1.59808119874227E-2</v>
       </c>
-      <c r="E4" s="163">
+      <c r="E4" s="157">
         <v>3.2071468696963902E-2</v>
       </c>
-      <c r="F4" s="165">
+      <c r="F4" s="159">
         <v>0.33838387456298602</v>
       </c>
-      <c r="G4" s="163">
+      <c r="G4" s="157">
         <v>3.5852467840604099E-2</v>
       </c>
-      <c r="H4" s="166">
+      <c r="H4" s="160">
         <v>0</v>
       </c>
-      <c r="I4" s="167">
+      <c r="I4" s="161">
         <v>26723</v>
       </c>
-      <c r="J4" s="167">
+      <c r="J4" s="161">
         <v>45777</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="154" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="190" t="s">
+    <row r="5" spans="1:10" s="148" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="191"/>
-      <c r="C5" s="192"/>
-      <c r="D5" s="193"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="192"/>
-      <c r="H5" s="195"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
+      <c r="B5" s="185"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="187"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="189"/>
+      <c r="I5" s="190"/>
+      <c r="J5" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3782,76 +4761,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70"/>
-      <c r="B1" s="71" t="s">
+      <c r="A1" s="66"/>
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="73">
+      <c r="B2" s="69">
         <v>0.745</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="75">
+      <c r="B3" s="71">
         <v>24.5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="77">
+      <c r="B4" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="134"/>
-      <c r="B5" s="135"/>
+      <c r="A5" s="130"/>
+      <c r="B5" s="131"/>
     </row>
     <row r="6" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="136" t="s">
+      <c r="A6" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="137">
+      <c r="B6" s="133">
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="132" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="138">
+      <c r="B7" s="134">
         <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="139"/>
-      <c r="B8" s="140"/>
+      <c r="A8" s="135"/>
+      <c r="B8" s="136"/>
     </row>
     <row r="9" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="136" t="s">
+      <c r="A9" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="137">
+      <c r="B9" s="133">
         <v>3.1E-2</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="139"/>
-      <c r="B10" s="141"/>
+      <c r="A10" s="135"/>
+      <c r="B10" s="137"/>
     </row>
     <row r="11" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="142" t="s">
+      <c r="B11" s="138" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3871,672 +4850,672 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="53"/>
-      <c r="B1" s="206" t="s">
+      <c r="A1" s="49"/>
+      <c r="B1" s="194" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206" t="s">
+      <c r="C1" s="194"/>
+      <c r="D1" s="194" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206" t="s">
+      <c r="E1" s="194"/>
+      <c r="F1" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206" t="s">
+      <c r="G1" s="194"/>
+      <c r="H1" s="194" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="207"/>
+      <c r="I1" s="200"/>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="208">
+      <c r="B2" s="193">
         <v>0.745</v>
       </c>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208" t="s">
+      <c r="C2" s="193"/>
+      <c r="D2" s="193" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208">
+      <c r="E2" s="193"/>
+      <c r="F2" s="193">
         <v>0.36</v>
       </c>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208">
+      <c r="G2" s="193"/>
+      <c r="H2" s="193">
         <v>0.15</v>
       </c>
-      <c r="I2" s="208"/>
+      <c r="I2" s="193"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="201">
+      <c r="B3" s="195">
         <v>0.02</v>
       </c>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201">
+      <c r="C3" s="195"/>
+      <c r="D3" s="195">
         <v>0.03</v>
       </c>
-      <c r="E3" s="201"/>
-      <c r="F3" s="201">
+      <c r="E3" s="195"/>
+      <c r="F3" s="195">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G3" s="201"/>
-      <c r="H3" s="201">
+      <c r="G3" s="195"/>
+      <c r="H3" s="195">
         <v>5.5E-2</v>
       </c>
-      <c r="I3" s="201"/>
+      <c r="I3" s="195"/>
     </row>
     <row r="4" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="201">
+      <c r="B4" s="195">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C4" s="201"/>
-      <c r="D4" s="201">
+      <c r="C4" s="195"/>
+      <c r="D4" s="195">
         <v>0.22500000000000001</v>
       </c>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201">
+      <c r="E4" s="195"/>
+      <c r="F4" s="195">
         <v>0.35499999999999998</v>
       </c>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201">
+      <c r="G4" s="195"/>
+      <c r="H4" s="195">
         <v>0.505</v>
       </c>
-      <c r="I4" s="201"/>
+      <c r="I4" s="195"/>
     </row>
     <row r="5" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="201">
+      <c r="B5" s="195">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201">
+      <c r="C5" s="195"/>
+      <c r="D5" s="195">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201">
+      <c r="E5" s="195"/>
+      <c r="F5" s="195">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G5" s="201"/>
-      <c r="H5" s="201">
+      <c r="G5" s="195"/>
+      <c r="H5" s="195">
         <v>0.03</v>
       </c>
-      <c r="I5" s="201"/>
+      <c r="I5" s="195"/>
     </row>
     <row r="6" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="201">
+      <c r="B6" s="195">
         <v>0.04</v>
       </c>
-      <c r="C6" s="201"/>
-      <c r="D6" s="201">
+      <c r="C6" s="195"/>
+      <c r="D6" s="195">
         <v>5.5E-2</v>
       </c>
-      <c r="E6" s="201"/>
-      <c r="F6" s="201">
+      <c r="E6" s="195"/>
+      <c r="F6" s="195">
         <v>0.12</v>
       </c>
-      <c r="G6" s="201"/>
-      <c r="H6" s="201">
+      <c r="G6" s="195"/>
+      <c r="H6" s="195">
         <v>0.185</v>
       </c>
-      <c r="I6" s="201"/>
+      <c r="I6" s="195"/>
     </row>
     <row r="7" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="202">
+      <c r="B7" s="199">
         <v>0.04</v>
       </c>
-      <c r="C7" s="202"/>
-      <c r="D7" s="202">
+      <c r="C7" s="199"/>
+      <c r="D7" s="199">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E7" s="202"/>
-      <c r="F7" s="202">
+      <c r="E7" s="199"/>
+      <c r="F7" s="199">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G7" s="202"/>
-      <c r="H7" s="202">
+      <c r="G7" s="199"/>
+      <c r="H7" s="199">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I7" s="202"/>
+      <c r="I7" s="199"/>
     </row>
     <row r="8" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="203">
+      <c r="B8" s="198">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="C8" s="203"/>
-      <c r="D8" s="203">
+      <c r="C8" s="198"/>
+      <c r="D8" s="198">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203">
+      <c r="E8" s="198"/>
+      <c r="F8" s="198">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="G8" s="203"/>
-      <c r="H8" s="203">
+      <c r="G8" s="198"/>
+      <c r="H8" s="198">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="I8" s="203"/>
+      <c r="I8" s="198"/>
     </row>
     <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="204">
+      <c r="B9" s="197">
         <v>0.6</v>
       </c>
-      <c r="C9" s="204"/>
-      <c r="D9" s="204">
+      <c r="C9" s="197"/>
+      <c r="D9" s="197">
         <v>0.59</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204">
+      <c r="E9" s="197"/>
+      <c r="F9" s="197">
         <v>0.53</v>
       </c>
-      <c r="G9" s="204"/>
-      <c r="H9" s="204">
+      <c r="G9" s="197"/>
+      <c r="H9" s="197">
         <v>0.49</v>
       </c>
-      <c r="I9" s="204"/>
+      <c r="I9" s="197"/>
     </row>
     <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="201">
+      <c r="B10" s="195">
         <v>3.1E-2</v>
       </c>
-      <c r="C10" s="201"/>
-      <c r="D10" s="201">
+      <c r="C10" s="195"/>
+      <c r="D10" s="195">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="E10" s="201"/>
-      <c r="F10" s="201">
+      <c r="E10" s="195"/>
+      <c r="F10" s="195">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="G10" s="201"/>
-      <c r="H10" s="201">
+      <c r="G10" s="195"/>
+      <c r="H10" s="195">
         <v>0.10299999999999999</v>
       </c>
-      <c r="I10" s="201"/>
+      <c r="I10" s="195"/>
     </row>
     <row r="11" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="205" t="s">
+      <c r="B11" s="196" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="205"/>
-      <c r="D11" s="205" t="s">
+      <c r="C11" s="196"/>
+      <c r="D11" s="196" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="205"/>
-      <c r="F11" s="205" t="s">
+      <c r="E11" s="196"/>
+      <c r="F11" s="196" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="205"/>
-      <c r="H11" s="205" t="s">
+      <c r="G11" s="196"/>
+      <c r="H11" s="196" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="205"/>
+      <c r="I11" s="196"/>
     </row>
     <row r="12" spans="1:9" s="8" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
     </row>
     <row r="13" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="61" t="s">
+      <c r="D13" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="61" t="s">
+      <c r="E13" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="61" t="s">
+      <c r="G13" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="61" t="s">
+      <c r="H13" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="61" t="s">
+      <c r="I13" s="57" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="63">
+      <c r="B14" s="59">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="59">
         <v>-0.184</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="59">
         <v>-0.11799999999999999</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="59">
         <v>-0.25600000000000001</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="59">
         <v>-0.2</v>
       </c>
-      <c r="G14" s="63">
+      <c r="G14" s="59">
         <v>-0.32700000000000001</v>
       </c>
-      <c r="H14" s="63">
+      <c r="H14" s="59">
         <v>-0.28299999999999997</v>
       </c>
-      <c r="I14" s="63">
+      <c r="I14" s="59">
         <v>-0.39500000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="63">
+      <c r="B15" s="59">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C15" s="63">
+      <c r="C15" s="59">
         <v>-9.8000000000000004E-2</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D15" s="59">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E15" s="59">
         <v>-0.128</v>
       </c>
-      <c r="F15" s="63">
+      <c r="F15" s="59">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="G15" s="63">
+      <c r="G15" s="59">
         <v>-0.11</v>
       </c>
-      <c r="H15" s="63">
+      <c r="H15" s="59">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="I15" s="63">
+      <c r="I15" s="59">
         <v>-9.1999999999999998E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="63">
+      <c r="B16" s="59">
         <v>0.16200000000000001</v>
       </c>
-      <c r="C16" s="63">
+      <c r="C16" s="59">
         <v>0.02</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="59">
         <v>0.112</v>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="59">
         <v>-2.3E-2</v>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="59">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="G16" s="63">
+      <c r="G16" s="59">
         <v>-8.2000000000000003E-2</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="59">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="I16" s="63">
+      <c r="I16" s="59">
         <v>-0.14000000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="63">
+      <c r="B17" s="59">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="59">
         <v>-2.8000000000000001E-2</v>
       </c>
-      <c r="D17" s="63">
+      <c r="D17" s="59">
         <v>-4.8000000000000001E-2</v>
       </c>
-      <c r="E17" s="63">
+      <c r="E17" s="59">
         <v>-0.05</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="59">
         <v>-9.7000000000000003E-2</v>
       </c>
-      <c r="G17" s="63">
+      <c r="G17" s="59">
         <v>-9.9000000000000005E-2</v>
       </c>
-      <c r="H17" s="63">
+      <c r="H17" s="59">
         <v>-0.14799999999999999</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="59">
         <v>-0.15</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="63">
+      <c r="B18" s="59">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="59">
         <v>-3.5999999999999997E-2</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D18" s="59">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E18" s="59">
         <v>-5.2999999999999999E-2</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F18" s="59">
         <v>-2.7E-2</v>
       </c>
-      <c r="G18" s="63">
+      <c r="G18" s="59">
         <v>-4.7E-2</v>
       </c>
-      <c r="H18" s="63">
+      <c r="H18" s="59">
         <v>-2.1999999999999999E-2</v>
       </c>
-      <c r="I18" s="63">
+      <c r="I18" s="59">
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="63">
+      <c r="B19" s="59">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C19" s="63">
+      <c r="C19" s="59">
         <v>-4.3999999999999997E-2</v>
       </c>
-      <c r="D19" s="63">
+      <c r="D19" s="59">
         <v>-4.9000000000000002E-2</v>
       </c>
-      <c r="E19" s="63">
+      <c r="E19" s="59">
         <v>-0.1</v>
       </c>
-      <c r="F19" s="63">
+      <c r="F19" s="59">
         <v>-0.16700000000000001</v>
       </c>
-      <c r="G19" s="63">
+      <c r="G19" s="59">
         <v>-0.21199999999999999</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="59">
         <v>-0.27500000000000002</v>
       </c>
-      <c r="I19" s="63">
+      <c r="I19" s="59">
         <v>-0.315</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="63">
+      <c r="B20" s="59">
         <v>-8.7999999999999995E-2</v>
       </c>
-      <c r="C20" s="63">
+      <c r="C20" s="59">
         <v>-0.10299999999999999</v>
       </c>
-      <c r="D20" s="63">
+      <c r="D20" s="59">
         <v>-0.159</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E20" s="59">
         <v>-0.17299999999999999</v>
       </c>
-      <c r="F20" s="63">
+      <c r="F20" s="59">
         <v>-0.28299999999999997</v>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="59">
         <v>-0.29499999999999998</v>
       </c>
-      <c r="H20" s="63">
+      <c r="H20" s="59">
         <v>-0.39300000000000002</v>
       </c>
-      <c r="I20" s="63">
+      <c r="I20" s="59">
         <v>-0.40300000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="65">
+      <c r="B21" s="61">
         <v>-0.03</v>
       </c>
-      <c r="C21" s="65">
+      <c r="C21" s="61">
         <v>-2.8000000000000001E-2</v>
       </c>
-      <c r="D21" s="65">
+      <c r="D21" s="61">
         <v>-5.2999999999999999E-2</v>
       </c>
-      <c r="E21" s="65">
+      <c r="E21" s="61">
         <v>-5.0999999999999997E-2</v>
       </c>
-      <c r="F21" s="65">
+      <c r="F21" s="61">
         <v>-9.8000000000000004E-2</v>
       </c>
-      <c r="G21" s="65">
+      <c r="G21" s="61">
         <v>-9.7000000000000003E-2</v>
       </c>
-      <c r="H21" s="65">
+      <c r="H21" s="61">
         <v>-0.14499999999999999</v>
       </c>
-      <c r="I21" s="65">
+      <c r="I21" s="61">
         <v>-0.14299999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="60"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="56"/>
     </row>
     <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="199">
+      <c r="B23" s="201">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C23" s="199"/>
-      <c r="D23" s="199">
+      <c r="C23" s="201"/>
+      <c r="D23" s="201">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E23" s="199"/>
-      <c r="F23" s="199">
+      <c r="E23" s="201"/>
+      <c r="F23" s="201">
         <v>6.3E-2</v>
       </c>
-      <c r="G23" s="199"/>
-      <c r="H23" s="199">
+      <c r="G23" s="201"/>
+      <c r="H23" s="201">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="I23" s="199"/>
+      <c r="I23" s="201"/>
     </row>
     <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="62" t="s">
+      <c r="A24" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="199">
+      <c r="B24" s="201">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C24" s="199"/>
-      <c r="D24" s="199">
+      <c r="C24" s="201"/>
+      <c r="D24" s="201">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="E24" s="199"/>
-      <c r="F24" s="199">
+      <c r="E24" s="201"/>
+      <c r="F24" s="201">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G24" s="199"/>
-      <c r="H24" s="199">
+      <c r="G24" s="201"/>
+      <c r="H24" s="201">
         <v>0.24299999999999999</v>
       </c>
-      <c r="I24" s="199"/>
+      <c r="I24" s="201"/>
     </row>
     <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="62" t="s">
+      <c r="A25" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="200">
+      <c r="B25" s="202">
         <v>0</v>
       </c>
-      <c r="C25" s="200"/>
-      <c r="D25" s="200">
+      <c r="C25" s="202"/>
+      <c r="D25" s="202">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="E25" s="200"/>
-      <c r="F25" s="200">
+      <c r="E25" s="202"/>
+      <c r="F25" s="202">
         <v>0.14899999999999999</v>
       </c>
-      <c r="G25" s="200"/>
-      <c r="H25" s="200">
+      <c r="G25" s="202"/>
+      <c r="H25" s="202">
         <v>0.253</v>
       </c>
-      <c r="I25" s="200"/>
+      <c r="I25" s="202"/>
     </row>
     <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="67" t="s">
+      <c r="A26" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="68"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
     </row>
     <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="199">
+      <c r="B27" s="201">
         <v>0.23799999999999999</v>
       </c>
-      <c r="C27" s="199"/>
-      <c r="D27" s="199">
+      <c r="C27" s="201"/>
+      <c r="D27" s="201">
         <v>0.27900000000000003</v>
       </c>
-      <c r="E27" s="199"/>
-      <c r="F27" s="199">
+      <c r="E27" s="201"/>
+      <c r="F27" s="201">
         <v>0.314</v>
       </c>
-      <c r="G27" s="199"/>
-      <c r="H27" s="199">
+      <c r="G27" s="201"/>
+      <c r="H27" s="201">
         <v>0.33700000000000002</v>
       </c>
-      <c r="I27" s="199"/>
+      <c r="I27" s="201"/>
     </row>
     <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="62" t="s">
+      <c r="A28" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="199">
+      <c r="B28" s="201">
         <v>0.04</v>
       </c>
-      <c r="C28" s="199"/>
-      <c r="D28" s="199">
+      <c r="C28" s="201"/>
+      <c r="D28" s="201">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="E28" s="199"/>
-      <c r="F28" s="199">
+      <c r="E28" s="201"/>
+      <c r="F28" s="201">
         <v>0.14299999999999999</v>
       </c>
-      <c r="G28" s="199"/>
-      <c r="H28" s="199">
+      <c r="G28" s="201"/>
+      <c r="H28" s="201">
         <v>0.187</v>
       </c>
-      <c r="I28" s="199"/>
+      <c r="I28" s="201"/>
     </row>
     <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="199">
+      <c r="B29" s="201">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C29" s="199"/>
-      <c r="D29" s="199">
+      <c r="C29" s="201"/>
+      <c r="D29" s="201">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="E29" s="199"/>
-      <c r="F29" s="199">
+      <c r="E29" s="201"/>
+      <c r="F29" s="201">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G29" s="199"/>
-      <c r="H29" s="199">
+      <c r="G29" s="201"/>
+      <c r="H29" s="201">
         <v>0.108</v>
       </c>
-      <c r="I29" s="199"/>
+      <c r="I29" s="201"/>
     </row>
     <row r="30" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="59" t="s">
+      <c r="A30" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="65"/>
     </row>
     <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
@@ -4917,11 +5896,56 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="B5:C5"/>
@@ -4935,56 +5959,11 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B14:I21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
@@ -5000,7 +5979,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280EE335-971B-7742-8503-0E6908774862}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" style="11" bestFit="1" customWidth="1"/>
@@ -5008,7 +5987,7 @@
     <col min="5" max="5" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
       <c r="B1" s="3" t="s">
         <v>64</v>
@@ -5022,74 +6001,159 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="13"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G2" s="210">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>59</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="151"/>
+      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G3" s="210">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="210">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="152"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G4" s="210">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="210">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="14"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G5" s="210">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="210">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="15"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G6" s="210">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="210">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>63</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="16"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G7" s="210">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="210">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5097,8 +6161,19 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" s="2"/>
+      <c r="I8" s="210">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5106,8 +6181,17 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -5115,8 +6199,17 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -5124,8 +6217,17 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5133,8 +6235,17 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5142,9 +6253,289 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" s="12"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" s="12"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="12"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" s="12"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" s="12"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="12"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="12"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="12"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" s="12"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" s="12"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" s="12"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" s="12"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" s="12"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" s="12"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5154,7 +6545,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="18" customWidth="1"/>
+    <col min="2" max="2" width="16" style="14" customWidth="1"/>
     <col min="3" max="3" width="2.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="2.83203125" style="1" customWidth="1"/>
@@ -5167,41 +6558,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19"/>
-      <c r="B1" s="211" t="s">
+      <c r="A1" s="15"/>
+      <c r="B1" s="205" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="21"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="17"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:16" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22"/>
-      <c r="B2" s="209" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="203" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="209"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="24" t="s">
+      <c r="C2" s="203"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="20" t="s">
         <v>67</v>
       </c>
       <c r="K2" s="3"/>
@@ -5212,18 +6603,18 @@
       <c r="P2" s="3"/>
     </row>
     <row r="3" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -5232,35 +6623,35 @@
       <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="26">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="28">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="28">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="17">
         <v>0.35</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="28">
         <f>D4+2.5%</f>
         <v>3.6000000000000004E-2</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="31">
         <v>0</v>
       </c>
       <c r="K4" s="3"/>
@@ -5271,35 +6662,35 @@
       <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="33">
         <v>1E-3</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="35">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="35">
         <v>1.6E-2</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="38">
         <v>0.25</v>
       </c>
-      <c r="I5" s="39">
+      <c r="I5" s="35">
         <f>D5+2.5%</f>
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="39">
         <v>0</v>
       </c>
       <c r="K5" s="3"/>
@@ -5310,18 +6701,18 @@
       <c r="P5" s="3"/>
     </row>
     <row r="6" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="35"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="31"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -5330,35 +6721,35 @@
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="33">
         <v>1.6E-2</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="35">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="35">
         <v>0.11700000000000001</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="38">
         <v>0.3</v>
       </c>
-      <c r="I7" s="39">
+      <c r="I7" s="35">
         <f>D7+2.5%</f>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="J7" s="43">
+      <c r="J7" s="39">
         <v>0</v>
       </c>
       <c r="K7" s="3"/>
@@ -5369,18 +6760,18 @@
       <c r="P7" s="3"/>
     </row>
     <row r="8" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="35"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="31"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -5389,35 +6780,35 @@
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="26">
         <v>2.7E-2</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="28">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="28">
         <v>0.16800000000000001</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="17">
         <v>0.32</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="28">
         <f>D9+2.5%</f>
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="31">
         <v>0</v>
       </c>
       <c r="K9" s="3"/>
@@ -5428,35 +6819,35 @@
       <c r="P9" s="3"/>
     </row>
     <row r="10" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="26">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="28">
         <v>0.06</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="28">
         <v>0.14499999999999999</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="17">
         <v>0.41</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="28">
         <f t="shared" ref="I10:I30" si="0">D10+2.5%</f>
         <v>8.4999999999999992E-2</v>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="31">
         <v>0</v>
       </c>
       <c r="K10" s="3"/>
@@ -5467,35 +6858,35 @@
       <c r="P10" s="3"/>
     </row>
     <row r="11" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="26">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="28">
         <v>6.3E-2</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="34" t="s">
+      <c r="F11" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="28">
         <v>0.191</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="17">
         <v>0.33</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="28">
         <f t="shared" si="0"/>
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="31">
         <v>0</v>
       </c>
       <c r="K11" s="3"/>
@@ -5506,35 +6897,35 @@
       <c r="P11" s="3"/>
     </row>
     <row r="12" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="26">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="28">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="28">
         <v>0.16400000000000001</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="17">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="28">
         <f t="shared" si="0"/>
         <v>7.3000000000000009E-2</v>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="31">
         <v>0.7</v>
       </c>
       <c r="K12" s="3"/>
@@ -5545,35 +6936,35 @@
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="26">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="28">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="28">
         <v>0.151</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="17">
         <v>0.34</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="28">
         <f t="shared" si="0"/>
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="31">
         <v>0.7</v>
       </c>
       <c r="K13" s="3"/>
@@ -5584,35 +6975,35 @@
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="26">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="28">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="28">
         <v>0.16400000000000001</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="17">
         <v>0.16</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="28">
         <f t="shared" si="0"/>
         <v>5.1000000000000004E-2</v>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="31">
         <v>0.7</v>
       </c>
       <c r="K14" s="3"/>
@@ -5623,35 +7014,35 @@
       <c r="P14" s="3"/>
     </row>
     <row r="15" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="26">
         <v>0.04</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="28">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="28">
         <v>0.18099999999999999</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="17">
         <v>0.38</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="28">
         <f t="shared" si="0"/>
         <v>9.4E-2</v>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="31">
         <v>0.7</v>
       </c>
       <c r="K15" s="3"/>
@@ -5662,35 +7053,35 @@
       <c r="P15" s="3"/>
     </row>
     <row r="16" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="26">
         <v>0.02</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="28">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="28">
         <v>0.22</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="17">
         <v>0.39</v>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="28">
         <f t="shared" si="0"/>
         <v>0.11099999999999999</v>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="31">
         <v>0</v>
       </c>
       <c r="K16" s="3"/>
@@ -5701,35 +7092,35 @@
       <c r="P16" s="3"/>
     </row>
     <row r="17" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="26">
         <v>0.03</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="28">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="28">
         <v>0.16200000000000001</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="17">
         <v>0.38</v>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="28">
         <f t="shared" si="0"/>
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="41">
         <v>0.7</v>
       </c>
       <c r="K17" s="3"/>
@@ -5740,35 +7131,35 @@
       <c r="P17" s="3"/>
     </row>
     <row r="18" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="33">
         <v>1.9E-2</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="35">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="35">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="38">
         <v>0.34</v>
       </c>
-      <c r="I18" s="39">
+      <c r="I18" s="35">
         <f t="shared" si="0"/>
         <v>7.3000000000000009E-2</v>
       </c>
-      <c r="J18" s="43">
+      <c r="J18" s="39">
         <v>0.7</v>
       </c>
       <c r="K18" s="3"/>
@@ -5779,18 +7170,18 @@
       <c r="P18" s="3"/>
     </row>
     <row r="19" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="35"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="31"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -5799,35 +7190,35 @@
       <c r="P19" s="3"/>
     </row>
     <row r="20" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="26">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="28">
         <v>1.9E-2</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="28">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="17">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="28">
         <f t="shared" si="0"/>
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="31">
         <v>1</v>
       </c>
       <c r="K20" s="3"/>
@@ -5838,35 +7229,35 @@
       <c r="P20" s="3"/>
     </row>
     <row r="21" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="26">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="28">
         <v>2.7E-2</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="28">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="17">
         <v>0.31</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="28">
         <f t="shared" si="0"/>
         <v>5.2000000000000005E-2</v>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="31">
         <v>1</v>
       </c>
       <c r="K21" s="3"/>
@@ -5877,35 +7268,35 @@
       <c r="P21" s="3"/>
     </row>
     <row r="22" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="33">
         <v>-2E-3</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="35">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G22" s="35">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="38">
         <v>0.35</v>
       </c>
-      <c r="I22" s="39">
+      <c r="I22" s="35">
         <f t="shared" si="0"/>
         <v>5.4000000000000006E-2</v>
       </c>
-      <c r="J22" s="43">
+      <c r="J22" s="39">
         <v>1</v>
       </c>
       <c r="K22" s="3"/>
@@ -5916,18 +7307,18 @@
       <c r="P22" s="3"/>
     </row>
     <row r="23" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="35"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="31"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -5936,35 +7327,35 @@
       <c r="P23" s="3"/>
     </row>
     <row r="24" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="26">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="28">
         <v>0.08</v>
       </c>
-      <c r="E24" s="33" t="s">
+      <c r="E24" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="30">
         <v>0.113</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="28">
         <v>0.16200000000000001</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="17">
         <v>0.51</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="28">
         <f t="shared" si="0"/>
         <v>0.10500000000000001</v>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="31">
         <v>0</v>
       </c>
       <c r="K24" s="3"/>
@@ -5975,35 +7366,35 @@
       <c r="P24" s="3"/>
     </row>
     <row r="25" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="26">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="28">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="E25" s="33" t="s">
+      <c r="E25" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="30">
         <v>0.115</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="28">
         <v>0.22800000000000001</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="17">
         <v>0.51</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="28">
         <f t="shared" si="0"/>
         <v>0.10700000000000001</v>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="31">
         <v>0</v>
       </c>
       <c r="K25" s="3"/>
@@ -6014,35 +7405,35 @@
       <c r="P25" s="3"/>
     </row>
     <row r="26" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="33">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="35">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="E26" s="40" t="s">
+      <c r="E26" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F26" s="41" t="s">
+      <c r="F26" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="35">
         <v>0.22800000000000001</v>
       </c>
-      <c r="H26" s="42">
+      <c r="H26" s="38">
         <v>0.32</v>
       </c>
-      <c r="I26" s="39">
+      <c r="I26" s="35">
         <f t="shared" si="0"/>
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="J26" s="43">
+      <c r="J26" s="39">
         <v>0</v>
       </c>
       <c r="K26" s="3"/>
@@ -6053,18 +7444,18 @@
       <c r="P26" s="3"/>
     </row>
     <row r="27" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="153" t="s">
+      <c r="A27" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="35"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="31"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -6073,35 +7464,35 @@
       <c r="P27" s="3"/>
     </row>
     <row r="28" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="26">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="28">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="E28" s="33" t="s">
+      <c r="E28" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="28">
         <v>0.11</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="17">
         <v>0.4</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="28">
         <f t="shared" si="0"/>
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="31">
         <v>0</v>
       </c>
       <c r="K28" s="3"/>
@@ -6112,35 +7503,35 @@
       <c r="P28" s="3"/>
     </row>
     <row r="29" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="26">
         <v>2.3E-2</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="28">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="34" t="s">
+      <c r="F29" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="28">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="17">
         <v>0.53</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="28">
         <f t="shared" si="0"/>
         <v>6.3E-2</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="31">
         <v>0</v>
       </c>
       <c r="K29" s="3"/>
@@ -6151,35 +7542,35 @@
       <c r="P29" s="3"/>
     </row>
     <row r="30" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="46" t="s">
+      <c r="A30" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="43">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="49">
+      <c r="D30" s="45">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="E30" s="50" t="s">
+      <c r="E30" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="F30" s="51" t="s">
+      <c r="F30" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="G30" s="49">
+      <c r="G30" s="45">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="16">
         <v>0.51</v>
       </c>
-      <c r="I30" s="49">
+      <c r="I30" s="45">
         <f t="shared" si="0"/>
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="J30" s="52">
+      <c r="J30" s="48">
         <v>0</v>
       </c>
       <c r="K30" s="3"/>
@@ -6191,7 +7582,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -6209,7 +7600,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
-      <c r="B32" s="17"/>
+      <c r="B32" s="13"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -6227,7 +7618,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
-      <c r="B33" s="17"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -6245,7 +7636,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
-      <c r="B34" s="17"/>
+      <c r="B34" s="13"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -6263,7 +7654,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
-      <c r="B35" s="17"/>
+      <c r="B35" s="13"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -6281,7 +7672,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
-      <c r="B36" s="17"/>
+      <c r="B36" s="13"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -6299,7 +7690,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
-      <c r="B37" s="17"/>
+      <c r="B37" s="13"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -6339,832 +7730,832 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="155"/>
-      <c r="B1" s="212" t="s">
+      <c r="A1" s="149"/>
+      <c r="B1" s="206" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="212"/>
-      <c r="D1" s="212"/>
-      <c r="E1" s="212"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="212" t="s">
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="206" t="s">
         <v>154</v>
       </c>
-      <c r="J1" s="212"/>
+      <c r="J1" s="206"/>
     </row>
     <row r="2" spans="1:10" s="8" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="157"/>
-      <c r="B2" s="213" t="s">
+      <c r="A2" s="151"/>
+      <c r="B2" s="207" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="159" t="s">
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="153" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="159" t="s">
+      <c r="F2" s="153" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="158" t="s">
+      <c r="G2" s="152" t="s">
         <v>151</v>
       </c>
-      <c r="H2" s="159" t="s">
+      <c r="H2" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="159" t="s">
+      <c r="I2" s="153" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="159" t="s">
+      <c r="J2" s="153" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="160" t="s">
+    <row r="3" spans="1:10" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="154" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="161"/>
-      <c r="C3" s="161"/>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="161"/>
-      <c r="I3" s="161"/>
-      <c r="J3" s="161"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="155" t="s">
+      <c r="A4" s="149" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="162">
+      <c r="B4" s="156">
         <v>5.7241236937856403E-3</v>
       </c>
-      <c r="C4" s="163">
+      <c r="C4" s="157">
         <v>1.08524678406041E-2</v>
       </c>
-      <c r="D4" s="164">
+      <c r="D4" s="158">
         <v>1.59808119874227E-2</v>
       </c>
-      <c r="E4" s="163">
+      <c r="E4" s="157">
         <v>3.2071468696963902E-2</v>
       </c>
-      <c r="F4" s="165">
+      <c r="F4" s="159">
         <v>0.33838387456298602</v>
       </c>
-      <c r="G4" s="163">
+      <c r="G4" s="157">
         <v>3.5852467840604099E-2</v>
       </c>
-      <c r="H4" s="166">
+      <c r="H4" s="160">
         <v>0</v>
       </c>
-      <c r="I4" s="167">
+      <c r="I4" s="161">
         <v>26723</v>
       </c>
-      <c r="J4" s="167">
+      <c r="J4" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="177" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="184">
+      <c r="B5" s="178">
         <v>4.32971260588862E-4</v>
       </c>
-      <c r="C5" s="185">
+      <c r="C5" s="179">
         <v>3.0821903711752401E-3</v>
       </c>
-      <c r="D5" s="186">
+      <c r="D5" s="180">
         <v>5.73140948176162E-3</v>
       </c>
-      <c r="E5" s="185">
+      <c r="E5" s="179">
         <v>1.4716286970652999E-2</v>
       </c>
-      <c r="F5" s="187">
+      <c r="F5" s="181">
         <v>0.20944076296702299</v>
       </c>
-      <c r="G5" s="185">
+      <c r="G5" s="179">
         <v>2.8082190371175202E-2</v>
       </c>
-      <c r="H5" s="188">
+      <c r="H5" s="182">
         <v>0</v>
       </c>
-      <c r="I5" s="189">
+      <c r="I5" s="183">
         <v>33662</v>
       </c>
-      <c r="J5" s="189">
+      <c r="J5" s="183">
         <v>45777</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="176" t="s">
+    <row r="6" spans="1:10" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="177"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="179"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="180"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="181"/>
-      <c r="I6" s="182"/>
-      <c r="J6" s="182"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="175"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="176"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="183" t="s">
+      <c r="A7" s="177" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="184">
+      <c r="B7" s="178">
         <v>2.64039774019777E-2</v>
       </c>
-      <c r="C7" s="185">
+      <c r="C7" s="179">
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="D7" s="186">
+      <c r="D7" s="180">
         <v>6.0324053411324102E-2</v>
       </c>
-      <c r="E7" s="185">
+      <c r="E7" s="179">
         <v>0.106064123700363</v>
       </c>
-      <c r="F7" s="187">
+      <c r="F7" s="181">
         <v>0.40884715673658401</v>
       </c>
-      <c r="G7" s="185">
+      <c r="G7" s="179">
         <v>6.8364015406650894E-2</v>
       </c>
-      <c r="H7" s="188">
+      <c r="H7" s="182">
         <v>0</v>
       </c>
-      <c r="I7" s="189">
+      <c r="I7" s="183">
         <v>30589</v>
       </c>
-      <c r="J7" s="189">
+      <c r="J7" s="183">
         <v>45777</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="176" t="s">
+    <row r="8" spans="1:10" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="177"/>
-      <c r="C8" s="178"/>
-      <c r="D8" s="179"/>
-      <c r="E8" s="178"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="178"/>
-      <c r="H8" s="181"/>
-      <c r="I8" s="182"/>
-      <c r="J8" s="182"/>
+      <c r="B8" s="171"/>
+      <c r="C8" s="172"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="172"/>
+      <c r="F8" s="174"/>
+      <c r="G8" s="172"/>
+      <c r="H8" s="175"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="149" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="162">
+      <c r="B9" s="156">
         <v>1.7523010713942501E-2</v>
       </c>
-      <c r="C9" s="163">
+      <c r="C9" s="157">
         <v>4.4567317353041203E-2</v>
       </c>
-      <c r="D9" s="164">
+      <c r="D9" s="158">
         <v>7.1611623992139897E-2</v>
       </c>
-      <c r="E9" s="163">
+      <c r="E9" s="157">
         <v>0.16912878874266299</v>
       </c>
-      <c r="F9" s="165">
+      <c r="F9" s="159">
         <v>0.26351112477280397</v>
       </c>
-      <c r="G9" s="163">
+      <c r="G9" s="157">
         <v>6.9567317353041197E-2</v>
       </c>
-      <c r="H9" s="166">
+      <c r="H9" s="160">
         <v>0</v>
       </c>
-      <c r="I9" s="167">
+      <c r="I9" s="161">
         <v>28886</v>
       </c>
-      <c r="J9" s="167">
+      <c r="J9" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="155" t="s">
+      <c r="A10" s="149" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="162">
+      <c r="B10" s="156">
         <v>3.7739774522967298E-2</v>
       </c>
-      <c r="C10" s="163">
+      <c r="C10" s="157">
         <v>6.09896272276437E-2</v>
       </c>
-      <c r="D10" s="164">
+      <c r="D10" s="158">
         <v>8.4239479932320005E-2</v>
       </c>
-      <c r="E10" s="163">
+      <c r="E10" s="157">
         <v>0.145399158457341</v>
       </c>
-      <c r="F10" s="165">
+      <c r="F10" s="159">
         <v>0.41946341281980098</v>
       </c>
-      <c r="G10" s="163">
+      <c r="G10" s="157">
         <v>8.5989627227643695E-2</v>
       </c>
-      <c r="H10" s="166">
+      <c r="H10" s="160">
         <v>0</v>
       </c>
-      <c r="I10" s="167">
+      <c r="I10" s="161">
         <v>28886</v>
       </c>
-      <c r="J10" s="167">
+      <c r="J10" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="149" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="162">
+      <c r="B11" s="156">
         <v>3.9116118459153602E-2</v>
       </c>
-      <c r="C11" s="163">
+      <c r="C11" s="157">
         <v>6.9881103642633002E-2</v>
       </c>
-      <c r="D11" s="164">
+      <c r="D11" s="158">
         <v>0.10064608882611201</v>
       </c>
-      <c r="E11" s="163">
+      <c r="E11" s="157">
         <v>0.19239704493830101</v>
       </c>
-      <c r="F11" s="165">
+      <c r="F11" s="159">
         <v>0.36321297795942198</v>
       </c>
-      <c r="G11" s="163">
+      <c r="G11" s="157">
         <v>9.4881103642632997E-2</v>
       </c>
-      <c r="H11" s="166">
+      <c r="H11" s="160">
         <v>0</v>
       </c>
-      <c r="I11" s="167">
+      <c r="I11" s="161">
         <v>28886</v>
       </c>
-      <c r="J11" s="167">
+      <c r="J11" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="155" t="s">
+      <c r="A12" s="149" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="162">
+      <c r="B12" s="156">
         <v>2.0982633206710101E-2</v>
       </c>
-      <c r="C12" s="163">
+      <c r="C12" s="157">
         <v>4.7043208728656999E-2</v>
       </c>
-      <c r="D12" s="164">
+      <c r="D12" s="158">
         <v>7.3103784250604098E-2</v>
       </c>
-      <c r="E12" s="163">
+      <c r="E12" s="157">
         <v>0.16297676367829</v>
       </c>
-      <c r="F12" s="165">
+      <c r="F12" s="159">
         <v>0.288649790724268</v>
       </c>
-      <c r="G12" s="163">
+      <c r="G12" s="157">
         <v>7.2043208728657104E-2</v>
       </c>
-      <c r="H12" s="166">
+      <c r="H12" s="160">
         <v>0.7</v>
       </c>
-      <c r="I12" s="167">
+      <c r="I12" s="161">
         <v>25626</v>
       </c>
-      <c r="J12" s="167">
+      <c r="J12" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="155" t="s">
+      <c r="A13" s="149" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="162">
+      <c r="B13" s="156">
         <v>2.5237430201924101E-2</v>
       </c>
-      <c r="C13" s="163">
+      <c r="C13" s="157">
         <v>4.8975926757622301E-2</v>
       </c>
-      <c r="D13" s="164">
+      <c r="D13" s="158">
         <v>7.2714423313320495E-2</v>
       </c>
-      <c r="E13" s="163">
+      <c r="E13" s="157">
         <v>0.14845502318157899</v>
       </c>
-      <c r="F13" s="165">
+      <c r="F13" s="159">
         <v>0.32990414004192098</v>
       </c>
-      <c r="G13" s="163">
+      <c r="G13" s="157">
         <v>7.3975926757622296E-2</v>
       </c>
-      <c r="H13" s="166">
+      <c r="H13" s="160">
         <v>0.7</v>
       </c>
-      <c r="I13" s="167">
+      <c r="I13" s="161">
         <v>25598</v>
       </c>
-      <c r="J13" s="167">
+      <c r="J13" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="155" t="s">
+      <c r="A14" s="149" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="162">
+      <c r="B14" s="156">
         <v>-1.15459534877681E-3</v>
       </c>
-      <c r="C14" s="163">
+      <c r="C14" s="157">
         <v>2.82523559089745E-2</v>
       </c>
-      <c r="D14" s="164">
+      <c r="D14" s="158">
         <v>5.76593071667258E-2</v>
       </c>
-      <c r="E14" s="163">
+      <c r="E14" s="157">
         <v>0.18390421737222901</v>
       </c>
-      <c r="F14" s="165">
+      <c r="F14" s="159">
         <v>0.15362538343419599</v>
       </c>
-      <c r="G14" s="163">
+      <c r="G14" s="157">
         <v>5.3252355908974501E-2</v>
       </c>
-      <c r="H14" s="166">
+      <c r="H14" s="160">
         <v>0.7</v>
       </c>
-      <c r="I14" s="167">
+      <c r="I14" s="161">
         <v>25598</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="149" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="162">
+      <c r="B15" s="156">
         <v>2.74370548378081E-2</v>
       </c>
-      <c r="C15" s="163">
+      <c r="C15" s="157">
         <v>5.6359980577740498E-2</v>
       </c>
-      <c r="D15" s="164">
+      <c r="D15" s="158">
         <v>8.5282906317672894E-2</v>
       </c>
-      <c r="E15" s="163">
+      <c r="E15" s="157">
         <v>0.17096972354367099</v>
       </c>
-      <c r="F15" s="165">
+      <c r="F15" s="159">
         <v>0.32964889577857998</v>
       </c>
-      <c r="G15" s="163">
+      <c r="G15" s="157">
         <v>8.1359980577740507E-2</v>
       </c>
-      <c r="H15" s="166">
+      <c r="H15" s="160">
         <v>0.7</v>
       </c>
-      <c r="I15" s="167">
+      <c r="I15" s="161">
         <v>25626</v>
       </c>
-      <c r="J15" s="167">
+      <c r="J15" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="149" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="162">
+      <c r="B16" s="156">
         <v>3.5865028766390701E-2</v>
       </c>
-      <c r="C16" s="163">
+      <c r="C16" s="157">
         <v>7.5241692772873098E-2</v>
       </c>
-      <c r="D16" s="164">
+      <c r="D16" s="158">
         <v>0.114618356779355</v>
       </c>
-      <c r="E16" s="163">
+      <c r="E16" s="157">
         <v>0.23276405090531699</v>
       </c>
-      <c r="F16" s="165">
+      <c r="F16" s="159">
         <v>0.32325306455282199</v>
       </c>
-      <c r="G16" s="163">
+      <c r="G16" s="157">
         <v>0.100241692772873</v>
       </c>
-      <c r="H16" s="166">
+      <c r="H16" s="160">
         <v>0</v>
       </c>
-      <c r="I16" s="167">
+      <c r="I16" s="161">
         <v>32171</v>
       </c>
-      <c r="J16" s="167">
+      <c r="J16" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="155" t="s">
+      <c r="A17" s="149" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="162">
+      <c r="B17" s="156">
         <v>3.9211523567242897E-2</v>
       </c>
-      <c r="C17" s="163">
+      <c r="C17" s="157">
         <v>6.4800724140040705E-2</v>
       </c>
-      <c r="D17" s="164">
+      <c r="D17" s="158">
         <v>9.0389924712838396E-2</v>
       </c>
-      <c r="E17" s="163">
+      <c r="E17" s="157">
         <v>0.14797197236920701</v>
       </c>
-      <c r="F17" s="165">
+      <c r="F17" s="159">
         <v>0.43792566323543602</v>
       </c>
-      <c r="G17" s="163">
+      <c r="G17" s="157">
         <v>8.98007241400407E-2</v>
       </c>
-      <c r="H17" s="166">
+      <c r="H17" s="160">
         <v>0.7</v>
       </c>
-      <c r="I17" s="167">
+      <c r="I17" s="161">
         <v>32720</v>
       </c>
-      <c r="J17" s="167">
+      <c r="J17" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="183" t="s">
+      <c r="A18" s="177" t="s">
         <v>147</v>
       </c>
-      <c r="B18" s="184">
+      <c r="B18" s="178">
         <v>1.6403181443203799E-2</v>
       </c>
-      <c r="C18" s="185">
+      <c r="C18" s="179">
         <v>4.4976836696510598E-2</v>
       </c>
-      <c r="D18" s="186">
+      <c r="D18" s="180">
         <v>7.3550491949817401E-2</v>
       </c>
-      <c r="E18" s="185">
+      <c r="E18" s="179">
         <v>0.139789727557039</v>
       </c>
-      <c r="F18" s="187">
+      <c r="F18" s="181">
         <v>0.32174636493341902</v>
       </c>
-      <c r="G18" s="185">
+      <c r="G18" s="179">
         <v>6.99768366965106E-2</v>
       </c>
-      <c r="H18" s="188">
+      <c r="H18" s="182">
         <v>0.7</v>
       </c>
-      <c r="I18" s="189">
+      <c r="I18" s="183">
         <v>36189</v>
       </c>
-      <c r="J18" s="189">
+      <c r="J18" s="183">
         <v>45777</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="176" t="s">
+    <row r="19" spans="1:10" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="177"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="179"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="180"/>
-      <c r="G19" s="178"/>
-      <c r="H19" s="181"/>
-      <c r="I19" s="182"/>
-      <c r="J19" s="182"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="172"/>
+      <c r="F19" s="174"/>
+      <c r="G19" s="172"/>
+      <c r="H19" s="175"/>
+      <c r="I19" s="176"/>
+      <c r="J19" s="176"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="155" t="s">
+      <c r="A20" s="149" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="162">
+      <c r="B20" s="156">
         <v>7.6750631221554899E-3</v>
       </c>
-      <c r="C20" s="163">
+      <c r="C20" s="157">
         <v>1.9169505465816701E-2</v>
       </c>
-      <c r="D20" s="164">
+      <c r="D20" s="158">
         <v>3.0663947809477999E-2</v>
       </c>
-      <c r="E20" s="163">
+      <c r="E20" s="157">
         <v>6.1826317761391997E-2</v>
       </c>
-      <c r="F20" s="175">
+      <c r="F20" s="169">
         <v>0.31005413487178901</v>
       </c>
-      <c r="G20" s="163">
+      <c r="G20" s="157">
         <v>4.41695054658168E-2</v>
       </c>
-      <c r="H20" s="166">
+      <c r="H20" s="160">
         <v>1</v>
       </c>
-      <c r="I20" s="167">
+      <c r="I20" s="161">
         <v>34365</v>
       </c>
-      <c r="J20" s="167">
+      <c r="J20" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="155" t="s">
+      <c r="A21" s="149" t="s">
         <v>184</v>
       </c>
-      <c r="B21" s="162">
+      <c r="B21" s="156">
         <v>4.3657888915111303E-3</v>
       </c>
-      <c r="C21" s="163">
+      <c r="C21" s="157">
         <v>2.0771382280796301E-2</v>
       </c>
-      <c r="D21" s="164">
+      <c r="D21" s="158">
         <v>3.7176975670081602E-2</v>
       </c>
-      <c r="E21" s="163">
+      <c r="E21" s="157">
         <v>8.8242421826534606E-2</v>
       </c>
-      <c r="F21" s="165">
+      <c r="F21" s="159">
         <v>0.23538998421449001</v>
       </c>
-      <c r="G21" s="163">
+      <c r="G21" s="157">
         <v>4.5771382280796302E-2</v>
       </c>
-      <c r="H21" s="166">
+      <c r="H21" s="160">
         <v>1</v>
       </c>
-      <c r="I21" s="167">
+      <c r="I21" s="161">
         <v>34365</v>
       </c>
-      <c r="J21" s="167">
+      <c r="J21" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="183" t="s">
+      <c r="A22" s="177" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="184">
+      <c r="B22" s="178">
         <v>3.4812134452342201E-3</v>
       </c>
-      <c r="C22" s="185">
+      <c r="C22" s="179">
         <v>1.8658048030354601E-2</v>
       </c>
-      <c r="D22" s="186">
+      <c r="D22" s="180">
         <v>3.3834882615475001E-2</v>
       </c>
-      <c r="E22" s="185">
+      <c r="E22" s="179">
         <v>8.1633172764504602E-2</v>
       </c>
-      <c r="F22" s="187">
+      <c r="F22" s="181">
         <v>0.228559633277753</v>
       </c>
-      <c r="G22" s="185">
+      <c r="G22" s="179">
         <v>4.3658048030354599E-2</v>
       </c>
-      <c r="H22" s="188">
+      <c r="H22" s="182">
         <v>1</v>
       </c>
-      <c r="I22" s="189">
+      <c r="I22" s="183">
         <v>34365</v>
       </c>
-      <c r="J22" s="189">
+      <c r="J22" s="183">
         <v>45777</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="176" t="s">
+    <row r="23" spans="1:10" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="177"/>
-      <c r="C23" s="178"/>
-      <c r="D23" s="179"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="180"/>
-      <c r="G23" s="178"/>
-      <c r="H23" s="181"/>
-      <c r="I23" s="182"/>
-      <c r="J23" s="182"/>
+      <c r="B23" s="171"/>
+      <c r="C23" s="172"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="172"/>
+      <c r="F23" s="174"/>
+      <c r="G23" s="172"/>
+      <c r="H23" s="175"/>
+      <c r="I23" s="176"/>
+      <c r="J23" s="176"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="155" t="s">
+      <c r="A24" s="149" t="s">
         <v>144</v>
       </c>
-      <c r="B24" s="162">
+      <c r="B24" s="156">
         <v>2.6608812004023499E-2</v>
       </c>
-      <c r="C24" s="163">
+      <c r="C24" s="157">
         <v>5.0216749358222103E-2</v>
       </c>
-      <c r="D24" s="164">
+      <c r="D24" s="158">
         <v>7.3824686712420803E-2</v>
       </c>
-      <c r="E24" s="163">
+      <c r="E24" s="157">
         <v>0.14763853637333799</v>
       </c>
-      <c r="F24" s="165">
+      <c r="F24" s="159">
         <v>0.340133074952987</v>
       </c>
-      <c r="G24" s="163">
+      <c r="G24" s="157">
         <v>7.5216749358222104E-2</v>
       </c>
-      <c r="H24" s="166">
+      <c r="H24" s="160">
         <v>0</v>
       </c>
-      <c r="I24" s="167">
+      <c r="I24" s="161">
         <v>25598</v>
       </c>
-      <c r="J24" s="167">
+      <c r="J24" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="155" t="s">
+      <c r="A25" s="149" t="s">
         <v>185</v>
       </c>
-      <c r="B25" s="162">
+      <c r="B25" s="156">
         <v>1.78707608365977E-2</v>
       </c>
-      <c r="C25" s="163">
+      <c r="C25" s="157">
         <v>3.5944264317563202E-2</v>
       </c>
-      <c r="D25" s="164">
+      <c r="D25" s="158">
         <v>5.40177677985288E-2</v>
       </c>
-      <c r="E25" s="163">
+      <c r="E25" s="157">
         <v>9.7213778264937697E-2</v>
       </c>
-      <c r="F25" s="165">
+      <c r="F25" s="159">
         <v>0.369744546082799</v>
       </c>
-      <c r="G25" s="163">
+      <c r="G25" s="157">
         <v>6.0944264317563203E-2</v>
       </c>
-      <c r="H25" s="166">
+      <c r="H25" s="160">
         <v>0</v>
       </c>
-      <c r="I25" s="167">
+      <c r="I25" s="161">
         <v>34365</v>
       </c>
-      <c r="J25" s="167">
+      <c r="J25" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="183" t="s">
+      <c r="A26" s="177" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="184">
+      <c r="B26" s="178">
         <v>1.3852677823030299E-2</v>
       </c>
-      <c r="C26" s="185">
+      <c r="C26" s="179">
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="D26" s="186">
+      <c r="D26" s="180">
         <v>8.1345289061248299E-2</v>
       </c>
-      <c r="E26" s="185">
+      <c r="E26" s="179">
         <v>0.21081962919687999</v>
       </c>
-      <c r="F26" s="187">
+      <c r="F26" s="181">
         <v>0.225780605076804</v>
       </c>
-      <c r="G26" s="185">
+      <c r="G26" s="179">
         <v>7.2598983442139303E-2</v>
       </c>
-      <c r="H26" s="188">
+      <c r="H26" s="182">
         <v>0</v>
       </c>
-      <c r="I26" s="189">
+      <c r="I26" s="183">
         <v>30680</v>
       </c>
-      <c r="J26" s="189">
+      <c r="J26" s="183">
         <v>44925</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="154" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="176" t="s">
+    <row r="27" spans="1:10" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="177"/>
-      <c r="C27" s="178"/>
-      <c r="D27" s="179"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="180"/>
-      <c r="G27" s="178"/>
-      <c r="H27" s="181"/>
-      <c r="I27" s="182"/>
-      <c r="J27" s="182"/>
+      <c r="B27" s="171"/>
+      <c r="C27" s="172"/>
+      <c r="D27" s="173"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="174"/>
+      <c r="G27" s="172"/>
+      <c r="H27" s="175"/>
+      <c r="I27" s="176"/>
+      <c r="J27" s="176"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="155" t="s">
+      <c r="A28" s="149" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="162">
+      <c r="B28" s="156">
         <v>2.64039774019777E-2</v>
       </c>
-      <c r="C28" s="163">
+      <c r="C28" s="157">
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="D28" s="164">
+      <c r="D28" s="158">
         <v>6.0324053411324102E-2</v>
       </c>
-      <c r="E28" s="163">
+      <c r="E28" s="157">
         <v>0.106064123700363</v>
       </c>
-      <c r="F28" s="165">
+      <c r="F28" s="159">
         <v>0.40884715673658401</v>
       </c>
-      <c r="G28" s="163">
+      <c r="G28" s="157">
         <v>6.8364015406650894E-2</v>
       </c>
-      <c r="H28" s="166">
+      <c r="H28" s="160">
         <v>0</v>
       </c>
-      <c r="I28" s="167">
+      <c r="I28" s="161">
         <v>30589</v>
       </c>
-      <c r="J28" s="167">
+      <c r="J28" s="161">
         <v>45777</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="155" t="s">
+      <c r="A29" s="149" t="s">
         <v>186</v>
       </c>
-      <c r="B29" s="162">
+      <c r="B29" s="156">
         <v>3.9132178171297799E-2</v>
       </c>
-      <c r="C29" s="163">
+      <c r="C29" s="157">
         <v>6.2011235623535797E-2</v>
       </c>
-      <c r="D29" s="164">
+      <c r="D29" s="158">
         <v>8.4890293075773796E-2</v>
       </c>
-      <c r="E29" s="163">
+      <c r="E29" s="157">
         <v>0.143080291393996</v>
       </c>
-      <c r="F29" s="165">
+      <c r="F29" s="159">
         <v>0.43340165874262299</v>
       </c>
-      <c r="G29" s="163">
+      <c r="G29" s="157">
         <v>8.7011235623535799E-2</v>
       </c>
-      <c r="H29" s="166">
+      <c r="H29" s="160">
         <v>0</v>
       </c>
-      <c r="I29" s="167">
+      <c r="I29" s="161">
         <v>30650</v>
       </c>
-      <c r="J29" s="167">
+      <c r="J29" s="161">
         <v>44925</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="168" t="s">
+      <c r="A30" s="162" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="169">
+      <c r="B30" s="163">
         <v>1.3852677823030299E-2</v>
       </c>
-      <c r="C30" s="170">
+      <c r="C30" s="164">
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="D30" s="171">
+      <c r="D30" s="165">
         <v>8.1345289061248299E-2</v>
       </c>
-      <c r="E30" s="170">
+      <c r="E30" s="164">
         <v>0.21081962919687999</v>
       </c>
-      <c r="F30" s="172">
+      <c r="F30" s="166">
         <v>0.225780605076804</v>
       </c>
-      <c r="G30" s="170">
+      <c r="G30" s="164">
         <v>7.2598983442139303E-2</v>
       </c>
-      <c r="H30" s="173">
+      <c r="H30" s="167">
         <v>0</v>
       </c>
-      <c r="I30" s="174">
+      <c r="I30" s="168">
         <v>30680</v>
       </c>
-      <c r="J30" s="174">
+      <c r="J30" s="168">
         <v>44925</v>
       </c>
     </row>
@@ -7193,28 +8584,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="C1" s="86" t="s">
+      <c r="C1" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="87" t="s">
+      <c r="D1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="87" t="s">
+      <c r="E1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="87" t="s">
+      <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="88" t="s">
+      <c r="H1" s="84" t="s">
         <v>99</v>
       </c>
     </row>
@@ -7222,25 +8613,25 @@
       <c r="A2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="56">
+      <c r="D2" s="52">
         <v>0.245</v>
       </c>
-      <c r="E2" s="56">
+      <c r="E2" s="52">
         <v>0.58499999999999996</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="52">
         <v>0.36</v>
       </c>
-      <c r="G2" s="56">
+      <c r="G2" s="52">
         <v>0.15</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7248,25 +8639,25 @@
       <c r="A3" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="56">
+      <c r="D3" s="52">
         <v>0.5</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7274,25 +8665,25 @@
       <c r="A4" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="70" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="56">
+      <c r="D4" s="52">
         <v>0.02</v>
       </c>
-      <c r="E4" s="56">
+      <c r="E4" s="52">
         <v>0.03</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="52">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G4" s="56">
+      <c r="G4" s="52">
         <v>5.5E-2</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7300,25 +8691,25 @@
       <c r="A5" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="74" t="s">
+      <c r="C5" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="56">
+      <c r="D5" s="52">
         <v>3.9E-2</v>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="52">
         <v>6.3E-2</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="52">
         <v>0.1</v>
       </c>
-      <c r="G5" s="56">
+      <c r="G5" s="52">
         <v>0.14199999999999999</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7326,25 +8717,25 @@
       <c r="A6" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="74" t="s">
+      <c r="B6" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="56">
+      <c r="D6" s="52">
         <v>4.4000000000000004E-2</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="52">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="52">
         <v>0.11199999999999999</v>
       </c>
-      <c r="G6" s="56">
+      <c r="G6" s="52">
         <v>0.159</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7352,25 +8743,25 @@
       <c r="A7" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="52">
         <v>1.3999999999999999E-2</v>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="52">
         <v>2.2000000000000002E-2</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="52">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="52">
         <v>0.05</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7378,25 +8769,25 @@
       <c r="A8" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="52">
         <v>1.6E-2</v>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="52">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="52">
         <v>0.04</v>
       </c>
-      <c r="G8" s="56">
+      <c r="G8" s="52">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="31">
         <v>0.7</v>
       </c>
     </row>
@@ -7404,25 +8795,25 @@
       <c r="A9" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="52">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="52">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="52">
         <v>1.2E-2</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="52">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="31">
         <v>0.7</v>
       </c>
     </row>
@@ -7430,25 +8821,25 @@
       <c r="A10" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="74" t="s">
+      <c r="C10" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="52">
         <v>6.9999999999999993E-3</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="52">
         <v>1.1000000000000001E-2</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="52">
         <v>1.8000000000000002E-2</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="52">
         <v>2.6000000000000002E-2</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="31">
         <v>0.7</v>
       </c>
     </row>
@@ -7456,25 +8847,25 @@
       <c r="A11" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="52">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="52">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="52">
         <v>9.0000000000000011E-3</v>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="52">
         <v>1.3000000000000001E-2</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="31">
         <v>0.7</v>
       </c>
     </row>
@@ -7482,25 +8873,25 @@
       <c r="A12" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="52">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="52">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="52">
         <v>9.0000000000000011E-3</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="52">
         <v>1.3000000000000001E-2</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7508,25 +8899,25 @@
       <c r="A13" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C13" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="52">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="52">
         <v>6.5000000000000006E-3</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="52">
         <v>0.01</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="52">
         <v>1.3999999999999999E-2</v>
       </c>
-      <c r="H13" s="89">
+      <c r="H13" s="85">
         <v>0.7</v>
       </c>
     </row>
@@ -7534,25 +8925,25 @@
       <c r="A14" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="74" t="s">
+      <c r="C14" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D14" s="52">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E14" s="52">
         <v>6.5000000000000006E-3</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="52">
         <v>0.01</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="52">
         <v>1.3999999999999999E-2</v>
       </c>
-      <c r="H14" s="89">
+      <c r="H14" s="85">
         <v>0.7</v>
       </c>
     </row>
@@ -7560,25 +8951,25 @@
       <c r="A15" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="52">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="52">
         <v>6.9999999999999993E-3</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="52">
         <v>9.0000000000000011E-3</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="52">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="31">
         <v>1</v>
       </c>
     </row>
@@ -7586,25 +8977,25 @@
       <c r="A16" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="52">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="52">
         <v>1.3999999999999999E-2</v>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="52">
         <v>1.8000000000000002E-2</v>
       </c>
-      <c r="G16" s="56">
+      <c r="G16" s="52">
         <v>1.2E-2</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="31">
         <v>1</v>
       </c>
     </row>
@@ -7612,25 +9003,25 @@
       <c r="A17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="B17" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="74" t="s">
+      <c r="C17" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="56">
+      <c r="D17" s="52">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="52">
         <v>1.3999999999999999E-2</v>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="52">
         <v>1.8000000000000002E-2</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="52">
         <v>1.2E-2</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="31">
         <v>1</v>
       </c>
     </row>
@@ -7638,25 +9029,25 @@
       <c r="A18" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="74" t="s">
+      <c r="C18" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="56">
+      <c r="D18" s="52">
         <v>0.03</v>
       </c>
-      <c r="E18" s="56">
+      <c r="E18" s="52">
         <v>4.0999999999999995E-2</v>
       </c>
-      <c r="F18" s="56">
+      <c r="F18" s="52">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="G18" s="56">
+      <c r="G18" s="52">
         <v>0.13</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7664,25 +9055,25 @@
       <c r="A19" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="56">
+      <c r="D19" s="52">
         <v>0.01</v>
       </c>
-      <c r="E19" s="56">
+      <c r="E19" s="52">
         <v>1.3999999999999999E-2</v>
       </c>
-      <c r="F19" s="56">
+      <c r="F19" s="52">
         <v>2.7999999999999997E-2</v>
       </c>
-      <c r="G19" s="56">
+      <c r="G19" s="52">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7690,25 +9081,25 @@
       <c r="A20" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="74" t="s">
+      <c r="C20" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="56">
+      <c r="D20" s="52">
         <v>0</v>
       </c>
-      <c r="E20" s="56">
+      <c r="E20" s="52">
         <v>0</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="52">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="52">
         <v>1.2E-2</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7716,25 +9107,25 @@
       <c r="A21" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="74" t="s">
+      <c r="C21" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="56">
+      <c r="D21" s="52">
         <v>1.3000000000000001E-2</v>
       </c>
-      <c r="E21" s="56">
+      <c r="E21" s="52">
         <v>2.3E-2</v>
       </c>
-      <c r="F21" s="56">
+      <c r="F21" s="52">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G21" s="56">
+      <c r="G21" s="52">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7742,25 +9133,25 @@
       <c r="A22" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="74" t="s">
+      <c r="C22" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="52">
         <v>1.3500000000000002E-2</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="52">
         <v>2.35E-2</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="52">
         <v>0.02</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="52">
         <v>0.02</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="31">
         <v>0</v>
       </c>
     </row>
@@ -7768,51 +9159,51 @@
       <c r="A23" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="74" t="s">
+      <c r="C23" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="56">
+      <c r="D23" s="52">
         <v>1.3500000000000002E-2</v>
       </c>
-      <c r="E23" s="56">
+      <c r="E23" s="52">
         <v>2.35E-2</v>
       </c>
-      <c r="F23" s="56">
+      <c r="F23" s="52">
         <v>0.02</v>
       </c>
-      <c r="G23" s="56">
+      <c r="G23" s="52">
         <v>0.02</v>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="84"/>
-      <c r="B24" s="82" t="s">
+      <c r="A24" s="80"/>
+      <c r="B24" s="78" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="82"/>
-      <c r="D24" s="90">
+      <c r="C24" s="78"/>
+      <c r="D24" s="86">
         <f>SUM(D2:D23)</f>
         <v>1.0010000000000001</v>
       </c>
-      <c r="E24" s="90">
+      <c r="E24" s="86">
         <f t="shared" ref="E24:G24" si="0">SUM(E2:E23)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F24" s="90">
+      <c r="F24" s="86">
         <f t="shared" si="0"/>
         <v>1.0000000000000002</v>
       </c>
-      <c r="G24" s="90">
+      <c r="G24" s="86">
         <f t="shared" si="0"/>
         <v>1.0000000000000002</v>
       </c>
-      <c r="H24" s="83"/>
+      <c r="H24" s="79"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7834,59 +9225,59 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
-      <c r="B1" s="214" t="s">
+      <c r="B1" s="208" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="214" t="s">
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="208" t="s">
         <v>154</v>
       </c>
-      <c r="J1" s="214"/>
+      <c r="J1" s="208"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:13" s="8" customFormat="1" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96" t="s">
+      <c r="A2" s="91"/>
+      <c r="B2" s="92" t="s">
         <v>148</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="93" t="s">
         <v>149</v>
       </c>
-      <c r="D2" s="96" t="s">
+      <c r="D2" s="92" t="s">
         <v>150</v>
       </c>
-      <c r="E2" s="96" t="s">
+      <c r="E2" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="97" t="s">
+      <c r="G2" s="93" t="s">
         <v>151</v>
       </c>
-      <c r="H2" s="96" t="s">
+      <c r="H2" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="96" t="s">
+      <c r="I2" s="92" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="96" t="s">
+      <c r="J2" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="120" t="s">
+      <c r="K2" s="116" t="s">
         <v>155</v>
       </c>
-      <c r="L2" s="96" t="s">
+      <c r="L2" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="M2" s="112" t="s">
+      <c r="M2" s="108" t="s">
         <v>157</v>
       </c>
     </row>
@@ -7894,59 +9285,59 @@
       <c r="A3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="114"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="110"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="88">
         <v>5.7241236937856403E-3</v>
       </c>
-      <c r="C4" s="92">
+      <c r="C4" s="88">
         <v>1.08524678406041E-2</v>
       </c>
-      <c r="D4" s="92">
+      <c r="D4" s="88">
         <v>1.59808119874227E-2</v>
       </c>
-      <c r="E4" s="92">
+      <c r="E4" s="88">
         <v>3.2071468696963902E-2</v>
       </c>
-      <c r="F4" s="93">
+      <c r="F4" s="89">
         <v>0.33838387456298602</v>
       </c>
-      <c r="G4" s="92">
+      <c r="G4" s="88">
         <v>3.5852467840604099E-2</v>
       </c>
-      <c r="H4" s="92">
+      <c r="H4" s="88">
         <v>0</v>
       </c>
-      <c r="I4" s="99">
+      <c r="I4" s="95">
         <v>26723</v>
       </c>
-      <c r="J4" s="99">
+      <c r="J4" s="95">
         <v>45777</v>
       </c>
-      <c r="K4" s="122">
+      <c r="K4" s="118">
         <f>Assumptions!D4</f>
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="L4" s="115">
+      <c r="L4" s="111">
         <f>C4</f>
         <v>1.08524678406041E-2</v>
       </c>
-      <c r="M4" s="116">
+      <c r="M4" s="112">
         <f>L4-K4</f>
         <v>-1.4753215939589982E-4</v>
       </c>
@@ -7955,42 +9346,42 @@
       <c r="A5" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B5" s="92">
+      <c r="B5" s="88">
         <v>4.32971260588862E-4</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="88">
         <v>3.0821903711752401E-3</v>
       </c>
-      <c r="D5" s="92">
+      <c r="D5" s="88">
         <v>5.73140948176162E-3</v>
       </c>
-      <c r="E5" s="92">
+      <c r="E5" s="88">
         <v>1.4716286970652999E-2</v>
       </c>
-      <c r="F5" s="93">
+      <c r="F5" s="89">
         <v>0.20944076296702299</v>
       </c>
-      <c r="G5" s="92">
+      <c r="G5" s="88">
         <v>2.8082190371175202E-2</v>
       </c>
-      <c r="H5" s="92">
+      <c r="H5" s="88">
         <v>0</v>
       </c>
-      <c r="I5" s="99">
+      <c r="I5" s="95">
         <v>33662</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="95">
         <v>45777</v>
       </c>
-      <c r="K5" s="122">
+      <c r="K5" s="118">
         <f>Assumptions!D5</f>
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L5" s="115">
+      <c r="L5" s="111">
         <f t="shared" ref="L5:L30" si="0">C5</f>
         <v>3.0821903711752401E-3</v>
       </c>
-      <c r="M5" s="116">
+      <c r="M5" s="112">
         <f t="shared" ref="M5:M30" si="1">L5-K5</f>
         <v>-9.1780962882475996E-4</v>
       </c>
@@ -7999,59 +9390,59 @@
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="116"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="112"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="108" t="s">
+      <c r="A7" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="109">
+      <c r="B7" s="105">
         <v>2.64039774019777E-2</v>
       </c>
-      <c r="C7" s="109">
+      <c r="C7" s="105">
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="D7" s="109">
+      <c r="D7" s="105">
         <v>6.0324053411324102E-2</v>
       </c>
-      <c r="E7" s="109">
+      <c r="E7" s="105">
         <v>0.106064123700363</v>
       </c>
-      <c r="F7" s="110">
+      <c r="F7" s="106">
         <v>0.40884715673658401</v>
       </c>
-      <c r="G7" s="109">
+      <c r="G7" s="105">
         <v>6.8364015406650894E-2</v>
       </c>
-      <c r="H7" s="109">
+      <c r="H7" s="105">
         <v>0</v>
       </c>
-      <c r="I7" s="111">
+      <c r="I7" s="107">
         <v>30589</v>
       </c>
-      <c r="J7" s="111">
+      <c r="J7" s="107">
         <v>45777</v>
       </c>
-      <c r="K7" s="123">
+      <c r="K7" s="119">
         <f>Assumptions!D7</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="L7" s="117">
+      <c r="L7" s="113">
         <f t="shared" si="0"/>
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="M7" s="118">
+      <c r="M7" s="114">
         <f t="shared" si="1"/>
         <v>8.3640154066508959E-3</v>
       </c>
@@ -8060,59 +9451,59 @@
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="92"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="116"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="112"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="108" t="s">
+      <c r="A9" s="104" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="109">
+      <c r="B9" s="105">
         <v>1.7523010713942501E-2</v>
       </c>
-      <c r="C9" s="109">
+      <c r="C9" s="105">
         <v>4.4567317353041203E-2</v>
       </c>
-      <c r="D9" s="109">
+      <c r="D9" s="105">
         <v>7.1611623992139897E-2</v>
       </c>
-      <c r="E9" s="109">
+      <c r="E9" s="105">
         <v>0.16912878874266299</v>
       </c>
-      <c r="F9" s="110">
+      <c r="F9" s="106">
         <v>0.26351112477280397</v>
       </c>
-      <c r="G9" s="109">
+      <c r="G9" s="105">
         <v>6.9567317353041197E-2</v>
       </c>
-      <c r="H9" s="109">
+      <c r="H9" s="105">
         <v>0</v>
       </c>
-      <c r="I9" s="111">
+      <c r="I9" s="107">
         <v>28886</v>
       </c>
-      <c r="J9" s="111">
+      <c r="J9" s="107">
         <v>45777</v>
       </c>
-      <c r="K9" s="123">
+      <c r="K9" s="119">
         <f>Assumptions!D9</f>
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="L9" s="117">
+      <c r="L9" s="113">
         <f t="shared" si="0"/>
         <v>4.4567317353041203E-2</v>
       </c>
-      <c r="M9" s="118">
+      <c r="M9" s="114">
         <f t="shared" si="1"/>
         <v>-9.4326826469587968E-3</v>
       </c>
@@ -8121,86 +9512,86 @@
       <c r="A10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="92">
+      <c r="B10" s="88">
         <v>3.7739774522967298E-2</v>
       </c>
-      <c r="C10" s="92">
+      <c r="C10" s="88">
         <v>6.09896272276437E-2</v>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="88">
         <v>8.4239479932320005E-2</v>
       </c>
-      <c r="E10" s="92">
+      <c r="E10" s="88">
         <v>0.145399158457341</v>
       </c>
-      <c r="F10" s="93">
+      <c r="F10" s="89">
         <v>0.41946341281980098</v>
       </c>
-      <c r="G10" s="92">
+      <c r="G10" s="88">
         <v>8.5989627227643695E-2</v>
       </c>
-      <c r="H10" s="92">
+      <c r="H10" s="88">
         <v>0</v>
       </c>
-      <c r="I10" s="99">
+      <c r="I10" s="95">
         <v>28886</v>
       </c>
-      <c r="J10" s="99">
+      <c r="J10" s="95">
         <v>45777</v>
       </c>
-      <c r="K10" s="122">
+      <c r="K10" s="118">
         <f>Assumptions!D10</f>
         <v>0.06</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="111">
         <f t="shared" si="0"/>
         <v>6.09896272276437E-2</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="112">
         <f t="shared" si="1"/>
         <v>9.8962722764370237E-4</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="108" t="s">
+      <c r="A11" s="104" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="109">
+      <c r="B11" s="105">
         <v>3.9116118459153602E-2</v>
       </c>
-      <c r="C11" s="109">
+      <c r="C11" s="105">
         <v>6.9881103642633002E-2</v>
       </c>
-      <c r="D11" s="109">
+      <c r="D11" s="105">
         <v>0.10064608882611201</v>
       </c>
-      <c r="E11" s="109">
+      <c r="E11" s="105">
         <v>0.19239704493830101</v>
       </c>
-      <c r="F11" s="110">
+      <c r="F11" s="106">
         <v>0.36321297795942198</v>
       </c>
-      <c r="G11" s="109">
+      <c r="G11" s="105">
         <v>9.4881103642632997E-2</v>
       </c>
-      <c r="H11" s="109">
+      <c r="H11" s="105">
         <v>0</v>
       </c>
-      <c r="I11" s="111">
+      <c r="I11" s="107">
         <v>28886</v>
       </c>
-      <c r="J11" s="111">
+      <c r="J11" s="107">
         <v>45777</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="119">
         <f>Assumptions!D11</f>
         <v>6.3E-2</v>
       </c>
-      <c r="L11" s="117">
+      <c r="L11" s="113">
         <f t="shared" si="0"/>
         <v>6.9881103642633002E-2</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="114">
         <f t="shared" si="1"/>
         <v>6.8811036426330019E-3</v>
       </c>
@@ -8209,42 +9600,42 @@
       <c r="A12" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="92">
+      <c r="B12" s="88">
         <v>2.0982633206710101E-2</v>
       </c>
-      <c r="C12" s="92">
+      <c r="C12" s="88">
         <v>4.7043208728656999E-2</v>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="88">
         <v>7.3103784250604098E-2</v>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="88">
         <v>0.16297676367829</v>
       </c>
-      <c r="F12" s="93">
+      <c r="F12" s="89">
         <v>0.288649790724268</v>
       </c>
-      <c r="G12" s="92">
+      <c r="G12" s="88">
         <v>7.2043208728657104E-2</v>
       </c>
-      <c r="H12" s="92">
+      <c r="H12" s="88">
         <v>0.7</v>
       </c>
-      <c r="I12" s="99">
+      <c r="I12" s="95">
         <v>25626</v>
       </c>
-      <c r="J12" s="99">
+      <c r="J12" s="95">
         <v>45777</v>
       </c>
-      <c r="K12" s="122">
+      <c r="K12" s="118">
         <f>Assumptions!D12</f>
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="L12" s="115">
+      <c r="L12" s="111">
         <f t="shared" si="0"/>
         <v>4.7043208728656999E-2</v>
       </c>
-      <c r="M12" s="116">
+      <c r="M12" s="112">
         <f t="shared" si="1"/>
         <v>-9.5679127134300213E-4</v>
       </c>
@@ -8253,42 +9644,42 @@
       <c r="A13" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="92">
+      <c r="B13" s="88">
         <v>2.5237430201924101E-2</v>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="88">
         <v>4.8975926757622301E-2</v>
       </c>
-      <c r="D13" s="92">
+      <c r="D13" s="88">
         <v>7.2714423313320495E-2</v>
       </c>
-      <c r="E13" s="92">
+      <c r="E13" s="88">
         <v>0.14845502318157899</v>
       </c>
-      <c r="F13" s="93">
+      <c r="F13" s="89">
         <v>0.32990414004192098</v>
       </c>
-      <c r="G13" s="92">
+      <c r="G13" s="88">
         <v>7.3975926757622296E-2</v>
       </c>
-      <c r="H13" s="92">
+      <c r="H13" s="88">
         <v>0.7</v>
       </c>
-      <c r="I13" s="99">
+      <c r="I13" s="95">
         <v>25598</v>
       </c>
-      <c r="J13" s="99">
+      <c r="J13" s="95">
         <v>45777</v>
       </c>
-      <c r="K13" s="122">
+      <c r="K13" s="118">
         <f>Assumptions!D13</f>
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="L13" s="115">
+      <c r="L13" s="111">
         <f t="shared" si="0"/>
         <v>4.8975926757622301E-2</v>
       </c>
-      <c r="M13" s="116">
+      <c r="M13" s="112">
         <f t="shared" si="1"/>
         <v>-2.0240732423776955E-3</v>
       </c>
@@ -8297,130 +9688,130 @@
       <c r="A14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="92">
+      <c r="B14" s="88">
         <v>-1.15459534877681E-3</v>
       </c>
-      <c r="C14" s="92">
+      <c r="C14" s="88">
         <v>2.82523559089745E-2</v>
       </c>
-      <c r="D14" s="92">
+      <c r="D14" s="88">
         <v>5.76593071667258E-2</v>
       </c>
-      <c r="E14" s="92">
+      <c r="E14" s="88">
         <v>0.18390421737222901</v>
       </c>
-      <c r="F14" s="93">
+      <c r="F14" s="89">
         <v>0.15362538343419599</v>
       </c>
-      <c r="G14" s="92">
+      <c r="G14" s="88">
         <v>5.3252355908974501E-2</v>
       </c>
-      <c r="H14" s="92">
+      <c r="H14" s="88">
         <v>0.7</v>
       </c>
-      <c r="I14" s="99">
+      <c r="I14" s="95">
         <v>25598</v>
       </c>
-      <c r="J14" s="99">
+      <c r="J14" s="95">
         <v>45777</v>
       </c>
-      <c r="K14" s="122">
+      <c r="K14" s="118">
         <f>Assumptions!D14</f>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="L14" s="115">
+      <c r="L14" s="111">
         <f t="shared" si="0"/>
         <v>2.82523559089745E-2</v>
       </c>
-      <c r="M14" s="116">
+      <c r="M14" s="112">
         <f t="shared" si="1"/>
         <v>2.2523559089745009E-3</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="108" t="s">
+      <c r="A15" s="104" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="109">
+      <c r="B15" s="105">
         <v>2.74370548378081E-2</v>
       </c>
-      <c r="C15" s="109">
+      <c r="C15" s="105">
         <v>5.6359980577740498E-2</v>
       </c>
-      <c r="D15" s="109">
+      <c r="D15" s="105">
         <v>8.5282906317672894E-2</v>
       </c>
-      <c r="E15" s="109">
+      <c r="E15" s="105">
         <v>0.17096972354367099</v>
       </c>
-      <c r="F15" s="110">
+      <c r="F15" s="106">
         <v>0.32964889577857998</v>
       </c>
-      <c r="G15" s="109">
+      <c r="G15" s="105">
         <v>8.1359980577740507E-2</v>
       </c>
-      <c r="H15" s="109">
+      <c r="H15" s="105">
         <v>0.7</v>
       </c>
-      <c r="I15" s="111">
+      <c r="I15" s="107">
         <v>25626</v>
       </c>
-      <c r="J15" s="111">
+      <c r="J15" s="107">
         <v>45777</v>
       </c>
-      <c r="K15" s="123">
+      <c r="K15" s="119">
         <f>Assumptions!D15</f>
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="L15" s="117">
+      <c r="L15" s="113">
         <f t="shared" si="0"/>
         <v>5.6359980577740498E-2</v>
       </c>
-      <c r="M15" s="118">
+      <c r="M15" s="114">
         <f t="shared" si="1"/>
         <v>-1.2640019422259507E-2</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="108" t="s">
+      <c r="A16" s="104" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="109">
+      <c r="B16" s="105">
         <v>3.5865028766390701E-2</v>
       </c>
-      <c r="C16" s="109">
+      <c r="C16" s="105">
         <v>7.5241692772873098E-2</v>
       </c>
-      <c r="D16" s="109">
+      <c r="D16" s="105">
         <v>0.114618356779355</v>
       </c>
-      <c r="E16" s="109">
+      <c r="E16" s="105">
         <v>0.23276405090531699</v>
       </c>
-      <c r="F16" s="110">
+      <c r="F16" s="106">
         <v>0.32325306455282199</v>
       </c>
-      <c r="G16" s="109">
+      <c r="G16" s="105">
         <v>0.100241692772873</v>
       </c>
-      <c r="H16" s="109">
+      <c r="H16" s="105">
         <v>0</v>
       </c>
-      <c r="I16" s="111">
+      <c r="I16" s="107">
         <v>32171</v>
       </c>
-      <c r="J16" s="111">
+      <c r="J16" s="107">
         <v>45777</v>
       </c>
-      <c r="K16" s="123">
+      <c r="K16" s="119">
         <f>Assumptions!D16</f>
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="L16" s="117">
+      <c r="L16" s="113">
         <f t="shared" si="0"/>
         <v>7.5241692772873098E-2</v>
       </c>
-      <c r="M16" s="118">
+      <c r="M16" s="114">
         <f t="shared" si="1"/>
         <v>-1.0758307227126895E-2</v>
       </c>
@@ -8429,42 +9820,42 @@
       <c r="A17" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="92">
+      <c r="B17" s="88">
         <v>3.9211523567242897E-2</v>
       </c>
-      <c r="C17" s="92">
+      <c r="C17" s="88">
         <v>6.4800724140040705E-2</v>
       </c>
-      <c r="D17" s="92">
+      <c r="D17" s="88">
         <v>9.0389924712838396E-2</v>
       </c>
-      <c r="E17" s="92">
+      <c r="E17" s="88">
         <v>0.14797197236920701</v>
       </c>
-      <c r="F17" s="93">
+      <c r="F17" s="89">
         <v>0.43792566323543602</v>
       </c>
-      <c r="G17" s="92">
+      <c r="G17" s="88">
         <v>8.98007241400407E-2</v>
       </c>
-      <c r="H17" s="92">
+      <c r="H17" s="88">
         <v>0.7</v>
       </c>
-      <c r="I17" s="99">
+      <c r="I17" s="95">
         <v>32720</v>
       </c>
-      <c r="J17" s="99">
+      <c r="J17" s="95">
         <v>45777</v>
       </c>
-      <c r="K17" s="122">
+      <c r="K17" s="118">
         <f>Assumptions!D17</f>
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="L17" s="115">
+      <c r="L17" s="111">
         <f t="shared" si="0"/>
         <v>6.4800724140040705E-2</v>
       </c>
-      <c r="M17" s="116">
+      <c r="M17" s="112">
         <f t="shared" si="1"/>
         <v>3.8007241400407066E-3</v>
       </c>
@@ -8473,42 +9864,42 @@
       <c r="A18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B18" s="92">
+      <c r="B18" s="88">
         <v>1.6403181443203799E-2</v>
       </c>
-      <c r="C18" s="92">
+      <c r="C18" s="88">
         <v>4.4976836696510598E-2</v>
       </c>
-      <c r="D18" s="92">
+      <c r="D18" s="88">
         <v>7.3550491949817401E-2</v>
       </c>
-      <c r="E18" s="92">
+      <c r="E18" s="88">
         <v>0.139789727557039</v>
       </c>
-      <c r="F18" s="93">
+      <c r="F18" s="89">
         <v>0.32174636493341902</v>
       </c>
-      <c r="G18" s="92">
+      <c r="G18" s="88">
         <v>6.99768366965106E-2</v>
       </c>
-      <c r="H18" s="92">
+      <c r="H18" s="88">
         <v>0.7</v>
       </c>
-      <c r="I18" s="99">
+      <c r="I18" s="95">
         <v>36189</v>
       </c>
-      <c r="J18" s="99">
+      <c r="J18" s="95">
         <v>45777</v>
       </c>
-      <c r="K18" s="122">
+      <c r="K18" s="118">
         <f>Assumptions!D18</f>
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="L18" s="115">
+      <c r="L18" s="111">
         <f t="shared" si="0"/>
         <v>4.4976836696510598E-2</v>
       </c>
-      <c r="M18" s="116">
+      <c r="M18" s="112">
         <f t="shared" si="1"/>
         <v>-3.0231633034894026E-3</v>
       </c>
@@ -8517,147 +9908,147 @@
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="92"/>
-      <c r="I19" s="99"/>
-      <c r="J19" s="99"/>
-      <c r="K19" s="122"/>
-      <c r="L19" s="115"/>
-      <c r="M19" s="116"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="112"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="92">
+      <c r="B20" s="88">
         <v>7.6750631221554899E-3</v>
       </c>
-      <c r="C20" s="92">
+      <c r="C20" s="88">
         <v>1.9169505465816701E-2</v>
       </c>
-      <c r="D20" s="92">
+      <c r="D20" s="88">
         <v>3.0663947809477999E-2</v>
       </c>
-      <c r="E20" s="92">
+      <c r="E20" s="88">
         <v>6.1826317761391997E-2</v>
       </c>
-      <c r="F20" s="93">
+      <c r="F20" s="89">
         <v>0.31005413487178901</v>
       </c>
-      <c r="G20" s="92">
+      <c r="G20" s="88">
         <v>4.41695054658168E-2</v>
       </c>
-      <c r="H20" s="92">
+      <c r="H20" s="88">
         <v>1</v>
       </c>
-      <c r="I20" s="99">
+      <c r="I20" s="95">
         <v>34365</v>
       </c>
-      <c r="J20" s="99">
+      <c r="J20" s="95">
         <v>45777</v>
       </c>
-      <c r="K20" s="122">
+      <c r="K20" s="118">
         <f>Assumptions!D20</f>
         <v>1.9E-2</v>
       </c>
-      <c r="L20" s="115">
+      <c r="L20" s="111">
         <f t="shared" si="0"/>
         <v>1.9169505465816701E-2</v>
       </c>
-      <c r="M20" s="116">
+      <c r="M20" s="112">
         <f t="shared" si="1"/>
         <v>1.6950546581670153E-4</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="108" t="s">
+      <c r="A21" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="109">
+      <c r="B21" s="105">
         <v>4.3657888915111303E-3</v>
       </c>
-      <c r="C21" s="109">
+      <c r="C21" s="105">
         <v>2.0771382280796301E-2</v>
       </c>
-      <c r="D21" s="109">
+      <c r="D21" s="105">
         <v>3.7176975670081602E-2</v>
       </c>
-      <c r="E21" s="109">
+      <c r="E21" s="105">
         <v>8.8242421826534606E-2</v>
       </c>
-      <c r="F21" s="110">
+      <c r="F21" s="106">
         <v>0.23538998421449001</v>
       </c>
-      <c r="G21" s="109">
+      <c r="G21" s="105">
         <v>4.5771382280796302E-2</v>
       </c>
-      <c r="H21" s="109">
+      <c r="H21" s="105">
         <v>1</v>
       </c>
-      <c r="I21" s="111">
+      <c r="I21" s="107">
         <v>34365</v>
       </c>
-      <c r="J21" s="111">
+      <c r="J21" s="107">
         <v>45777</v>
       </c>
-      <c r="K21" s="123">
+      <c r="K21" s="119">
         <f>Assumptions!D21</f>
         <v>2.7E-2</v>
       </c>
-      <c r="L21" s="117">
+      <c r="L21" s="113">
         <f t="shared" si="0"/>
         <v>2.0771382280796301E-2</v>
       </c>
-      <c r="M21" s="118">
+      <c r="M21" s="114">
         <f t="shared" si="1"/>
         <v>-6.2286177192036989E-3</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="108" t="s">
+      <c r="A22" s="104" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="109">
+      <c r="B22" s="105">
         <v>3.4812134452342201E-3</v>
       </c>
-      <c r="C22" s="109">
+      <c r="C22" s="105">
         <v>1.8658048030354601E-2</v>
       </c>
-      <c r="D22" s="109">
+      <c r="D22" s="105">
         <v>3.3834882615475001E-2</v>
       </c>
-      <c r="E22" s="109">
+      <c r="E22" s="105">
         <v>8.1633172764504602E-2</v>
       </c>
-      <c r="F22" s="110">
+      <c r="F22" s="106">
         <v>0.228559633277753</v>
       </c>
-      <c r="G22" s="109">
+      <c r="G22" s="105">
         <v>4.3658048030354599E-2</v>
       </c>
-      <c r="H22" s="109">
+      <c r="H22" s="105">
         <v>1</v>
       </c>
-      <c r="I22" s="111">
+      <c r="I22" s="107">
         <v>34365</v>
       </c>
-      <c r="J22" s="111">
+      <c r="J22" s="107">
         <v>45777</v>
       </c>
-      <c r="K22" s="123">
+      <c r="K22" s="119">
         <f>Assumptions!D22</f>
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="L22" s="117">
+      <c r="L22" s="113">
         <f t="shared" si="0"/>
         <v>1.8658048030354601E-2</v>
       </c>
-      <c r="M22" s="118">
+      <c r="M22" s="114">
         <f t="shared" si="1"/>
         <v>-1.0341951969645401E-2</v>
       </c>
@@ -8666,59 +10057,59 @@
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="99"/>
-      <c r="J23" s="99"/>
-      <c r="K23" s="122"/>
-      <c r="L23" s="115"/>
-      <c r="M23" s="116"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="112"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B24" s="92">
+      <c r="B24" s="88">
         <v>2.6608812004023499E-2</v>
       </c>
-      <c r="C24" s="92">
+      <c r="C24" s="88">
         <v>5.0216749358222103E-2</v>
       </c>
-      <c r="D24" s="92">
+      <c r="D24" s="88">
         <v>7.3824686712420803E-2</v>
       </c>
-      <c r="E24" s="92">
+      <c r="E24" s="88">
         <v>0.14763853637333799</v>
       </c>
-      <c r="F24" s="93">
+      <c r="F24" s="89">
         <v>0.340133074952987</v>
       </c>
-      <c r="G24" s="92">
+      <c r="G24" s="88">
         <v>7.5216749358222104E-2</v>
       </c>
-      <c r="H24" s="92">
+      <c r="H24" s="88">
         <v>0</v>
       </c>
-      <c r="I24" s="99">
+      <c r="I24" s="95">
         <v>25598</v>
       </c>
-      <c r="J24" s="99">
+      <c r="J24" s="95">
         <v>45777</v>
       </c>
-      <c r="K24" s="122">
+      <c r="K24" s="118">
         <f>Assumptions!D24</f>
         <v>0.08</v>
       </c>
-      <c r="L24" s="115">
+      <c r="L24" s="111">
         <f t="shared" si="0"/>
         <v>5.0216749358222103E-2</v>
       </c>
-      <c r="M24" s="116">
+      <c r="M24" s="112">
         <f t="shared" si="1"/>
         <v>-2.9783250641777899E-2</v>
       </c>
@@ -8727,42 +10118,42 @@
       <c r="A25" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="92">
+      <c r="B25" s="88">
         <v>1.78707608365977E-2</v>
       </c>
-      <c r="C25" s="92">
+      <c r="C25" s="88">
         <v>3.5944264317563202E-2</v>
       </c>
-      <c r="D25" s="92">
+      <c r="D25" s="88">
         <v>5.40177677985288E-2</v>
       </c>
-      <c r="E25" s="92">
+      <c r="E25" s="88">
         <v>9.7213778264937697E-2</v>
       </c>
-      <c r="F25" s="93">
+      <c r="F25" s="89">
         <v>0.369744546082799</v>
       </c>
-      <c r="G25" s="92">
+      <c r="G25" s="88">
         <v>6.0944264317563203E-2</v>
       </c>
-      <c r="H25" s="92">
+      <c r="H25" s="88">
         <v>0</v>
       </c>
-      <c r="I25" s="99">
+      <c r="I25" s="95">
         <v>34365</v>
       </c>
-      <c r="J25" s="99">
+      <c r="J25" s="95">
         <v>45777</v>
       </c>
-      <c r="K25" s="122">
+      <c r="K25" s="118">
         <f>Assumptions!D25</f>
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="L25" s="115">
+      <c r="L25" s="111">
         <f t="shared" si="0"/>
         <v>3.5944264317563202E-2</v>
       </c>
-      <c r="M25" s="116">
+      <c r="M25" s="112">
         <f t="shared" si="1"/>
         <v>-4.6055735682436802E-2</v>
       </c>
@@ -8771,42 +10162,42 @@
       <c r="A26" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="92">
+      <c r="B26" s="88">
         <v>1.3852677823030299E-2</v>
       </c>
-      <c r="C26" s="92">
+      <c r="C26" s="88">
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="D26" s="92">
+      <c r="D26" s="88">
         <v>8.1345289061248299E-2</v>
       </c>
-      <c r="E26" s="92">
+      <c r="E26" s="88">
         <v>0.21081962919687999</v>
       </c>
-      <c r="F26" s="93">
+      <c r="F26" s="89">
         <v>0.225780605076804</v>
       </c>
-      <c r="G26" s="92">
+      <c r="G26" s="88">
         <v>7.2598983442139303E-2</v>
       </c>
-      <c r="H26" s="92">
+      <c r="H26" s="88">
         <v>0</v>
       </c>
-      <c r="I26" s="99">
+      <c r="I26" s="95">
         <v>30680</v>
       </c>
-      <c r="J26" s="99">
+      <c r="J26" s="95">
         <v>44925</v>
       </c>
-      <c r="K26" s="122">
+      <c r="K26" s="118">
         <f>Assumptions!D26</f>
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="L26" s="115">
+      <c r="L26" s="111">
         <f t="shared" si="0"/>
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="M26" s="116">
+      <c r="M26" s="112">
         <f t="shared" si="1"/>
         <v>-2.5401016557860694E-2</v>
       </c>
@@ -8815,147 +10206,147 @@
       <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="92"/>
-      <c r="H27" s="92"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="115"/>
-      <c r="M27" s="116"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="118"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="112"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="92">
+      <c r="B28" s="88">
         <v>2.64039774019777E-2</v>
       </c>
-      <c r="C28" s="92">
+      <c r="C28" s="88">
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="D28" s="92">
+      <c r="D28" s="88">
         <v>6.0324053411324102E-2</v>
       </c>
-      <c r="E28" s="92">
+      <c r="E28" s="88">
         <v>0.106064123700363</v>
       </c>
-      <c r="F28" s="93">
+      <c r="F28" s="89">
         <v>0.40884715673658401</v>
       </c>
-      <c r="G28" s="92">
+      <c r="G28" s="88">
         <v>6.8364015406650894E-2</v>
       </c>
-      <c r="H28" s="92">
+      <c r="H28" s="88">
         <v>0</v>
       </c>
-      <c r="I28" s="99">
+      <c r="I28" s="95">
         <v>30589</v>
       </c>
-      <c r="J28" s="99">
+      <c r="J28" s="95">
         <v>45777</v>
       </c>
-      <c r="K28" s="122">
+      <c r="K28" s="118">
         <f>Assumptions!D28</f>
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="L28" s="115">
+      <c r="L28" s="111">
         <f t="shared" si="0"/>
         <v>4.3364015406650899E-2</v>
       </c>
-      <c r="M28" s="116">
+      <c r="M28" s="112">
         <f t="shared" si="1"/>
         <v>-6.3598459334909818E-4</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="100" t="s">
+      <c r="A29" s="96" t="s">
         <v>142</v>
       </c>
-      <c r="B29" s="101">
+      <c r="B29" s="97">
         <v>3.9132178171297799E-2</v>
       </c>
-      <c r="C29" s="101">
+      <c r="C29" s="97">
         <v>6.2011235623535797E-2</v>
       </c>
-      <c r="D29" s="101">
+      <c r="D29" s="97">
         <v>8.4890293075773796E-2</v>
       </c>
-      <c r="E29" s="101">
+      <c r="E29" s="97">
         <v>0.143080291393996</v>
       </c>
-      <c r="F29" s="102">
+      <c r="F29" s="98">
         <v>0.43340165874262299</v>
       </c>
-      <c r="G29" s="101">
+      <c r="G29" s="97">
         <v>8.7011235623535799E-2</v>
       </c>
-      <c r="H29" s="101">
+      <c r="H29" s="97">
         <v>0</v>
       </c>
-      <c r="I29" s="103">
+      <c r="I29" s="99">
         <v>30650</v>
       </c>
-      <c r="J29" s="103">
+      <c r="J29" s="99">
         <v>44925</v>
       </c>
-      <c r="K29" s="122">
+      <c r="K29" s="118">
         <f>Assumptions!D29</f>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="L29" s="115">
+      <c r="L29" s="111">
         <f t="shared" si="0"/>
         <v>6.2011235623535797E-2</v>
       </c>
-      <c r="M29" s="116">
+      <c r="M29" s="112">
         <f t="shared" si="1"/>
         <v>2.4011235623535798E-2</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="94" t="s">
+      <c r="A30" s="90" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="104">
+      <c r="B30" s="100">
         <v>1.3852677823030299E-2</v>
       </c>
-      <c r="C30" s="104">
+      <c r="C30" s="100">
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="D30" s="104">
+      <c r="D30" s="100">
         <v>8.1345289061248299E-2</v>
       </c>
-      <c r="E30" s="104">
+      <c r="E30" s="100">
         <v>0.21081962919687999</v>
       </c>
-      <c r="F30" s="105">
+      <c r="F30" s="101">
         <v>0.225780605076804</v>
       </c>
-      <c r="G30" s="104">
+      <c r="G30" s="100">
         <v>7.2598983442139303E-2</v>
       </c>
-      <c r="H30" s="104">
+      <c r="H30" s="100">
         <v>0</v>
       </c>
-      <c r="I30" s="106">
+      <c r="I30" s="102">
         <v>30680</v>
       </c>
-      <c r="J30" s="106">
+      <c r="J30" s="102">
         <v>44925</v>
       </c>
-      <c r="K30" s="124">
+      <c r="K30" s="120">
         <f>Assumptions!D30</f>
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="L30" s="107">
+      <c r="L30" s="103">
         <f t="shared" si="0"/>
         <v>4.7598983442139302E-2</v>
       </c>
-      <c r="M30" s="119">
+      <c r="M30" s="115">
         <f t="shared" si="1"/>
         <v>4.5989834421393053E-3</v>
       </c>
@@ -9114,78 +10505,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="139" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="143" t="s">
+      <c r="B1" s="139" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="140" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="124" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="145" t="s">
+      <c r="A3" s="141" t="s">
         <v>165</v>
       </c>
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="141" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="146" t="s">
+      <c r="A4" s="142" t="s">
         <v>164</v>
       </c>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="143" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="129"/>
-      <c r="B5" s="129"/>
+      <c r="A5" s="125"/>
+      <c r="B5" s="125"/>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="129" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="133" t="s">
+      <c r="B6" s="129" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="129" t="s">
         <v>162</v>
       </c>
-      <c r="B7" s="133" t="s">
+      <c r="B7" s="129" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="130"/>
-      <c r="B8" s="131"/>
+      <c r="A8" s="126"/>
+      <c r="B8" s="127"/>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="133" t="s">
+      <c r="A9" s="129" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="133" t="s">
+      <c r="B9" s="129" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="130"/>
-      <c r="B10" s="132"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="128"/>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="133" t="s">
+      <c r="A11" s="129" t="s">
         <v>162</v>
       </c>
-      <c r="B11" s="133" t="s">
+      <c r="B11" s="129" t="s">
         <v>162</v>
       </c>
     </row>
